--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="238">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -559,6 +559,9 @@
     <t>['51', '90+8']</t>
   </si>
   <si>
+    <t>['5', '16', '24', '79']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -719,6 +722,12 @@
   </si>
   <si>
     <t>['22']</t>
+  </si>
+  <si>
+    <t>['66']</t>
+  </si>
+  <si>
+    <t>['33', '68']</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP128"/>
+  <dimension ref="A1:BP131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1336,7 +1345,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1623,7 +1632,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ3">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1829,7 +1838,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ4">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2035,7 +2044,7 @@
         <v>3</v>
       </c>
       <c r="AQ5">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2160,7 +2169,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2238,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ6">
         <v>0.88</v>
@@ -2366,7 +2375,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2444,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -2572,7 +2581,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2984,7 +2993,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3190,7 +3199,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -4014,7 +4023,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4632,7 +4641,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4710,7 +4719,7 @@
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ18">
         <v>2.13</v>
@@ -4916,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ19">
         <v>0.43</v>
@@ -5250,7 +5259,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5456,7 +5465,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5534,10 +5543,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ22">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -5662,7 +5671,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5868,7 +5877,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -6074,7 +6083,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6361,7 +6370,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ26">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR26">
         <v>1.39</v>
@@ -6486,7 +6495,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6692,7 +6701,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6898,7 +6907,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7104,7 +7113,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7185,7 +7194,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ30">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR30">
         <v>1.85</v>
@@ -7928,7 +7937,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8006,10 +8015,10 @@
         <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ34">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR34">
         <v>1.52</v>
@@ -8212,7 +8221,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ35">
         <v>2.13</v>
@@ -8418,7 +8427,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8627,7 +8636,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ37">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR37">
         <v>1.78</v>
@@ -8958,7 +8967,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9164,7 +9173,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9448,7 +9457,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -9576,7 +9585,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9988,7 +9997,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10400,7 +10409,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10687,7 +10696,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ47">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR47">
         <v>1.72</v>
@@ -10893,7 +10902,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ48">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR48">
         <v>2</v>
@@ -11018,7 +11027,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11430,7 +11439,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -11508,7 +11517,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ51">
         <v>1</v>
@@ -11923,7 +11932,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ53">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR53">
         <v>1.48</v>
@@ -12126,7 +12135,7 @@
         <v>0.33</v>
       </c>
       <c r="AP54">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ54">
         <v>0.22</v>
@@ -12666,7 +12675,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12747,7 +12756,7 @@
         <v>2</v>
       </c>
       <c r="AQ57">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR57">
         <v>1.34</v>
@@ -12872,7 +12881,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -13078,7 +13087,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13156,7 +13165,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -14314,7 +14323,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14726,7 +14735,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14932,7 +14941,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15138,7 +15147,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15422,7 +15431,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ70">
         <v>0.88</v>
@@ -15631,7 +15640,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ71">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR71">
         <v>1.48</v>
@@ -15756,7 +15765,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -15834,7 +15843,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ72">
         <v>1.88</v>
@@ -16455,7 +16464,7 @@
         <v>0.57</v>
       </c>
       <c r="AQ75">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR75">
         <v>1.77</v>
@@ -16580,7 +16589,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16786,7 +16795,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -17198,7 +17207,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17610,7 +17619,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -17688,7 +17697,7 @@
         <v>2</v>
       </c>
       <c r="AP81">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ81">
         <v>1.88</v>
@@ -17897,7 +17906,7 @@
         <v>3</v>
       </c>
       <c r="AQ82">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR82">
         <v>2.19</v>
@@ -18022,7 +18031,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18228,7 +18237,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18309,7 +18318,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ84">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR84">
         <v>1.95</v>
@@ -18434,7 +18443,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18512,7 +18521,7 @@
         <v>0.4</v>
       </c>
       <c r="AP85">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ85">
         <v>0.22</v>
@@ -18718,7 +18727,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ86">
         <v>1</v>
@@ -18846,7 +18855,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -18924,10 +18933,10 @@
         <v>1.4</v>
       </c>
       <c r="AP87">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ87">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR87">
         <v>1.7</v>
@@ -19670,7 +19679,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -20082,7 +20091,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20163,7 +20172,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ93">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR93">
         <v>1.73</v>
@@ -20288,7 +20297,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20369,7 +20378,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR94">
         <v>1.4</v>
@@ -20494,7 +20503,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -20572,7 +20581,7 @@
         <v>1.83</v>
       </c>
       <c r="AP95">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ95">
         <v>2.13</v>
@@ -20984,7 +20993,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ97">
         <v>1.43</v>
@@ -21112,7 +21121,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21318,7 +21327,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21524,7 +21533,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21730,7 +21739,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q101">
         <v>2.75</v>
@@ -21936,7 +21945,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -22142,7 +22151,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22220,7 +22229,7 @@
         <v>0.83</v>
       </c>
       <c r="AP103">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ103">
         <v>1</v>
@@ -22635,7 +22644,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ105">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR105">
         <v>1.74</v>
@@ -23172,7 +23181,7 @@
         <v>165</v>
       </c>
       <c r="P108" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23378,7 +23387,7 @@
         <v>157</v>
       </c>
       <c r="P109" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23665,7 +23674,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ110">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR110">
         <v>2.16</v>
@@ -23996,7 +24005,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q112">
         <v>3.45</v>
@@ -24202,7 +24211,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q113">
         <v>1.76</v>
@@ -24408,7 +24417,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q114">
         <v>3.3</v>
@@ -24614,7 +24623,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24692,7 +24701,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ115">
         <v>0.5</v>
@@ -24820,7 +24829,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -25026,7 +25035,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25107,7 +25116,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ117">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR117">
         <v>1.73</v>
@@ -25232,7 +25241,7 @@
         <v>86</v>
       </c>
       <c r="P118" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q118">
         <v>3</v>
@@ -25310,7 +25319,7 @@
         <v>1.14</v>
       </c>
       <c r="AP118">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ118">
         <v>1.22</v>
@@ -25438,7 +25447,7 @@
         <v>86</v>
       </c>
       <c r="P119" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26134,7 +26143,7 @@
         <v>0.43</v>
       </c>
       <c r="AP122">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AQ122">
         <v>0.5</v>
@@ -26262,7 +26271,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26674,7 +26683,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q125">
         <v>2.05</v>
@@ -26880,7 +26889,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27086,7 +27095,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27292,7 +27301,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q128">
         <v>3.25</v>
@@ -27449,6 +27458,624 @@
       </c>
       <c r="BP128">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7818940</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45863.83333333334</v>
+      </c>
+      <c r="F129">
+        <v>17</v>
+      </c>
+      <c r="G129" t="s">
+        <v>75</v>
+      </c>
+      <c r="H129" t="s">
+        <v>81</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>1</v>
+      </c>
+      <c r="N129">
+        <v>1</v>
+      </c>
+      <c r="O129" t="s">
+        <v>86</v>
+      </c>
+      <c r="P129" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q129">
+        <v>2.88</v>
+      </c>
+      <c r="R129">
+        <v>2.05</v>
+      </c>
+      <c r="S129">
+        <v>3.45</v>
+      </c>
+      <c r="T129">
+        <v>1.38</v>
+      </c>
+      <c r="U129">
+        <v>2.8</v>
+      </c>
+      <c r="V129">
+        <v>2.75</v>
+      </c>
+      <c r="W129">
+        <v>1.4</v>
+      </c>
+      <c r="X129">
+        <v>7</v>
+      </c>
+      <c r="Y129">
+        <v>1.1</v>
+      </c>
+      <c r="Z129">
+        <v>2.2</v>
+      </c>
+      <c r="AA129">
+        <v>3.3</v>
+      </c>
+      <c r="AB129">
+        <v>3</v>
+      </c>
+      <c r="AC129">
+        <v>1.05</v>
+      </c>
+      <c r="AD129">
+        <v>8.5</v>
+      </c>
+      <c r="AE129">
+        <v>1.3</v>
+      </c>
+      <c r="AF129">
+        <v>3.35</v>
+      </c>
+      <c r="AG129">
+        <v>1.91</v>
+      </c>
+      <c r="AH129">
+        <v>1.83</v>
+      </c>
+      <c r="AI129">
+        <v>1.67</v>
+      </c>
+      <c r="AJ129">
+        <v>2</v>
+      </c>
+      <c r="AK129">
+        <v>1.36</v>
+      </c>
+      <c r="AL129">
+        <v>1.25</v>
+      </c>
+      <c r="AM129">
+        <v>1.62</v>
+      </c>
+      <c r="AN129">
+        <v>1.25</v>
+      </c>
+      <c r="AO129">
+        <v>1.14</v>
+      </c>
+      <c r="AP129">
+        <v>1.11</v>
+      </c>
+      <c r="AQ129">
+        <v>1.38</v>
+      </c>
+      <c r="AR129">
+        <v>1.52</v>
+      </c>
+      <c r="AS129">
+        <v>1.32</v>
+      </c>
+      <c r="AT129">
+        <v>2.84</v>
+      </c>
+      <c r="AU129">
+        <v>4</v>
+      </c>
+      <c r="AV129">
+        <v>4</v>
+      </c>
+      <c r="AW129">
+        <v>11</v>
+      </c>
+      <c r="AX129">
+        <v>16</v>
+      </c>
+      <c r="AY129">
+        <v>15</v>
+      </c>
+      <c r="AZ129">
+        <v>20</v>
+      </c>
+      <c r="BA129">
+        <v>4</v>
+      </c>
+      <c r="BB129">
+        <v>6</v>
+      </c>
+      <c r="BC129">
+        <v>10</v>
+      </c>
+      <c r="BD129">
+        <v>1.79</v>
+      </c>
+      <c r="BE129">
+        <v>8.5</v>
+      </c>
+      <c r="BF129">
+        <v>2.48</v>
+      </c>
+      <c r="BG129">
+        <v>1.29</v>
+      </c>
+      <c r="BH129">
+        <v>3.1</v>
+      </c>
+      <c r="BI129">
+        <v>1.52</v>
+      </c>
+      <c r="BJ129">
+        <v>2.28</v>
+      </c>
+      <c r="BK129">
+        <v>1.83</v>
+      </c>
+      <c r="BL129">
+        <v>1.81</v>
+      </c>
+      <c r="BM129">
+        <v>2.3</v>
+      </c>
+      <c r="BN129">
+        <v>1.5</v>
+      </c>
+      <c r="BO129">
+        <v>2.95</v>
+      </c>
+      <c r="BP129">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7818937</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45864.66666666666</v>
+      </c>
+      <c r="F130">
+        <v>17</v>
+      </c>
+      <c r="G130" t="s">
+        <v>74</v>
+      </c>
+      <c r="H130" t="s">
+        <v>83</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>2</v>
+      </c>
+      <c r="N130">
+        <v>2</v>
+      </c>
+      <c r="O130" t="s">
+        <v>86</v>
+      </c>
+      <c r="P130" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q130">
+        <v>2.79</v>
+      </c>
+      <c r="R130">
+        <v>2.05</v>
+      </c>
+      <c r="S130">
+        <v>3.85</v>
+      </c>
+      <c r="T130">
+        <v>1.41</v>
+      </c>
+      <c r="U130">
+        <v>2.69</v>
+      </c>
+      <c r="V130">
+        <v>2.88</v>
+      </c>
+      <c r="W130">
+        <v>1.36</v>
+      </c>
+      <c r="X130">
+        <v>6.8</v>
+      </c>
+      <c r="Y130">
+        <v>1.04</v>
+      </c>
+      <c r="Z130">
+        <v>2.22</v>
+      </c>
+      <c r="AA130">
+        <v>3.3</v>
+      </c>
+      <c r="AB130">
+        <v>3.22</v>
+      </c>
+      <c r="AC130">
+        <v>1.02</v>
+      </c>
+      <c r="AD130">
+        <v>8</v>
+      </c>
+      <c r="AE130">
+        <v>1.28</v>
+      </c>
+      <c r="AF130">
+        <v>3.08</v>
+      </c>
+      <c r="AG130">
+        <v>2</v>
+      </c>
+      <c r="AH130">
+        <v>1.78</v>
+      </c>
+      <c r="AI130">
+        <v>1.77</v>
+      </c>
+      <c r="AJ130">
+        <v>1.94</v>
+      </c>
+      <c r="AK130">
+        <v>1.33</v>
+      </c>
+      <c r="AL130">
+        <v>1.32</v>
+      </c>
+      <c r="AM130">
+        <v>1.63</v>
+      </c>
+      <c r="AN130">
+        <v>1.86</v>
+      </c>
+      <c r="AO130">
+        <v>1.14</v>
+      </c>
+      <c r="AP130">
+        <v>1.63</v>
+      </c>
+      <c r="AQ130">
+        <v>1.38</v>
+      </c>
+      <c r="AR130">
+        <v>1.72</v>
+      </c>
+      <c r="AS130">
+        <v>1.47</v>
+      </c>
+      <c r="AT130">
+        <v>3.19</v>
+      </c>
+      <c r="AU130">
+        <v>4</v>
+      </c>
+      <c r="AV130">
+        <v>6</v>
+      </c>
+      <c r="AW130">
+        <v>16</v>
+      </c>
+      <c r="AX130">
+        <v>7</v>
+      </c>
+      <c r="AY130">
+        <v>20</v>
+      </c>
+      <c r="AZ130">
+        <v>13</v>
+      </c>
+      <c r="BA130">
+        <v>11</v>
+      </c>
+      <c r="BB130">
+        <v>4</v>
+      </c>
+      <c r="BC130">
+        <v>15</v>
+      </c>
+      <c r="BD130">
+        <v>1.81</v>
+      </c>
+      <c r="BE130">
+        <v>8.5</v>
+      </c>
+      <c r="BF130">
+        <v>2.43</v>
+      </c>
+      <c r="BG130">
+        <v>1.32</v>
+      </c>
+      <c r="BH130">
+        <v>2.9</v>
+      </c>
+      <c r="BI130">
+        <v>1.56</v>
+      </c>
+      <c r="BJ130">
+        <v>2.17</v>
+      </c>
+      <c r="BK130">
+        <v>1.93</v>
+      </c>
+      <c r="BL130">
+        <v>1.73</v>
+      </c>
+      <c r="BM130">
+        <v>2.45</v>
+      </c>
+      <c r="BN130">
+        <v>1.45</v>
+      </c>
+      <c r="BO130">
+        <v>3.2</v>
+      </c>
+      <c r="BP130">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7818939</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45864.77083333334</v>
+      </c>
+      <c r="F131">
+        <v>17</v>
+      </c>
+      <c r="G131" t="s">
+        <v>85</v>
+      </c>
+      <c r="H131" t="s">
+        <v>82</v>
+      </c>
+      <c r="I131">
+        <v>3</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>4</v>
+      </c>
+      <c r="L131">
+        <v>4</v>
+      </c>
+      <c r="M131">
+        <v>1</v>
+      </c>
+      <c r="N131">
+        <v>5</v>
+      </c>
+      <c r="O131" t="s">
+        <v>181</v>
+      </c>
+      <c r="P131" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q131">
+        <v>2.5</v>
+      </c>
+      <c r="R131">
+        <v>2.25</v>
+      </c>
+      <c r="S131">
+        <v>4.33</v>
+      </c>
+      <c r="T131">
+        <v>1.36</v>
+      </c>
+      <c r="U131">
+        <v>3</v>
+      </c>
+      <c r="V131">
+        <v>2.75</v>
+      </c>
+      <c r="W131">
+        <v>1.4</v>
+      </c>
+      <c r="X131">
+        <v>7</v>
+      </c>
+      <c r="Y131">
+        <v>1.1</v>
+      </c>
+      <c r="Z131">
+        <v>1.87</v>
+      </c>
+      <c r="AA131">
+        <v>3.54</v>
+      </c>
+      <c r="AB131">
+        <v>4.09</v>
+      </c>
+      <c r="AC131">
+        <v>1.01</v>
+      </c>
+      <c r="AD131">
+        <v>8.5</v>
+      </c>
+      <c r="AE131">
+        <v>1.25</v>
+      </c>
+      <c r="AF131">
+        <v>3.28</v>
+      </c>
+      <c r="AG131">
+        <v>1.95</v>
+      </c>
+      <c r="AH131">
+        <v>1.85</v>
+      </c>
+      <c r="AI131">
+        <v>1.73</v>
+      </c>
+      <c r="AJ131">
+        <v>2</v>
+      </c>
+      <c r="AK131">
+        <v>1.23</v>
+      </c>
+      <c r="AL131">
+        <v>1.28</v>
+      </c>
+      <c r="AM131">
+        <v>1.88</v>
+      </c>
+      <c r="AN131">
+        <v>0.89</v>
+      </c>
+      <c r="AO131">
+        <v>0.63</v>
+      </c>
+      <c r="AP131">
+        <v>1.1</v>
+      </c>
+      <c r="AQ131">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR131">
+        <v>1.65</v>
+      </c>
+      <c r="AS131">
+        <v>1.26</v>
+      </c>
+      <c r="AT131">
+        <v>2.91</v>
+      </c>
+      <c r="AU131">
+        <v>8</v>
+      </c>
+      <c r="AV131">
+        <v>3</v>
+      </c>
+      <c r="AW131">
+        <v>10</v>
+      </c>
+      <c r="AX131">
+        <v>3</v>
+      </c>
+      <c r="AY131">
+        <v>18</v>
+      </c>
+      <c r="AZ131">
+        <v>6</v>
+      </c>
+      <c r="BA131">
+        <v>4</v>
+      </c>
+      <c r="BB131">
+        <v>8</v>
+      </c>
+      <c r="BC131">
+        <v>12</v>
+      </c>
+      <c r="BD131">
+        <v>1.66</v>
+      </c>
+      <c r="BE131">
+        <v>8.5</v>
+      </c>
+      <c r="BF131">
+        <v>2.75</v>
+      </c>
+      <c r="BG131">
+        <v>1.27</v>
+      </c>
+      <c r="BH131">
+        <v>3.2</v>
+      </c>
+      <c r="BI131">
+        <v>1.49</v>
+      </c>
+      <c r="BJ131">
+        <v>2.35</v>
+      </c>
+      <c r="BK131">
+        <v>1.8</v>
+      </c>
+      <c r="BL131">
+        <v>1.85</v>
+      </c>
+      <c r="BM131">
+        <v>2.25</v>
+      </c>
+      <c r="BN131">
+        <v>1.53</v>
+      </c>
+      <c r="BO131">
+        <v>2.9</v>
+      </c>
+      <c r="BP131">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="243">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -562,6 +562,15 @@
     <t>['5', '16', '24', '79']</t>
   </si>
   <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -688,9 +697,6 @@
     <t>['53', '59']</t>
   </si>
   <si>
-    <t>['63']</t>
-  </si>
-  <si>
     <t>['5', '10', '54']</t>
   </si>
   <si>
@@ -728,6 +734,15 @@
   </si>
   <si>
     <t>['33', '68']</t>
+  </si>
+  <si>
+    <t>['27']</t>
+  </si>
+  <si>
+    <t>['32', '38', '82']</t>
+  </si>
+  <si>
+    <t>['13', '22', '44', '76']</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP131"/>
+  <dimension ref="A1:BP136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1345,7 +1360,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1423,10 +1438,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ2">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1629,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>1.38</v>
@@ -1835,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>0.5600000000000001</v>
@@ -2169,7 +2184,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q6">
         <v>5.5</v>
@@ -2250,7 +2265,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ6">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2375,7 +2390,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -2581,7 +2596,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q8">
         <v>2.5</v>
@@ -2659,10 +2674,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AQ8">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2865,10 +2880,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ9">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2993,7 +3008,7 @@
         <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -3199,7 +3214,7 @@
         <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q11">
         <v>3.1</v>
@@ -4023,7 +4038,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q15">
         <v>2.5</v>
@@ -4641,7 +4656,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -4722,7 +4737,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ18">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR18">
         <v>1.84</v>
@@ -4928,7 +4943,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ19">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR19">
         <v>1.05</v>
@@ -5131,7 +5146,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AQ20">
         <v>0.22</v>
@@ -5259,7 +5274,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q21">
         <v>2.4</v>
@@ -5337,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR21">
         <v>1.92</v>
@@ -5465,7 +5480,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q22">
         <v>2.34</v>
@@ -5671,7 +5686,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -5752,7 +5767,7 @@
         <v>2</v>
       </c>
       <c r="AQ23">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR23">
         <v>1.43</v>
@@ -5877,7 +5892,7 @@
         <v>102</v>
       </c>
       <c r="P24" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q24">
         <v>5.2</v>
@@ -5958,7 +5973,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR24">
         <v>1.82</v>
@@ -6083,7 +6098,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q25">
         <v>2.88</v>
@@ -6161,7 +6176,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ25">
         <v>1.22</v>
@@ -6367,7 +6382,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ26">
         <v>0.5600000000000001</v>
@@ -6495,7 +6510,7 @@
         <v>105</v>
       </c>
       <c r="P27" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6701,7 +6716,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
@@ -6779,7 +6794,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ28">
         <v>1.88</v>
@@ -6907,7 +6922,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q29">
         <v>2.3</v>
@@ -7113,7 +7128,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q30">
         <v>2.32</v>
@@ -7397,7 +7412,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>0.44</v>
@@ -7812,7 +7827,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR33">
         <v>1.64</v>
@@ -7937,7 +7952,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q34">
         <v>3.4</v>
@@ -8224,7 +8239,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ35">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR35">
         <v>2.29</v>
@@ -8633,7 +8648,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ37">
         <v>1.38</v>
@@ -8967,7 +8982,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q39">
         <v>2.75</v>
@@ -9045,10 +9060,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ39">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR39">
         <v>1.64</v>
@@ -9173,7 +9188,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q40">
         <v>2.16</v>
@@ -9460,7 +9475,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ41">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR41">
         <v>2.17</v>
@@ -9585,7 +9600,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q42">
         <v>3.2</v>
@@ -9997,7 +10012,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q44">
         <v>2.29</v>
@@ -10075,7 +10090,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
         <v>0.5</v>
@@ -10409,7 +10424,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q46">
         <v>2.71</v>
@@ -10490,7 +10505,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ46">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR46">
         <v>2.2</v>
@@ -10693,7 +10708,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ47">
         <v>1.38</v>
@@ -11027,7 +11042,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q49">
         <v>3.25</v>
@@ -11439,7 +11454,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q51">
         <v>3.5</v>
@@ -11723,7 +11738,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
         <v>1</v>
@@ -12550,7 +12565,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ56">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR56">
         <v>1.6</v>
@@ -12675,7 +12690,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -12881,7 +12896,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q58">
         <v>2.25</v>
@@ -12959,7 +12974,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AQ58">
         <v>0.5</v>
@@ -13087,7 +13102,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -13371,7 +13386,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
         <v>1.88</v>
@@ -13580,7 +13595,7 @@
         <v>1</v>
       </c>
       <c r="AQ61">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR61">
         <v>1.9</v>
@@ -13783,10 +13798,10 @@
         <v>1</v>
       </c>
       <c r="AP62">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ62">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR62">
         <v>1.63</v>
@@ -14195,7 +14210,7 @@
         <v>0.25</v>
       </c>
       <c r="AP64">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14323,7 +14338,7 @@
         <v>135</v>
       </c>
       <c r="P65" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q65">
         <v>2.2</v>
@@ -14610,7 +14625,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ66">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR66">
         <v>2.18</v>
@@ -14735,7 +14750,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q67">
         <v>2.5</v>
@@ -14813,7 +14828,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
         <v>0.22</v>
@@ -14941,7 +14956,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q68">
         <v>4</v>
@@ -15019,10 +15034,10 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR68">
         <v>1.78</v>
@@ -15147,7 +15162,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15228,7 +15243,7 @@
         <v>2</v>
       </c>
       <c r="AQ69">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR69">
         <v>1.45</v>
@@ -15434,7 +15449,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ70">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -15765,7 +15780,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q72">
         <v>3</v>
@@ -16461,7 +16476,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ75">
         <v>0.5600000000000001</v>
@@ -16589,7 +16604,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -16795,7 +16810,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q77">
         <v>2.75</v>
@@ -17079,10 +17094,10 @@
         <v>1.6</v>
       </c>
       <c r="AP78">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ78">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR78">
         <v>1.51</v>
@@ -17207,7 +17222,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17288,7 +17303,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ79">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR79">
         <v>1.73</v>
@@ -17491,7 +17506,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
         <v>0.89</v>
@@ -17619,7 +17634,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q81">
         <v>4.7</v>
@@ -18031,7 +18046,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q83">
         <v>2.63</v>
@@ -18237,7 +18252,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18443,7 +18458,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18730,7 +18745,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR86">
         <v>1.51</v>
@@ -18855,7 +18870,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q87">
         <v>2.54</v>
@@ -19142,7 +19157,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ88">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR88">
         <v>2.08</v>
@@ -19679,7 +19694,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q91">
         <v>2.2</v>
@@ -19757,7 +19772,7 @@
         <v>0.17</v>
       </c>
       <c r="AP91">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AQ91">
         <v>0.44</v>
@@ -19963,7 +19978,7 @@
         <v>0.4</v>
       </c>
       <c r="AP92">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20091,7 +20106,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q93">
         <v>2.5</v>
@@ -20297,7 +20312,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q94">
         <v>2.65</v>
@@ -20503,7 +20518,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -20584,7 +20599,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ95">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR95">
         <v>1.68</v>
@@ -20996,7 +21011,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ97">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR97">
         <v>1.81</v>
@@ -21121,7 +21136,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q98">
         <v>3</v>
@@ -21199,7 +21214,7 @@
         <v>0.83</v>
       </c>
       <c r="AP98">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ98">
         <v>0.89</v>
@@ -21327,7 +21342,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21405,10 +21420,10 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ99">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR99">
         <v>1.47</v>
@@ -21533,7 +21548,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q100">
         <v>2.32</v>
@@ -21739,7 +21754,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q101">
         <v>2.75</v>
@@ -21945,7 +21960,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q102">
         <v>5.5</v>
@@ -22023,10 +22038,10 @@
         <v>1.5</v>
       </c>
       <c r="AP102">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ102">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR102">
         <v>1.69</v>
@@ -22151,7 +22166,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22435,7 +22450,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ104">
         <v>0.44</v>
@@ -22641,7 +22656,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AQ105">
         <v>0.5600000000000001</v>
@@ -22847,10 +22862,10 @@
         <v>0.5</v>
       </c>
       <c r="AP106">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR106">
         <v>1.87</v>
@@ -23056,7 +23071,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ107">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR107">
         <v>1.82</v>
@@ -23181,7 +23196,7 @@
         <v>165</v>
       </c>
       <c r="P108" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q108">
         <v>3.1</v>
@@ -23262,7 +23277,7 @@
         <v>1</v>
       </c>
       <c r="AQ108">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR108">
         <v>1.78</v>
@@ -23387,7 +23402,7 @@
         <v>157</v>
       </c>
       <c r="P109" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23465,7 +23480,7 @@
         <v>0.67</v>
       </c>
       <c r="AP109">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AQ109">
         <v>1</v>
@@ -23877,7 +23892,7 @@
         <v>0.86</v>
       </c>
       <c r="AP111">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ111">
         <v>0.89</v>
@@ -24005,7 +24020,7 @@
         <v>86</v>
       </c>
       <c r="P112" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q112">
         <v>3.45</v>
@@ -24086,7 +24101,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ112">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AR112">
         <v>1.64</v>
@@ -24211,7 +24226,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q113">
         <v>1.76</v>
@@ -24417,7 +24432,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q114">
         <v>3.3</v>
@@ -24623,7 +24638,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24829,7 +24844,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q116">
         <v>4.33</v>
@@ -24910,7 +24925,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ116">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR116">
         <v>1.79</v>
@@ -25035,7 +25050,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q117">
         <v>2.75</v>
@@ -25241,7 +25256,7 @@
         <v>86</v>
       </c>
       <c r="P118" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q118">
         <v>3</v>
@@ -25447,7 +25462,7 @@
         <v>86</v>
       </c>
       <c r="P119" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25528,7 +25543,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ119">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR119">
         <v>1.53</v>
@@ -25731,10 +25746,10 @@
         <v>1.17</v>
       </c>
       <c r="AP120">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AQ120">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR120">
         <v>1.79</v>
@@ -25940,7 +25955,7 @@
         <v>3</v>
       </c>
       <c r="AQ121">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AR121">
         <v>2.16</v>
@@ -26271,7 +26286,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q123">
         <v>3.2</v>
@@ -26683,7 +26698,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q125">
         <v>2.05</v>
@@ -26889,7 +26904,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q126">
         <v>3.4</v>
@@ -27095,7 +27110,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27176,7 +27191,7 @@
         <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR127">
         <v>1.81</v>
@@ -27301,7 +27316,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q128">
         <v>3.25</v>
@@ -27507,7 +27522,7 @@
         <v>86</v>
       </c>
       <c r="P129" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27713,7 +27728,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q130">
         <v>2.79</v>
@@ -28076,6 +28091,1036 @@
       </c>
       <c r="BP131">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7818942</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45865.5625</v>
+      </c>
+      <c r="F132">
+        <v>17</v>
+      </c>
+      <c r="G132" t="s">
+        <v>72</v>
+      </c>
+      <c r="H132" t="s">
+        <v>84</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>2</v>
+      </c>
+      <c r="O132" t="s">
+        <v>182</v>
+      </c>
+      <c r="P132" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q132">
+        <v>4</v>
+      </c>
+      <c r="R132">
+        <v>2.1</v>
+      </c>
+      <c r="S132">
+        <v>2.88</v>
+      </c>
+      <c r="T132">
+        <v>1.44</v>
+      </c>
+      <c r="U132">
+        <v>2.63</v>
+      </c>
+      <c r="V132">
+        <v>3</v>
+      </c>
+      <c r="W132">
+        <v>1.36</v>
+      </c>
+      <c r="X132">
+        <v>9</v>
+      </c>
+      <c r="Y132">
+        <v>1.07</v>
+      </c>
+      <c r="Z132">
+        <v>3.3</v>
+      </c>
+      <c r="AA132">
+        <v>3.25</v>
+      </c>
+      <c r="AB132">
+        <v>2.15</v>
+      </c>
+      <c r="AC132">
+        <v>1.06</v>
+      </c>
+      <c r="AD132">
+        <v>8</v>
+      </c>
+      <c r="AE132">
+        <v>1.36</v>
+      </c>
+      <c r="AF132">
+        <v>3</v>
+      </c>
+      <c r="AG132">
+        <v>2.05</v>
+      </c>
+      <c r="AH132">
+        <v>1.75</v>
+      </c>
+      <c r="AI132">
+        <v>1.83</v>
+      </c>
+      <c r="AJ132">
+        <v>1.83</v>
+      </c>
+      <c r="AK132">
+        <v>1.68</v>
+      </c>
+      <c r="AL132">
+        <v>1.3</v>
+      </c>
+      <c r="AM132">
+        <v>1.31</v>
+      </c>
+      <c r="AN132">
+        <v>2.14</v>
+      </c>
+      <c r="AO132">
+        <v>0.88</v>
+      </c>
+      <c r="AP132">
+        <v>2</v>
+      </c>
+      <c r="AQ132">
+        <v>0.89</v>
+      </c>
+      <c r="AR132">
+        <v>1.9</v>
+      </c>
+      <c r="AS132">
+        <v>1.75</v>
+      </c>
+      <c r="AT132">
+        <v>3.65</v>
+      </c>
+      <c r="AU132">
+        <v>6</v>
+      </c>
+      <c r="AV132">
+        <v>2</v>
+      </c>
+      <c r="AW132">
+        <v>12</v>
+      </c>
+      <c r="AX132">
+        <v>0</v>
+      </c>
+      <c r="AY132">
+        <v>18</v>
+      </c>
+      <c r="AZ132">
+        <v>2</v>
+      </c>
+      <c r="BA132">
+        <v>4</v>
+      </c>
+      <c r="BB132">
+        <v>0</v>
+      </c>
+      <c r="BC132">
+        <v>4</v>
+      </c>
+      <c r="BD132">
+        <v>2.08</v>
+      </c>
+      <c r="BE132">
+        <v>8.5</v>
+      </c>
+      <c r="BF132">
+        <v>2.07</v>
+      </c>
+      <c r="BG132">
+        <v>1.27</v>
+      </c>
+      <c r="BH132">
+        <v>3.2</v>
+      </c>
+      <c r="BI132">
+        <v>1.47</v>
+      </c>
+      <c r="BJ132">
+        <v>2.38</v>
+      </c>
+      <c r="BK132">
+        <v>1.78</v>
+      </c>
+      <c r="BL132">
+        <v>1.86</v>
+      </c>
+      <c r="BM132">
+        <v>2.2</v>
+      </c>
+      <c r="BN132">
+        <v>1.54</v>
+      </c>
+      <c r="BO132">
+        <v>2.85</v>
+      </c>
+      <c r="BP132">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7818941</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45865.66666666666</v>
+      </c>
+      <c r="F133">
+        <v>17</v>
+      </c>
+      <c r="G133" t="s">
+        <v>71</v>
+      </c>
+      <c r="H133" t="s">
+        <v>79</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>1</v>
+      </c>
+      <c r="O133" t="s">
+        <v>183</v>
+      </c>
+      <c r="P133" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q133">
+        <v>2.3</v>
+      </c>
+      <c r="R133">
+        <v>2.38</v>
+      </c>
+      <c r="S133">
+        <v>4.5</v>
+      </c>
+      <c r="T133">
+        <v>1.3</v>
+      </c>
+      <c r="U133">
+        <v>3.4</v>
+      </c>
+      <c r="V133">
+        <v>2.5</v>
+      </c>
+      <c r="W133">
+        <v>1.5</v>
+      </c>
+      <c r="X133">
+        <v>6</v>
+      </c>
+      <c r="Y133">
+        <v>1.13</v>
+      </c>
+      <c r="Z133">
+        <v>1.75</v>
+      </c>
+      <c r="AA133">
+        <v>3.4</v>
+      </c>
+      <c r="AB133">
+        <v>4.75</v>
+      </c>
+      <c r="AC133">
+        <v>1.04</v>
+      </c>
+      <c r="AD133">
+        <v>9</v>
+      </c>
+      <c r="AE133">
+        <v>1.25</v>
+      </c>
+      <c r="AF133">
+        <v>3.8</v>
+      </c>
+      <c r="AG133">
+        <v>1.75</v>
+      </c>
+      <c r="AH133">
+        <v>2.05</v>
+      </c>
+      <c r="AI133">
+        <v>1.67</v>
+      </c>
+      <c r="AJ133">
+        <v>2.1</v>
+      </c>
+      <c r="AK133">
+        <v>1.24</v>
+      </c>
+      <c r="AL133">
+        <v>1.25</v>
+      </c>
+      <c r="AM133">
+        <v>1.95</v>
+      </c>
+      <c r="AN133">
+        <v>1.86</v>
+      </c>
+      <c r="AO133">
+        <v>0.43</v>
+      </c>
+      <c r="AP133">
+        <v>2</v>
+      </c>
+      <c r="AQ133">
+        <v>0.38</v>
+      </c>
+      <c r="AR133">
+        <v>1.8</v>
+      </c>
+      <c r="AS133">
+        <v>1.59</v>
+      </c>
+      <c r="AT133">
+        <v>3.39</v>
+      </c>
+      <c r="AU133">
+        <v>7</v>
+      </c>
+      <c r="AV133">
+        <v>6</v>
+      </c>
+      <c r="AW133">
+        <v>8</v>
+      </c>
+      <c r="AX133">
+        <v>9</v>
+      </c>
+      <c r="AY133">
+        <v>15</v>
+      </c>
+      <c r="AZ133">
+        <v>15</v>
+      </c>
+      <c r="BA133">
+        <v>7</v>
+      </c>
+      <c r="BB133">
+        <v>2</v>
+      </c>
+      <c r="BC133">
+        <v>9</v>
+      </c>
+      <c r="BD133">
+        <v>1.77</v>
+      </c>
+      <c r="BE133">
+        <v>8.5</v>
+      </c>
+      <c r="BF133">
+        <v>2.5</v>
+      </c>
+      <c r="BG133">
+        <v>1.28</v>
+      </c>
+      <c r="BH133">
+        <v>3.15</v>
+      </c>
+      <c r="BI133">
+        <v>1.49</v>
+      </c>
+      <c r="BJ133">
+        <v>2.33</v>
+      </c>
+      <c r="BK133">
+        <v>1.79</v>
+      </c>
+      <c r="BL133">
+        <v>1.85</v>
+      </c>
+      <c r="BM133">
+        <v>2.25</v>
+      </c>
+      <c r="BN133">
+        <v>1.53</v>
+      </c>
+      <c r="BO133">
+        <v>2.95</v>
+      </c>
+      <c r="BP133">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7818935</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45865.66666666666</v>
+      </c>
+      <c r="F134">
+        <v>17</v>
+      </c>
+      <c r="G134" t="s">
+        <v>76</v>
+      </c>
+      <c r="H134" t="s">
+        <v>80</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>2</v>
+      </c>
+      <c r="K134">
+        <v>2</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>3</v>
+      </c>
+      <c r="N134">
+        <v>3</v>
+      </c>
+      <c r="O134" t="s">
+        <v>86</v>
+      </c>
+      <c r="P134" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q134">
+        <v>3.4</v>
+      </c>
+      <c r="R134">
+        <v>1.91</v>
+      </c>
+      <c r="S134">
+        <v>4</v>
+      </c>
+      <c r="T134">
+        <v>1.57</v>
+      </c>
+      <c r="U134">
+        <v>2.25</v>
+      </c>
+      <c r="V134">
+        <v>3.75</v>
+      </c>
+      <c r="W134">
+        <v>1.25</v>
+      </c>
+      <c r="X134">
+        <v>13</v>
+      </c>
+      <c r="Y134">
+        <v>1.04</v>
+      </c>
+      <c r="Z134">
+        <v>2.45</v>
+      </c>
+      <c r="AA134">
+        <v>2.9</v>
+      </c>
+      <c r="AB134">
+        <v>3.1</v>
+      </c>
+      <c r="AC134">
+        <v>1.08</v>
+      </c>
+      <c r="AD134">
+        <v>7</v>
+      </c>
+      <c r="AE134">
+        <v>1.44</v>
+      </c>
+      <c r="AF134">
+        <v>2.65</v>
+      </c>
+      <c r="AG134">
+        <v>2.7</v>
+      </c>
+      <c r="AH134">
+        <v>1.44</v>
+      </c>
+      <c r="AI134">
+        <v>2.2</v>
+      </c>
+      <c r="AJ134">
+        <v>1.62</v>
+      </c>
+      <c r="AK134">
+        <v>1.39</v>
+      </c>
+      <c r="AL134">
+        <v>1.34</v>
+      </c>
+      <c r="AM134">
+        <v>1.52</v>
+      </c>
+      <c r="AN134">
+        <v>2.57</v>
+      </c>
+      <c r="AO134">
+        <v>2.13</v>
+      </c>
+      <c r="AP134">
+        <v>2.25</v>
+      </c>
+      <c r="AQ134">
+        <v>2.22</v>
+      </c>
+      <c r="AR134">
+        <v>1.77</v>
+      </c>
+      <c r="AS134">
+        <v>1.54</v>
+      </c>
+      <c r="AT134">
+        <v>3.31</v>
+      </c>
+      <c r="AU134">
+        <v>0</v>
+      </c>
+      <c r="AV134">
+        <v>10</v>
+      </c>
+      <c r="AW134">
+        <v>5</v>
+      </c>
+      <c r="AX134">
+        <v>9</v>
+      </c>
+      <c r="AY134">
+        <v>5</v>
+      </c>
+      <c r="AZ134">
+        <v>19</v>
+      </c>
+      <c r="BA134">
+        <v>1</v>
+      </c>
+      <c r="BB134">
+        <v>6</v>
+      </c>
+      <c r="BC134">
+        <v>7</v>
+      </c>
+      <c r="BD134">
+        <v>1.95</v>
+      </c>
+      <c r="BE134">
+        <v>8</v>
+      </c>
+      <c r="BF134">
+        <v>2.25</v>
+      </c>
+      <c r="BG134">
+        <v>1.38</v>
+      </c>
+      <c r="BH134">
+        <v>2.65</v>
+      </c>
+      <c r="BI134">
+        <v>1.67</v>
+      </c>
+      <c r="BJ134">
+        <v>2</v>
+      </c>
+      <c r="BK134">
+        <v>2.07</v>
+      </c>
+      <c r="BL134">
+        <v>1.62</v>
+      </c>
+      <c r="BM134">
+        <v>2.7</v>
+      </c>
+      <c r="BN134">
+        <v>1.38</v>
+      </c>
+      <c r="BO134">
+        <v>3.55</v>
+      </c>
+      <c r="BP134">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7818936</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45865.79166666666</v>
+      </c>
+      <c r="F135">
+        <v>17</v>
+      </c>
+      <c r="G135" t="s">
+        <v>70</v>
+      </c>
+      <c r="H135" t="s">
+        <v>78</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>1</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>1</v>
+      </c>
+      <c r="O135" t="s">
+        <v>184</v>
+      </c>
+      <c r="P135" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q135">
+        <v>3.3</v>
+      </c>
+      <c r="R135">
+        <v>2.15</v>
+      </c>
+      <c r="S135">
+        <v>2.8</v>
+      </c>
+      <c r="T135">
+        <v>1.35</v>
+      </c>
+      <c r="U135">
+        <v>2.9</v>
+      </c>
+      <c r="V135">
+        <v>2.6</v>
+      </c>
+      <c r="W135">
+        <v>1.43</v>
+      </c>
+      <c r="X135">
+        <v>6.5</v>
+      </c>
+      <c r="Y135">
+        <v>1.1</v>
+      </c>
+      <c r="Z135">
+        <v>2.9</v>
+      </c>
+      <c r="AA135">
+        <v>3.25</v>
+      </c>
+      <c r="AB135">
+        <v>2.3</v>
+      </c>
+      <c r="AC135">
+        <v>1.05</v>
+      </c>
+      <c r="AD135">
+        <v>8.5</v>
+      </c>
+      <c r="AE135">
+        <v>1.25</v>
+      </c>
+      <c r="AF135">
+        <v>3.6</v>
+      </c>
+      <c r="AG135">
+        <v>1.8</v>
+      </c>
+      <c r="AH135">
+        <v>1.95</v>
+      </c>
+      <c r="AI135">
+        <v>1.68</v>
+      </c>
+      <c r="AJ135">
+        <v>2.05</v>
+      </c>
+      <c r="AK135">
+        <v>1.58</v>
+      </c>
+      <c r="AL135">
+        <v>1.29</v>
+      </c>
+      <c r="AM135">
+        <v>1.4</v>
+      </c>
+      <c r="AN135">
+        <v>0.57</v>
+      </c>
+      <c r="AO135">
+        <v>1.43</v>
+      </c>
+      <c r="AP135">
+        <v>0.88</v>
+      </c>
+      <c r="AQ135">
+        <v>1.25</v>
+      </c>
+      <c r="AR135">
+        <v>1.6</v>
+      </c>
+      <c r="AS135">
+        <v>1.2</v>
+      </c>
+      <c r="AT135">
+        <v>2.8</v>
+      </c>
+      <c r="AU135">
+        <v>4</v>
+      </c>
+      <c r="AV135">
+        <v>7</v>
+      </c>
+      <c r="AW135">
+        <v>7</v>
+      </c>
+      <c r="AX135">
+        <v>7</v>
+      </c>
+      <c r="AY135">
+        <v>11</v>
+      </c>
+      <c r="AZ135">
+        <v>14</v>
+      </c>
+      <c r="BA135">
+        <v>2</v>
+      </c>
+      <c r="BB135">
+        <v>6</v>
+      </c>
+      <c r="BC135">
+        <v>8</v>
+      </c>
+      <c r="BD135">
+        <v>2.08</v>
+      </c>
+      <c r="BE135">
+        <v>8</v>
+      </c>
+      <c r="BF135">
+        <v>2.08</v>
+      </c>
+      <c r="BG135">
+        <v>1.33</v>
+      </c>
+      <c r="BH135">
+        <v>2.9</v>
+      </c>
+      <c r="BI135">
+        <v>1.57</v>
+      </c>
+      <c r="BJ135">
+        <v>2.16</v>
+      </c>
+      <c r="BK135">
+        <v>1.92</v>
+      </c>
+      <c r="BL135">
+        <v>1.73</v>
+      </c>
+      <c r="BM135">
+        <v>2.45</v>
+      </c>
+      <c r="BN135">
+        <v>1.45</v>
+      </c>
+      <c r="BO135">
+        <v>3.2</v>
+      </c>
+      <c r="BP135">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7818938</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45866.79166666666</v>
+      </c>
+      <c r="F136">
+        <v>17</v>
+      </c>
+      <c r="G136" t="s">
+        <v>77</v>
+      </c>
+      <c r="H136" t="s">
+        <v>73</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>3</v>
+      </c>
+      <c r="K136">
+        <v>3</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>4</v>
+      </c>
+      <c r="N136">
+        <v>4</v>
+      </c>
+      <c r="O136" t="s">
+        <v>86</v>
+      </c>
+      <c r="P136" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q136">
+        <v>5</v>
+      </c>
+      <c r="R136">
+        <v>2.4</v>
+      </c>
+      <c r="S136">
+        <v>2.2</v>
+      </c>
+      <c r="T136">
+        <v>1.3</v>
+      </c>
+      <c r="U136">
+        <v>3.4</v>
+      </c>
+      <c r="V136">
+        <v>2.5</v>
+      </c>
+      <c r="W136">
+        <v>1.5</v>
+      </c>
+      <c r="X136">
+        <v>6</v>
+      </c>
+      <c r="Y136">
+        <v>1.13</v>
+      </c>
+      <c r="Z136">
+        <v>5.25</v>
+      </c>
+      <c r="AA136">
+        <v>3.5</v>
+      </c>
+      <c r="AB136">
+        <v>1.67</v>
+      </c>
+      <c r="AC136">
+        <v>1.04</v>
+      </c>
+      <c r="AD136">
+        <v>9.5</v>
+      </c>
+      <c r="AE136">
+        <v>1.2</v>
+      </c>
+      <c r="AF136">
+        <v>4.33</v>
+      </c>
+      <c r="AG136">
+        <v>1.7</v>
+      </c>
+      <c r="AH136">
+        <v>2.1</v>
+      </c>
+      <c r="AI136">
+        <v>1.67</v>
+      </c>
+      <c r="AJ136">
+        <v>2.1</v>
+      </c>
+      <c r="AK136">
+        <v>2.15</v>
+      </c>
+      <c r="AL136">
+        <v>1.23</v>
+      </c>
+      <c r="AM136">
+        <v>1.19</v>
+      </c>
+      <c r="AN136">
+        <v>1.75</v>
+      </c>
+      <c r="AO136">
+        <v>1</v>
+      </c>
+      <c r="AP136">
+        <v>1.56</v>
+      </c>
+      <c r="AQ136">
+        <v>1.22</v>
+      </c>
+      <c r="AR136">
+        <v>1.39</v>
+      </c>
+      <c r="AS136">
+        <v>1.69</v>
+      </c>
+      <c r="AT136">
+        <v>3.08</v>
+      </c>
+      <c r="AU136">
+        <v>2</v>
+      </c>
+      <c r="AV136">
+        <v>8</v>
+      </c>
+      <c r="AW136">
+        <v>2</v>
+      </c>
+      <c r="AX136">
+        <v>9</v>
+      </c>
+      <c r="AY136">
+        <v>4</v>
+      </c>
+      <c r="AZ136">
+        <v>17</v>
+      </c>
+      <c r="BA136">
+        <v>4</v>
+      </c>
+      <c r="BB136">
+        <v>3</v>
+      </c>
+      <c r="BC136">
+        <v>7</v>
+      </c>
+      <c r="BD136">
+        <v>2.88</v>
+      </c>
+      <c r="BE136">
+        <v>9</v>
+      </c>
+      <c r="BF136">
+        <v>1.58</v>
+      </c>
+      <c r="BG136">
+        <v>1.21</v>
+      </c>
+      <c r="BH136">
+        <v>3.65</v>
+      </c>
+      <c r="BI136">
+        <v>1.37</v>
+      </c>
+      <c r="BJ136">
+        <v>2.7</v>
+      </c>
+      <c r="BK136">
+        <v>1.62</v>
+      </c>
+      <c r="BL136">
+        <v>2.07</v>
+      </c>
+      <c r="BM136">
+        <v>1.96</v>
+      </c>
+      <c r="BN136">
+        <v>1.7</v>
+      </c>
+      <c r="BO136">
+        <v>2.43</v>
+      </c>
+      <c r="BP136">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP135"/>
+  <dimension ref="A1:BP136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.88</v>
@@ -5710,7 +5710,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR24" t="n">
         <v>1.82</v>
@@ -7672,7 +7672,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR33" t="n">
         <v>1.64</v>
@@ -9416,7 +9416,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR41" t="n">
         <v>2.17</v>
@@ -9631,7 +9631,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.89</v>
@@ -12029,7 +12029,7 @@
         <v>1</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.38</v>
@@ -15302,7 +15302,7 @@
         <v>2</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR68" t="n">
         <v>1.78</v>
@@ -15953,7 +15953,7 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.38</v>
@@ -18569,7 +18569,7 @@
         <v>0.2</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ83" t="n">
         <v>1</v>
@@ -19226,7 +19226,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR86" t="n">
         <v>1.51</v>
@@ -22493,7 +22493,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ101" t="n">
         <v>0.5</v>
@@ -22508,22 +22508,22 @@
         <v>3.22</v>
       </c>
       <c r="AU101" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV101" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW101" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AX101" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY101" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AZ101" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BA101" t="n">
         <v>10</v>
@@ -22726,31 +22726,31 @@
         <v>3.58</v>
       </c>
       <c r="AU102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV102" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW102" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX102" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AY102" t="n">
         <v>11</v>
       </c>
       <c r="AZ102" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="BA102" t="n">
         <v>6</v>
       </c>
       <c r="BB102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC102" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD102" t="n">
         <v>3.15</v>
@@ -22944,31 +22944,31 @@
         <v>2.71</v>
       </c>
       <c r="AU103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV103" t="n">
         <v>3</v>
       </c>
       <c r="AW103" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX103" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY103" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AZ103" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC103" t="n">
         <v>7</v>
-      </c>
-      <c r="BA103" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB103" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC103" t="n">
-        <v>8</v>
       </c>
       <c r="BD103" t="n">
         <v>1.85</v>
@@ -23165,19 +23165,19 @@
         <v>7</v>
       </c>
       <c r="AV104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX104" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY104" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ104" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA104" t="n">
         <v>7</v>
@@ -23380,22 +23380,22 @@
         <v>3.03</v>
       </c>
       <c r="AU105" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV105" t="n">
         <v>4</v>
       </c>
       <c r="AW105" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ105" t="n">
         <v>8</v>
-      </c>
-      <c r="AX105" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY105" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ105" t="n">
-        <v>5</v>
       </c>
       <c r="BA105" t="n">
         <v>4</v>
@@ -23598,22 +23598,22 @@
         <v>3.56</v>
       </c>
       <c r="AU106" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV106" t="n">
         <v>2</v>
       </c>
       <c r="AW106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AX106" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY106" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AZ106" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BA106" t="n">
         <v>6</v>
@@ -23804,7 +23804,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AR107" t="n">
         <v>1.82</v>
@@ -23819,28 +23819,28 @@
         <v>3</v>
       </c>
       <c r="AV107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW107" t="n">
         <v>1</v>
       </c>
       <c r="AX107" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AY107" t="n">
         <v>4</v>
       </c>
       <c r="AZ107" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BA107" t="n">
         <v>1</v>
       </c>
       <c r="BB107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD107" t="n">
         <v>1.97</v>
@@ -24037,28 +24037,28 @@
         <v>4</v>
       </c>
       <c r="AV108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW108" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC108" t="n">
         <v>9</v>
-      </c>
-      <c r="AX108" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY108" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ108" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA108" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC108" t="n">
-        <v>8</v>
       </c>
       <c r="BD108" t="n">
         <v>1.64</v>
@@ -24243,31 +24243,31 @@
         <v>1</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AS109" t="n">
         <v>1.47</v>
       </c>
       <c r="AT109" t="n">
-        <v>3.16</v>
+        <v>3.07</v>
       </c>
       <c r="AU109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV109" t="n">
         <v>6</v>
       </c>
       <c r="AW109" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX109" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY109" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ109" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA109" t="n">
         <v>4</v>
@@ -24470,22 +24470,22 @@
         <v>3.65</v>
       </c>
       <c r="AU110" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW110" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AX110" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY110" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ110" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ110" t="n">
-        <v>10</v>
       </c>
       <c r="BA110" t="n">
         <v>8</v>
@@ -24688,22 +24688,22 @@
         <v>2.69</v>
       </c>
       <c r="AU111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV111" t="n">
         <v>6</v>
       </c>
       <c r="AW111" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX111" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY111" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ111" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA111" t="n">
         <v>7</v>
@@ -24891,19 +24891,19 @@
         <v>2</v>
       </c>
       <c r="AP112" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AQ112" t="n">
         <v>2.22</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AS112" t="n">
         <v>1.39</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.95</v>
+        <v>3.03</v>
       </c>
       <c r="AU112" t="n">
         <v>2</v>
@@ -24915,13 +24915,13 @@
         <v>4</v>
       </c>
       <c r="AX112" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY112" t="n">
         <v>6</v>
       </c>
       <c r="AZ112" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA112" t="n">
         <v>2</v>
@@ -25127,19 +25127,19 @@
         <v>10</v>
       </c>
       <c r="AV113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX113" t="n">
         <v>3</v>
       </c>
       <c r="AY113" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA113" t="n">
         <v>7</v>
@@ -25342,22 +25342,22 @@
         <v>2.93</v>
       </c>
       <c r="AU114" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV114" t="n">
         <v>5</v>
       </c>
       <c r="AW114" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX114" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY114" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AZ114" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA114" t="n">
         <v>4</v>
@@ -25554,28 +25554,28 @@
         <v>1.68</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AT115" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AU115" t="n">
         <v>6</v>
       </c>
       <c r="AV115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW115" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX115" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AY115" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ115" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA115" t="n">
         <v>2</v>
@@ -25772,28 +25772,28 @@
         <v>1.79</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AT116" t="n">
-        <v>3.68</v>
+        <v>3.63</v>
       </c>
       <c r="AU116" t="n">
         <v>5</v>
       </c>
       <c r="AV116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW116" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX116" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AY116" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ116" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BA116" t="n">
         <v>2</v>
@@ -25999,28 +25999,28 @@
         <v>6</v>
       </c>
       <c r="AV117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW117" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX117" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY117" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ117" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BA117" t="n">
         <v>3</v>
       </c>
       <c r="BB117" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC117" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD117" t="n">
         <v>1.75</v>
@@ -26217,16 +26217,16 @@
         <v>3</v>
       </c>
       <c r="AV118" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW118" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX118" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY118" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ118" t="n">
         <v>15</v>
@@ -26285,7 +26285,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>7818839</v>
+        <v>7818831</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -26298,204 +26298,204 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>45844.66666666666</v>
+        <v>45843.66666666666</v>
       </c>
       <c r="F119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N119" t="n">
         <v>2</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>['70', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '90+7']</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R119" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S119" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="T119" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="U119" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="V119" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="W119" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="X119" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z119" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA119" t="n">
         <v>3.8</v>
       </c>
-      <c r="AA119" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AB119" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC119" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD119" t="n">
-        <v>7.3</v>
+        <v>13</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AF119" t="n">
-        <v>2.75</v>
+        <v>4.32</v>
       </c>
       <c r="AG119" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ119" t="n">
         <v>2.2</v>
       </c>
-      <c r="AH119" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI119" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ119" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AK119" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL119" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AM119" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AQ119" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN119" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO119" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AP119" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AQ119" t="n">
-        <v>0.89</v>
-      </c>
       <c r="AR119" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.63</v>
+        <v>3.37</v>
       </c>
       <c r="AU119" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX119" t="n">
         <v>7</v>
-      </c>
-      <c r="AV119" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW119" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX119" t="n">
-        <v>2</v>
       </c>
       <c r="AY119" t="n">
         <v>10</v>
       </c>
       <c r="AZ119" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA119" t="n">
         <v>4</v>
       </c>
-      <c r="BA119" t="n">
+      <c r="BB119" t="n">
         <v>3</v>
       </c>
-      <c r="BB119" t="n">
-        <v>1</v>
-      </c>
       <c r="BC119" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BD119" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ119" t="n">
         <v>2.45</v>
       </c>
-      <c r="BE119" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BF119" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG119" t="n">
+      <c r="BK119" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP119" t="n">
         <v>1.37</v>
-      </c>
-      <c r="BH119" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI119" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BJ119" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BK119" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BL119" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BM119" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BN119" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BO119" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP119" t="n">
-        <v>1.24</v>
       </c>
     </row>
     <row r="120">
@@ -26503,7 +26503,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>7818855</v>
+        <v>7818839</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -26516,14 +26516,14 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>45850.66666666666</v>
+        <v>45844.66666666666</v>
       </c>
       <c r="F120" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -26532,188 +26532,188 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>['33', '56']</t>
+          <t>['70', '90+5']</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="R120" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S120" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="T120" t="n">
         <v>1.44</v>
       </c>
       <c r="U120" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V120" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="W120" t="n">
         <v>1.33</v>
       </c>
       <c r="X120" t="n">
-        <v>8.25</v>
+        <v>10</v>
       </c>
       <c r="Y120" t="n">
         <v>1.06</v>
       </c>
       <c r="Z120" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA120" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC120" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AD120" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF120" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="AG120" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH120" t="n">
         <v>1.65</v>
       </c>
       <c r="AI120" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AJ120" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AK120" t="n">
-        <v>1.37</v>
+        <v>1.85</v>
       </c>
       <c r="AL120" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AM120" t="n">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="AN120" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AO120" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AP120" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.89</v>
       </c>
       <c r="AR120" t="n">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="AT120" t="n">
-        <v>4.02</v>
+        <v>3.87</v>
       </c>
       <c r="AU120" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW120" t="n">
         <v>5</v>
-      </c>
-      <c r="AV120" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW120" t="n">
-        <v>4</v>
       </c>
       <c r="AX120" t="n">
         <v>4</v>
       </c>
       <c r="AY120" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ120" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BA120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB120" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC120" t="n">
         <v>4</v>
       </c>
-      <c r="BC120" t="n">
-        <v>5</v>
-      </c>
       <c r="BD120" t="n">
-        <v>1.74</v>
+        <v>2.45</v>
       </c>
       <c r="BE120" t="n">
         <v>6.5</v>
       </c>
       <c r="BF120" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="BG120" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP120" t="n">
         <v>1.24</v>
-      </c>
-      <c r="BH120" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI120" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BJ120" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BK120" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BL120" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BM120" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BN120" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BO120" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP120" t="n">
-        <v>1.28</v>
       </c>
     </row>
     <row r="121">
@@ -26721,7 +26721,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>7818930</v>
+        <v>7818855</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -26734,204 +26734,204 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>45856.83333333334</v>
+        <v>45850.66666666666</v>
       </c>
       <c r="F121" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '56']</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R121" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S121" t="n">
         <v>3.5</v>
       </c>
       <c r="T121" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="U121" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="V121" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="W121" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="X121" t="n">
-        <v>6.5</v>
+        <v>8.25</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z121" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AA121" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AB121" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AC121" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AD121" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AE121" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AF121" t="n">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="AG121" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AH121" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AI121" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AJ121" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AK121" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AL121" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AM121" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AN121" t="n">
-        <v>0.88</v>
+        <v>3</v>
       </c>
       <c r="AO121" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AR121" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS121" t="n">
         <v>1.81</v>
       </c>
-      <c r="AS121" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AT121" t="n">
-        <v>3.47</v>
+        <v>3.97</v>
       </c>
       <c r="AU121" t="n">
         <v>5</v>
       </c>
       <c r="AV121" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW121" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX121" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY121" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ121" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA121" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BB121" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC121" t="n">
         <v>5</v>
       </c>
-      <c r="BC121" t="n">
-        <v>11</v>
-      </c>
       <c r="BD121" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="BE121" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="BF121" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="BG121" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="BH121" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BI121" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="BJ121" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="BK121" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="BL121" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="BM121" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="BN121" t="n">
-        <v>1.77</v>
+        <v>1.49</v>
       </c>
       <c r="BO121" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="BP121" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="122">
@@ -26939,7 +26939,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>7818932</v>
+        <v>7818930</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -26952,204 +26952,204 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>45857.5625</v>
+        <v>45856.83333333334</v>
       </c>
       <c r="F122" t="n">
         <v>16</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>['48', '69', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="R122" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S122" t="n">
         <v>3.5</v>
       </c>
       <c r="T122" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="U122" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="V122" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="W122" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="X122" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z122" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="AA122" t="n">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AC122" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD122" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="AE122" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF122" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="AG122" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AH122" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AI122" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AJ122" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AK122" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AL122" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AM122" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AN122" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AO122" t="n">
-        <v>1.14</v>
+        <v>0.43</v>
       </c>
       <c r="AP122" t="n">
-        <v>0.88</v>
+        <v>1.1</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.23</v>
+        <v>1.61</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.79</v>
+        <v>3.33</v>
       </c>
       <c r="AU122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB122" t="n">
         <v>5</v>
       </c>
-      <c r="AV122" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW122" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY122" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ122" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA122" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB122" t="n">
-        <v>2</v>
-      </c>
       <c r="BC122" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD122" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="BE122" t="n">
         <v>8.5</v>
       </c>
       <c r="BF122" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="BG122" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="BH122" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BI122" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="BJ122" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="BK122" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="BL122" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="BM122" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="BN122" t="n">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="BO122" t="n">
-        <v>2.85</v>
+        <v>2.35</v>
       </c>
       <c r="BP122" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="123">
@@ -27157,7 +27157,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>7818927</v>
+        <v>7818932</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -27170,204 +27170,204 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>45857.66666666666</v>
+        <v>45857.5625</v>
       </c>
       <c r="F123" t="n">
         <v>16</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M123" t="n">
         <v>1</v>
       </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>['68', '81']</t>
+          <t>['48', '69', '81']</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="R123" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S123" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T123" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U123" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V123" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W123" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X123" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW123" t="n">
         <v>8</v>
       </c>
-      <c r="T123" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U123" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V123" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W123" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X123" t="n">
+      <c r="AX123" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ123" t="n">
         <v>6</v>
       </c>
-      <c r="Y123" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z123" t="n">
+      <c r="BA123" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP123" t="n">
         <v>1.34</v>
-      </c>
-      <c r="AA123" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="AB123" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="AC123" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE123" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF123" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG123" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH123" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AI123" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ123" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AK123" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AL123" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AM123" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AN123" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO123" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP123" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AQ123" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="AR123" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS123" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AT123" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU123" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV123" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW123" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX123" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY123" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ123" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA123" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB123" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC123" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD123" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BE123" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF123" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG123" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BH123" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI123" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BJ123" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BK123" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BL123" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BM123" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BN123" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BO123" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BP123" t="n">
-        <v>1.4</v>
       </c>
     </row>
     <row r="124">
@@ -27375,7 +27375,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>7818929</v>
+        <v>7818927</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -27388,84 +27388,84 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>45857.77083333334</v>
+        <v>45857.66666666666</v>
       </c>
       <c r="F124" t="n">
         <v>16</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M124" t="n">
         <v>1</v>
       </c>
       <c r="N124" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>['3', '66', '74', '81']</t>
+          <t>['68', '81']</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="R124" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S124" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="T124" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="U124" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="V124" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="W124" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AA124" t="n">
-        <v>4.25</v>
+        <v>4.96</v>
       </c>
       <c r="AB124" t="n">
-        <v>6.55</v>
+        <v>8.35</v>
       </c>
       <c r="AC124" t="n">
         <v>1.01</v>
@@ -27474,118 +27474,118 @@
         <v>11</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF124" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="AG124" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH124" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AI124" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AJ124" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AK124" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AL124" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AM124" t="n">
-        <v>2.58</v>
+        <v>3.28</v>
       </c>
       <c r="AN124" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AO124" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AP124" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AT124" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="AU124" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV124" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AW124" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AX124" t="n">
         <v>6</v>
       </c>
       <c r="AY124" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AZ124" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA124" t="n">
         <v>7</v>
       </c>
       <c r="BB124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC124" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD124" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="BE124" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BF124" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BG124" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="BH124" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="BI124" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="BJ124" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="BK124" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="BL124" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="BM124" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="BN124" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="BO124" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="BP124" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="125">
@@ -27593,7 +27593,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>7818931</v>
+        <v>7818929</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -27606,204 +27606,204 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>45858.5625</v>
+        <v>45857.77083333334</v>
       </c>
       <c r="F125" t="n">
         <v>16</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>1</v>
       </c>
       <c r="K125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L125" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M125" t="n">
         <v>1</v>
       </c>
       <c r="N125" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['3', '66', '74', '81']</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="Q125" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R125" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S125" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T125" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U125" t="n">
+        <v>3</v>
+      </c>
+      <c r="V125" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W125" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X125" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO125" t="n">
         <v>3.4</v>
       </c>
-      <c r="R125" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S125" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T125" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U125" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V125" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W125" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X125" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA125" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC125" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE125" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF125" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AG125" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AK125" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AL125" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AM125" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN125" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AO125" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AP125" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AQ125" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AR125" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS125" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AT125" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AU125" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV125" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW125" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX125" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY125" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ125" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA125" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB125" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC125" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD125" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BE125" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF125" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BG125" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BH125" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BI125" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BJ125" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BK125" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BL125" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BM125" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BN125" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BO125" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BP125" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="126">
@@ -27811,7 +27811,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>7818933</v>
+        <v>7818931</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -27824,204 +27824,204 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>45858.66666666666</v>
+        <v>45858.5625</v>
       </c>
       <c r="F126" t="n">
         <v>16</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N126" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>['61', '89']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>['75', '81']</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R126" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S126" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T126" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U126" t="n">
         <v>2.63</v>
       </c>
-      <c r="T126" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U126" t="n">
-        <v>3</v>
-      </c>
       <c r="V126" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W126" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X126" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN126" t="n">
         <v>2.75</v>
       </c>
-      <c r="W126" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X126" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC126" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE126" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF126" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG126" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH126" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI126" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ126" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK126" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL126" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AM126" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN126" t="n">
-        <v>1</v>
-      </c>
       <c r="AO126" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="AP126" t="n">
-        <v>1</v>
+        <v>2.56</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.91</v>
+        <v>1.27</v>
       </c>
       <c r="AT126" t="n">
-        <v>3.69</v>
+        <v>3.02</v>
       </c>
       <c r="AU126" t="n">
         <v>5</v>
       </c>
       <c r="AV126" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW126" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB126" t="n">
         <v>5</v>
       </c>
-      <c r="AX126" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY126" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ126" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA126" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB126" t="n">
-        <v>3</v>
-      </c>
       <c r="BC126" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BD126" t="n">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="BE126" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BF126" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="BG126" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="BH126" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="BI126" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="BJ126" t="n">
-        <v>2.43</v>
+        <v>1.97</v>
       </c>
       <c r="BK126" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="BL126" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="BM126" t="n">
-        <v>2.17</v>
+        <v>2.8</v>
       </c>
       <c r="BN126" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="BO126" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP126" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="127">
@@ -28029,7 +28029,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>7818934</v>
+        <v>7818933</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -28042,204 +28042,204 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>45859.83333333334</v>
+        <v>45858.66666666666</v>
       </c>
       <c r="F127" t="n">
         <v>16</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L127" t="n">
         <v>2</v>
       </c>
       <c r="M127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N127" t="n">
+        <v>4</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>['61', '89']</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>['75', '81']</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>4</v>
+      </c>
+      <c r="R127" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S127" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T127" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U127" t="n">
         <v>3</v>
       </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>['51', '90+8']</t>
-        </is>
-      </c>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>['22']</t>
-        </is>
-      </c>
-      <c r="Q127" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R127" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S127" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T127" t="n">
+      <c r="V127" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W127" t="n">
         <v>1.4</v>
       </c>
-      <c r="U127" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V127" t="n">
-        <v>3</v>
-      </c>
-      <c r="W127" t="n">
-        <v>1.36</v>
-      </c>
       <c r="X127" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z127" t="n">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA127" t="n">
         <v>3.3</v>
       </c>
       <c r="AB127" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="AC127" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AD127" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AE127" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF127" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AG127" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH127" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AI127" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ127" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AK127" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AL127" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM127" t="n">
         <v>1.31</v>
       </c>
-      <c r="AM127" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AN127" t="n">
-        <v>1.86</v>
+        <v>1</v>
       </c>
       <c r="AO127" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.22</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AT127" t="n">
-        <v>3.05</v>
+        <v>3.53</v>
       </c>
       <c r="AU127" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY127" t="n">
         <v>9</v>
       </c>
-      <c r="AV127" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW127" t="n">
+      <c r="AZ127" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB127" t="n">
         <v>3</v>
       </c>
-      <c r="AX127" t="n">
+      <c r="BC127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE127" t="n">
         <v>9</v>
       </c>
-      <c r="AY127" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ127" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA127" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB127" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC127" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD127" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BE127" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BF127" t="n">
-        <v>2.35</v>
+        <v>1.66</v>
       </c>
       <c r="BG127" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BH127" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="BI127" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BJ127" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="BK127" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="BL127" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="BM127" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="BN127" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BO127" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="BP127" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="128">
@@ -28247,7 +28247,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>7818940</v>
+        <v>7818934</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -28260,204 +28260,204 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>45863.83333333334</v>
+        <v>45859.83333333334</v>
       </c>
       <c r="F128" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M128" t="n">
         <v>1</v>
       </c>
       <c r="N128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51', '90+8']</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="R128" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S128" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T128" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="U128" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V128" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="W128" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X128" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z128" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AA128" t="n">
         <v>3.3</v>
       </c>
       <c r="AB128" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AC128" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AD128" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF128" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AG128" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ128" t="n">
         <v>1.91</v>
       </c>
-      <c r="AH128" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI128" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ128" t="n">
-        <v>2</v>
-      </c>
       <c r="AK128" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AL128" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AM128" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AN128" t="n">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AO128" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="AT128" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="AU128" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV128" t="n">
         <v>6</v>
       </c>
       <c r="AW128" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AX128" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY128" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ128" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA128" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB128" t="n">
         <v>4</v>
-      </c>
-      <c r="BB128" t="n">
-        <v>6</v>
       </c>
       <c r="BC128" t="n">
         <v>10</v>
       </c>
       <c r="BD128" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="BE128" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF128" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="BG128" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BH128" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="BI128" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="BJ128" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="BK128" t="n">
         <v>1.83</v>
       </c>
       <c r="BL128" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="BM128" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="BN128" t="n">
         <v>1.5</v>
       </c>
       <c r="BO128" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="BP128" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="129">
@@ -28465,7 +28465,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>7818937</v>
+        <v>7818940</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -28478,38 +28478,38 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>45864.66666666666</v>
+        <v>45863.83333333334</v>
       </c>
       <c r="F129" t="n">
         <v>17</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -28518,164 +28518,164 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>['33', '68']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="R129" t="n">
         <v>2.05</v>
       </c>
       <c r="S129" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="T129" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="U129" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="V129" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="W129" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X129" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z129" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AA129" t="n">
         <v>3.3</v>
       </c>
       <c r="AB129" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="AC129" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AD129" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF129" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AG129" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH129" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AI129" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AJ129" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AK129" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL129" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AM129" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AN129" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="AO129" t="n">
         <v>1.14</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.38</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="AT129" t="n">
-        <v>3.17</v>
+        <v>2.84</v>
       </c>
       <c r="AU129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV129" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB129" t="n">
         <v>6</v>
       </c>
-      <c r="AW129" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX129" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY129" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ129" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA129" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB129" t="n">
-        <v>4</v>
-      </c>
       <c r="BC129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BD129" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="BE129" t="n">
         <v>8.5</v>
       </c>
       <c r="BF129" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="BG129" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BP129" t="n">
         <v>1.32</v>
-      </c>
-      <c r="BH129" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BI129" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BJ129" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BK129" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BL129" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BM129" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BN129" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BO129" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BP129" t="n">
-        <v>1.27</v>
       </c>
     </row>
     <row r="130">
@@ -28683,7 +28683,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>7818939</v>
+        <v>7818937</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -28696,204 +28696,204 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>45864.77083333334</v>
+        <v>45864.66666666666</v>
       </c>
       <c r="F130" t="n">
         <v>17</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
         <v>1</v>
       </c>
       <c r="K130" t="n">
+        <v>1</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>2</v>
+      </c>
+      <c r="N130" t="n">
+        <v>2</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>['33', '68']</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="R130" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S130" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T130" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U130" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V130" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W130" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X130" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AU130" t="n">
         <v>4</v>
       </c>
-      <c r="L130" t="n">
+      <c r="AV130" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB130" t="n">
         <v>4</v>
       </c>
-      <c r="M130" t="n">
-        <v>1</v>
-      </c>
-      <c r="N130" t="n">
-        <v>5</v>
-      </c>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>['5', '16', '24', '79']</t>
-        </is>
-      </c>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>['45+2']</t>
-        </is>
-      </c>
-      <c r="Q130" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R130" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S130" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T130" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U130" t="n">
-        <v>3</v>
-      </c>
-      <c r="V130" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="W130" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X130" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y130" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z130" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA130" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AB130" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AC130" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AD130" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AE130" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF130" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AG130" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH130" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI130" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ130" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK130" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AL130" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AM130" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AN130" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AO130" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="AP130" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ130" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AR130" t="n">
+      <c r="BC130" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD130" t="n">
         <v>1.81</v>
-      </c>
-      <c r="AS130" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AT130" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU130" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV130" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW130" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX130" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY130" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ130" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA130" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB130" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC130" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD130" t="n">
-        <v>1.66</v>
       </c>
       <c r="BE130" t="n">
         <v>8.5</v>
       </c>
       <c r="BF130" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="BG130" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP130" t="n">
         <v>1.27</v>
-      </c>
-      <c r="BH130" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BI130" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BJ130" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BK130" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BL130" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BM130" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BN130" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BO130" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BP130" t="n">
-        <v>1.33</v>
       </c>
     </row>
     <row r="131">
@@ -28901,7 +28901,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>7818942</v>
+        <v>7818939</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -28914,174 +28914,174 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>45865.5625</v>
+        <v>45864.77083333334</v>
       </c>
       <c r="F131" t="n">
         <v>17</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J131" t="n">
         <v>1</v>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M131" t="n">
         <v>1</v>
       </c>
       <c r="N131" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['5', '16', '24', '79']</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="R131" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S131" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="T131" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="U131" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="V131" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W131" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X131" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV131" t="n">
         <v>3</v>
-      </c>
-      <c r="W131" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X131" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC131" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD131" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE131" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF131" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG131" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH131" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI131" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ131" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AK131" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL131" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM131" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN131" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AO131" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AP131" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ131" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AR131" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS131" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AT131" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AU131" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV131" t="n">
-        <v>2</v>
       </c>
       <c r="AW131" t="n">
         <v>10</v>
       </c>
       <c r="AX131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY131" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ131" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BA131" t="n">
         <v>4</v>
       </c>
       <c r="BB131" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BC131" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BD131" t="n">
-        <v>2.08</v>
+        <v>1.66</v>
       </c>
       <c r="BE131" t="n">
         <v>8.5</v>
       </c>
       <c r="BF131" t="n">
-        <v>2.07</v>
+        <v>2.75</v>
       </c>
       <c r="BG131" t="n">
         <v>1.27</v>
@@ -29090,25 +29090,25 @@
         <v>3.2</v>
       </c>
       <c r="BI131" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="BJ131" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="BK131" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BL131" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BM131" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BN131" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BO131" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="BP131" t="n">
         <v>1.33</v>
@@ -29119,7 +29119,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>7818941</v>
+        <v>7818942</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -29132,204 +29132,204 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>45865.66666666666</v>
+        <v>45865.5625</v>
       </c>
       <c r="F132" t="n">
         <v>17</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" t="n">
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="R132" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S132" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="T132" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U132" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V132" t="n">
+        <v>3</v>
+      </c>
+      <c r="W132" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X132" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL132" t="n">
         <v>1.3</v>
       </c>
-      <c r="U132" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V132" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W132" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X132" t="n">
+      <c r="AM132" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU132" t="n">
         <v>6</v>
       </c>
-      <c r="Y132" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD132" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE132" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF132" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AG132" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH132" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI132" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ132" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK132" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AL132" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM132" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AN132" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO132" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AP132" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ132" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AR132" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS132" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AT132" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="AU132" t="n">
-        <v>7</v>
-      </c>
       <c r="AV132" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AW132" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AX132" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY132" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AZ132" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="BA132" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BB132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BC132" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BD132" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="BE132" t="n">
         <v>8.5</v>
       </c>
       <c r="BF132" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="BG132" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BH132" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI132" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="BJ132" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="BK132" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BL132" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BM132" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BN132" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="BO132" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="BP132" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="133">
@@ -29337,7 +29337,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>7818935</v>
+        <v>7818941</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -29357,197 +29357,197 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>['32', '38', '82']</t>
-        </is>
-      </c>
       <c r="Q133" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R133" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S133" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U133" t="n">
         <v>3.4</v>
       </c>
-      <c r="R133" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S133" t="n">
-        <v>4</v>
-      </c>
-      <c r="T133" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U133" t="n">
-        <v>2.25</v>
-      </c>
       <c r="V133" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="W133" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X133" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE133" t="n">
         <v>1.25</v>
       </c>
-      <c r="X133" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD133" t="n">
+      <c r="AF133" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AU133" t="n">
         <v>7</v>
       </c>
-      <c r="AE133" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF133" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AG133" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AK133" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AL133" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AM133" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AN133" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AO133" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AP133" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AQ133" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AR133" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS133" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AT133" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AU133" t="n">
-        <v>0</v>
-      </c>
       <c r="AV133" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX133" t="n">
         <v>9</v>
       </c>
-      <c r="AW133" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX133" t="n">
-        <v>6</v>
-      </c>
       <c r="AY133" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AZ133" t="n">
         <v>15</v>
       </c>
       <c r="BA133" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BB133" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC133" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD133" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="BE133" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BF133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM133" t="n">
         <v>2.25</v>
       </c>
-      <c r="BG133" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BH133" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BI133" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BJ133" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK133" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BL133" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BM133" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BN133" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BO133" t="n">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="BP133" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="134">
@@ -29555,7 +29555,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>7818936</v>
+        <v>7818935</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -29568,204 +29568,204 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>45865.79166666666</v>
+        <v>45865.66666666666</v>
       </c>
       <c r="F134" t="n">
         <v>17</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '38', '82']</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R134" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="S134" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="T134" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="U134" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V134" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W134" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X134" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA134" t="n">
         <v>2.9</v>
       </c>
-      <c r="V134" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W134" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X134" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AB134" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AC134" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AD134" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AE134" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF134" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="AG134" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH134" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AI134" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AJ134" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AK134" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AL134" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AM134" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AN134" t="n">
-        <v>0.57</v>
+        <v>2.57</v>
       </c>
       <c r="AO134" t="n">
-        <v>1.43</v>
+        <v>2.13</v>
       </c>
       <c r="AP134" t="n">
-        <v>0.88</v>
+        <v>2.25</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.9</v>
+        <v>3.31</v>
       </c>
       <c r="AU134" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV134" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AW134" t="n">
         <v>5</v>
       </c>
       <c r="AX134" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AY134" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AZ134" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BA134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB134" t="n">
         <v>6</v>
       </c>
       <c r="BC134" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD134" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="BE134" t="n">
         <v>8</v>
       </c>
       <c r="BF134" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="BG134" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BH134" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="BI134" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BJ134" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="BK134" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="BL134" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="BM134" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="BN134" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BO134" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BP134" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="135">
@@ -29773,7 +29773,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>7818938</v>
+        <v>7818936</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -29786,203 +29786,421 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>45866.79166666666</v>
+        <v>45865.79166666666</v>
       </c>
       <c r="F135" t="n">
         <v>17</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R135" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S135" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U135" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V135" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X135" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU135" t="n">
         <v>4</v>
       </c>
-      <c r="N135" t="n">
-        <v>4</v>
-      </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>['13', '22', '44', '76']</t>
-        </is>
-      </c>
-      <c r="Q135" t="n">
-        <v>5</v>
-      </c>
-      <c r="R135" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S135" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T135" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U135" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V135" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W135" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X135" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC135" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AD135" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE135" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF135" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AG135" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI135" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ135" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK135" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL135" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AM135" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN135" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO135" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AP135" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AQ135" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR135" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AS135" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AT135" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AU135" t="n">
-        <v>3</v>
-      </c>
       <c r="AV135" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW135" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX135" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY135" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AZ135" t="n">
         <v>14</v>
       </c>
       <c r="BA135" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>7818938</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>45866.79166666666</v>
+      </c>
+      <c r="F136" t="n">
+        <v>17</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>3</v>
+      </c>
+      <c r="K136" t="n">
+        <v>3</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
         <v>4</v>
       </c>
-      <c r="BB135" t="n">
+      <c r="N136" t="n">
+        <v>4</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>['13', '22', '44', '76']</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>5</v>
+      </c>
+      <c r="R136" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S136" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U136" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V136" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W136" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X136" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB136" t="n">
         <v>3</v>
       </c>
-      <c r="BC135" t="n">
+      <c r="BC136" t="n">
         <v>7</v>
       </c>
-      <c r="BD135" t="n">
+      <c r="BD136" t="n">
         <v>2.88</v>
       </c>
-      <c r="BE135" t="n">
+      <c r="BE136" t="n">
         <v>9</v>
       </c>
-      <c r="BF135" t="n">
+      <c r="BF136" t="n">
         <v>1.58</v>
       </c>
-      <c r="BG135" t="n">
+      <c r="BG136" t="n">
         <v>1.21</v>
       </c>
-      <c r="BH135" t="n">
+      <c r="BH136" t="n">
         <v>3.65</v>
       </c>
-      <c r="BI135" t="n">
+      <c r="BI136" t="n">
         <v>1.37</v>
       </c>
-      <c r="BJ135" t="n">
+      <c r="BJ136" t="n">
         <v>2.7</v>
       </c>
-      <c r="BK135" t="n">
+      <c r="BK136" t="n">
         <v>1.62</v>
       </c>
-      <c r="BL135" t="n">
+      <c r="BL136" t="n">
         <v>2.07</v>
       </c>
-      <c r="BM135" t="n">
+      <c r="BM136" t="n">
         <v>1.96</v>
       </c>
-      <c r="BN135" t="n">
+      <c r="BN136" t="n">
         <v>1.7</v>
       </c>
-      <c r="BO135" t="n">
+      <c r="BO136" t="n">
         <v>2.43</v>
       </c>
-      <c r="BP135" t="n">
+      <c r="BP136" t="n">
         <v>1.45</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP136"/>
+  <dimension ref="A1:BP137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.22</v>
@@ -2876,7 +2876,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -6582,7 +6582,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR28" t="n">
         <v>1.27</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.5</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.22</v>
@@ -9198,7 +9198,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR40" t="n">
         <v>2.12</v>
@@ -11375,7 +11375,7 @@
         <v>1.67</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.22</v>
@@ -12683,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.38</v>
@@ -13558,7 +13558,7 @@
         <v>2</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR60" t="n">
         <v>2.23</v>
@@ -16174,7 +16174,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR72" t="n">
         <v>1.83</v>
@@ -17043,7 +17043,7 @@
         <v>0.2</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.44</v>
@@ -18136,7 +18136,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR81" t="n">
         <v>1.51</v>
@@ -19880,7 +19880,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR89" t="n">
         <v>1.86</v>
@@ -20749,7 +20749,7 @@
         <v>0.83</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.5600000000000001</v>
@@ -25330,7 +25330,7 @@
         <v>2</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR114" t="n">
         <v>1.4</v>
@@ -25763,7 +25763,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.89</v>
@@ -27943,7 +27943,7 @@
         <v>0.88</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.89</v>
@@ -30202,6 +30202,224 @@
       </c>
       <c r="BP136" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>7818947</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>45870.83333333334</v>
+      </c>
+      <c r="F137" t="n">
+        <v>18</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" t="n">
+        <v>2</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>3</v>
+      </c>
+      <c r="R137" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S137" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T137" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U137" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V137" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W137" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X137" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP137"/>
+  <dimension ref="A1:BP140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ2" t="n">
         <v>2.22</v>
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
@@ -938,10 +938,10 @@
         <v>5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
         <v>6</v>
@@ -1144,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="n">
         <v>6</v>
@@ -1156,10 +1156,10 @@
         <v>8</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
         <v>2</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW4" t="n">
         <v>21</v>
@@ -1374,10 +1374,10 @@
         <v>5</v>
       </c>
       <c r="AY4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA4" t="n">
         <v>13</v>
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>14</v>
@@ -1592,10 +1592,10 @@
         <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA5" t="n">
         <v>15</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW6" t="n">
         <v>6</v>
@@ -1810,10 +1810,10 @@
         <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
         <v>5</v>
@@ -2016,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW7" t="n">
         <v>10</v>
@@ -2028,10 +2028,10 @@
         <v>8</v>
       </c>
       <c r="AY7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA7" t="n">
         <v>5</v>
@@ -2234,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW8" t="n">
         <v>6</v>
@@ -2246,10 +2246,10 @@
         <v>7</v>
       </c>
       <c r="AY8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
@@ -2452,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW9" t="n">
         <v>7</v>
@@ -2464,10 +2464,10 @@
         <v>12</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
         <v>1</v>
@@ -2670,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
         <v>11</v>
@@ -2682,10 +2682,10 @@
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>5</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.78</v>
@@ -2888,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
         <v>8</v>
@@ -2900,10 +2900,10 @@
         <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
         <v>7</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW12" t="n">
         <v>9</v>
@@ -3118,10 +3118,10 @@
         <v>12</v>
       </c>
       <c r="AY12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>16</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>17</v>
       </c>
       <c r="BA12" t="n">
         <v>6</v>
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3324,10 +3324,10 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV13" t="n">
         <v>4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5</v>
       </c>
       <c r="AW13" t="n">
         <v>18</v>
@@ -3336,10 +3336,10 @@
         <v>7</v>
       </c>
       <c r="AY13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -3536,16 +3536,16 @@
         <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
         <v>6</v>
@@ -3554,10 +3554,10 @@
         <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3748,7 +3748,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3760,10 +3760,10 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW15" t="n">
         <v>6</v>
@@ -3772,10 +3772,10 @@
         <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA15" t="n">
         <v>4</v>
@@ -3969,19 +3969,19 @@
         <v>1</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AU16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV16" t="n">
         <v>4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>5</v>
       </c>
       <c r="AW16" t="n">
         <v>9</v>
@@ -3990,10 +3990,10 @@
         <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
         <v>7</v>
@@ -4196,10 +4196,10 @@
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW17" t="n">
         <v>8</v>
@@ -4208,10 +4208,10 @@
         <v>8</v>
       </c>
       <c r="AY17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
         <v>6</v>
@@ -4405,19 +4405,19 @@
         <v>2.22</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW18" t="n">
         <v>6</v>
@@ -4426,10 +4426,10 @@
         <v>13</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
         <v>8</v>
@@ -4623,19 +4623,19 @@
         <v>0.38</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.05</v>
+        <v>0.91</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW19" t="n">
         <v>16</v>
@@ -4644,10 +4644,10 @@
         <v>8</v>
       </c>
       <c r="AY19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
         <v>8</v>
@@ -4841,19 +4841,19 @@
         <v>0.22</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.09</v>
+        <v>2.82</v>
       </c>
       <c r="AU20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
         <v>9</v>
@@ -4862,10 +4862,10 @@
         <v>3</v>
       </c>
       <c r="AY20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA20" t="n">
         <v>4</v>
@@ -5059,19 +5059,19 @@
         <v>1.25</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.23</v>
+        <v>2.96</v>
       </c>
       <c r="AU21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW21" t="n">
         <v>11</v>
@@ -5080,10 +5080,10 @@
         <v>5</v>
       </c>
       <c r="AY21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA21" t="n">
         <v>3</v>
@@ -5280,16 +5280,16 @@
         <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW22" t="n">
         <v>13</v>
@@ -5298,10 +5298,10 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA22" t="n">
         <v>10</v>
@@ -5495,19 +5495,19 @@
         <v>0.89</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.17</v>
+        <v>2.9</v>
       </c>
       <c r="AU23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW23" t="n">
         <v>2</v>
@@ -5516,10 +5516,10 @@
         <v>13</v>
       </c>
       <c r="AY23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA23" t="n">
         <v>2</v>
@@ -5713,19 +5713,19 @@
         <v>1.22</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AS24" t="n">
         <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW24" t="n">
         <v>15</v>
@@ -5734,10 +5734,10 @@
         <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA24" t="n">
         <v>2</v>
@@ -5931,19 +5931,19 @@
         <v>1.22</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="AU25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV25" t="n">
         <v>4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>5</v>
       </c>
       <c r="AW25" t="n">
         <v>12</v>
@@ -5952,10 +5952,10 @@
         <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA25" t="n">
         <v>3</v>
@@ -6149,19 +6149,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.53</v>
+        <v>2.27</v>
       </c>
       <c r="AU26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW26" t="n">
         <v>12</v>
@@ -6170,10 +6170,10 @@
         <v>4</v>
       </c>
       <c r="AY26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA26" t="n">
         <v>10</v>
@@ -6364,22 +6364,22 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.83</v>
+        <v>3.57</v>
       </c>
       <c r="AU27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW27" t="n">
         <v>8</v>
@@ -6388,10 +6388,10 @@
         <v>4</v>
       </c>
       <c r="AY27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA27" t="n">
         <v>6</v>
@@ -6579,25 +6579,25 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.78</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW28" t="n">
         <v>11</v>
@@ -6606,10 +6606,10 @@
         <v>9</v>
       </c>
       <c r="AY28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA28" t="n">
         <v>3</v>
@@ -6800,22 +6800,22 @@
         <v>2.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.16</v>
+        <v>2.89</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW29" t="n">
         <v>3</v>
@@ -6824,10 +6824,10 @@
         <v>4</v>
       </c>
       <c r="AY29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA29" t="n">
         <v>6</v>
@@ -7015,25 +7015,25 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.38</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.33</v>
+        <v>3.05</v>
       </c>
       <c r="AU30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW30" t="n">
         <v>17</v>
@@ -7042,10 +7042,10 @@
         <v>10</v>
       </c>
       <c r="AY30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA30" t="n">
         <v>6</v>
@@ -7236,22 +7236,22 @@
         <v>2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW31" t="n">
         <v>19</v>
@@ -7260,10 +7260,10 @@
         <v>9</v>
       </c>
       <c r="AY31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
         <v>9</v>
@@ -7457,19 +7457,19 @@
         <v>1</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW32" t="n">
         <v>15</v>
@@ -7478,10 +7478,10 @@
         <v>9</v>
       </c>
       <c r="AY32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA32" t="n">
         <v>7</v>
@@ -7675,19 +7675,19 @@
         <v>1.22</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW33" t="n">
         <v>6</v>
@@ -7696,10 +7696,10 @@
         <v>13</v>
       </c>
       <c r="AY33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA33" t="n">
         <v>2</v>
@@ -7893,19 +7893,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="AU34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW34" t="n">
         <v>4</v>
@@ -7914,10 +7914,10 @@
         <v>9</v>
       </c>
       <c r="AY34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA34" t="n">
         <v>4</v>
@@ -8111,19 +8111,19 @@
         <v>2.22</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="AU35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW35" t="n">
         <v>9</v>
@@ -8132,10 +8132,10 @@
         <v>6</v>
       </c>
       <c r="AY35" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA35" t="n">
         <v>10</v>
@@ -8329,19 +8329,19 @@
         <v>1</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="AU36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW36" t="n">
         <v>9</v>
@@ -8350,10 +8350,10 @@
         <v>7</v>
       </c>
       <c r="AY36" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA36" t="n">
         <v>1</v>
@@ -8547,19 +8547,19 @@
         <v>1.38</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.63</v>
+        <v>2.37</v>
       </c>
       <c r="AU37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW37" t="n">
         <v>6</v>
@@ -8568,10 +8568,10 @@
         <v>4</v>
       </c>
       <c r="AY37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA37" t="n">
         <v>5</v>
@@ -8765,19 +8765,19 @@
         <v>1.22</v>
       </c>
       <c r="AR38" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AU38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW38" t="n">
         <v>7</v>
@@ -8786,10 +8786,10 @@
         <v>17</v>
       </c>
       <c r="AY38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA38" t="n">
         <v>2</v>
@@ -8977,25 +8977,25 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.38</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW39" t="n">
         <v>11</v>
@@ -9004,10 +9004,10 @@
         <v>5</v>
       </c>
       <c r="AY39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA39" t="n">
         <v>7</v>
@@ -9201,19 +9201,19 @@
         <v>1.78</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="AT40" t="n">
-        <v>4.21</v>
+        <v>3.94</v>
       </c>
       <c r="AU40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW40" t="n">
         <v>13</v>
@@ -9222,10 +9222,10 @@
         <v>7</v>
       </c>
       <c r="AY40" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA40" t="n">
         <v>5</v>
@@ -9419,19 +9419,19 @@
         <v>1.22</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.73</v>
+        <v>3.47</v>
       </c>
       <c r="AU41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW41" t="n">
         <v>6</v>
@@ -9440,10 +9440,10 @@
         <v>19</v>
       </c>
       <c r="AY41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA41" t="n">
         <v>3</v>
@@ -9631,25 +9631,25 @@
         <v>0.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AU42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW42" t="n">
         <v>3</v>
@@ -9658,10 +9658,10 @@
         <v>2</v>
       </c>
       <c r="AY42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA42" t="n">
         <v>4</v>
@@ -9855,19 +9855,19 @@
         <v>0.22</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="AU43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW43" t="n">
         <v>15</v>
@@ -9876,10 +9876,10 @@
         <v>9</v>
       </c>
       <c r="AY43" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ43" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA43" t="n">
         <v>4</v>
@@ -10070,22 +10070,22 @@
         <v>2</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AT44" t="n">
-        <v>3.68</v>
+        <v>3.41</v>
       </c>
       <c r="AU44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV44" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW44" t="n">
         <v>8</v>
@@ -10094,10 +10094,10 @@
         <v>12</v>
       </c>
       <c r="AY44" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA44" t="n">
         <v>4</v>
@@ -10288,22 +10288,22 @@
         <v>2</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.54</v>
+        <v>2.28</v>
       </c>
       <c r="AU45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW45" t="n">
         <v>7</v>
@@ -10312,10 +10312,10 @@
         <v>5</v>
       </c>
       <c r="AY45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA45" t="n">
         <v>2</v>
@@ -10503,25 +10503,25 @@
         <v>1.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.25</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AT46" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AU46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW46" t="n">
         <v>9</v>
@@ -10530,10 +10530,10 @@
         <v>3</v>
       </c>
       <c r="AY46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA46" t="n">
         <v>11</v>
@@ -10727,19 +10727,19 @@
         <v>1.38</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT47" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW47" t="n">
         <v>4</v>
@@ -10748,10 +10748,10 @@
         <v>11</v>
       </c>
       <c r="AY47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ47" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA47" t="n">
         <v>1</v>
@@ -10939,25 +10939,25 @@
         <v>1.33</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="AR48" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.29</v>
+        <v>3.03</v>
       </c>
       <c r="AU48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW48" t="n">
         <v>11</v>
@@ -10966,10 +10966,10 @@
         <v>3</v>
       </c>
       <c r="AY48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA48" t="n">
         <v>12</v>
@@ -11160,22 +11160,22 @@
         <v>1.88</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="AU49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW49" t="n">
         <v>12</v>
@@ -11184,10 +11184,10 @@
         <v>11</v>
       </c>
       <c r="AY49" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ49" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA49" t="n">
         <v>6</v>
@@ -11381,19 +11381,19 @@
         <v>1.22</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="AU50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW50" t="n">
         <v>13</v>
@@ -11402,10 +11402,10 @@
         <v>17</v>
       </c>
       <c r="AY50" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA50" t="n">
         <v>3</v>
@@ -11599,19 +11599,19 @@
         <v>1</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.77</v>
+        <v>2.51</v>
       </c>
       <c r="AU51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW51" t="n">
         <v>8</v>
@@ -11620,10 +11620,10 @@
         <v>10</v>
       </c>
       <c r="AY51" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ51" t="n">
         <v>13</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>14</v>
       </c>
       <c r="BA51" t="n">
         <v>3</v>
@@ -11817,19 +11817,19 @@
         <v>1</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.98</v>
+        <v>2.71</v>
       </c>
       <c r="AU52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW52" t="n">
         <v>9</v>
@@ -11838,10 +11838,10 @@
         <v>7</v>
       </c>
       <c r="AY52" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA52" t="n">
         <v>7</v>
@@ -12029,25 +12029,25 @@
         <v>1</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.38</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AS53" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="AU53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW53" t="n">
         <v>7</v>
@@ -12056,10 +12056,10 @@
         <v>13</v>
       </c>
       <c r="AY53" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ53" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA53" t="n">
         <v>4</v>
@@ -12253,19 +12253,19 @@
         <v>0.22</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW54" t="n">
         <v>8</v>
@@ -12274,10 +12274,10 @@
         <v>8</v>
       </c>
       <c r="AY54" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA54" t="n">
         <v>6</v>
@@ -12468,22 +12468,22 @@
         <v>3</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.66</v>
+        <v>3.38</v>
       </c>
       <c r="AU55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW55" t="n">
         <v>13</v>
@@ -12492,10 +12492,10 @@
         <v>9</v>
       </c>
       <c r="AY55" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ55" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA55" t="n">
         <v>3</v>
@@ -12689,19 +12689,19 @@
         <v>0.38</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="AU56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW56" t="n">
         <v>14</v>
@@ -12710,10 +12710,10 @@
         <v>9</v>
       </c>
       <c r="AY56" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA56" t="n">
         <v>2</v>
@@ -12907,19 +12907,19 @@
         <v>1.38</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AU57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW57" t="n">
         <v>13</v>
@@ -12928,10 +12928,10 @@
         <v>3</v>
       </c>
       <c r="AY57" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA57" t="n">
         <v>5</v>
@@ -13122,22 +13122,22 @@
         <v>2.25</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AT58" t="n">
-        <v>3.13</v>
+        <v>2.86</v>
       </c>
       <c r="AU58" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW58" t="n">
         <v>12</v>
@@ -13146,10 +13146,10 @@
         <v>5</v>
       </c>
       <c r="AY58" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA58" t="n">
         <v>8</v>
@@ -13343,19 +13343,19 @@
         <v>1</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AT59" t="n">
-        <v>3.06</v>
+        <v>2.79</v>
       </c>
       <c r="AU59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW59" t="n">
         <v>8</v>
@@ -13364,10 +13364,10 @@
         <v>7</v>
       </c>
       <c r="AY59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA59" t="n">
         <v>4</v>
@@ -13561,19 +13561,19 @@
         <v>1.78</v>
       </c>
       <c r="AR60" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AT60" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="AU60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW60" t="n">
         <v>10</v>
@@ -13582,10 +13582,10 @@
         <v>5</v>
       </c>
       <c r="AY60" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA60" t="n">
         <v>4</v>
@@ -13779,19 +13779,19 @@
         <v>2.22</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AT61" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="AU61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW61" t="n">
         <v>9</v>
@@ -13800,10 +13800,10 @@
         <v>7</v>
       </c>
       <c r="AY61" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ61" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA61" t="n">
         <v>3</v>
@@ -13997,19 +13997,19 @@
         <v>1.25</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="AU62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV62" t="n">
         <v>3</v>
-      </c>
-      <c r="AV62" t="n">
-        <v>4</v>
       </c>
       <c r="AW62" t="n">
         <v>6</v>
@@ -14018,10 +14018,10 @@
         <v>8</v>
       </c>
       <c r="AY62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ62" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA62" t="n">
         <v>3</v>
@@ -14212,22 +14212,22 @@
         <v>1</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.98</v>
+        <v>2.71</v>
       </c>
       <c r="AU63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW63" t="n">
         <v>12</v>
@@ -14236,10 +14236,10 @@
         <v>8</v>
       </c>
       <c r="AY63" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA63" t="n">
         <v>3</v>
@@ -14433,19 +14433,19 @@
         <v>1</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT64" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="AU64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW64" t="n">
         <v>6</v>
@@ -14454,10 +14454,10 @@
         <v>6</v>
       </c>
       <c r="AY64" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA64" t="n">
         <v>8</v>
@@ -14648,22 +14648,22 @@
         <v>1.88</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.29</v>
+        <v>3.03</v>
       </c>
       <c r="AU65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW65" t="n">
         <v>4</v>
@@ -14672,10 +14672,10 @@
         <v>8</v>
       </c>
       <c r="AY65" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ65" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA65" t="n">
         <v>7</v>
@@ -14869,16 +14869,16 @@
         <v>2.22</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AS66" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AT66" t="n">
-        <v>3.84</v>
+        <v>3.57</v>
       </c>
       <c r="AU66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV66" t="n">
         <v>0</v>
@@ -14887,13 +14887,13 @@
         <v>6</v>
       </c>
       <c r="AX66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA66" t="n">
         <v>1</v>
@@ -15087,19 +15087,19 @@
         <v>0.22</v>
       </c>
       <c r="AR67" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT67" t="n">
-        <v>3.59</v>
+        <v>3.33</v>
       </c>
       <c r="AU67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW67" t="n">
         <v>9</v>
@@ -15108,10 +15108,10 @@
         <v>6</v>
       </c>
       <c r="AY67" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ67" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA67" t="n">
         <v>2</v>
@@ -15305,19 +15305,19 @@
         <v>1.22</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AT68" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="AU68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW68" t="n">
         <v>10</v>
@@ -15326,10 +15326,10 @@
         <v>11</v>
       </c>
       <c r="AY68" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ68" t="n">
         <v>16</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>17</v>
       </c>
       <c r="BA68" t="n">
         <v>4</v>
@@ -15523,19 +15523,19 @@
         <v>0.38</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT69" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AU69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW69" t="n">
         <v>5</v>
@@ -15544,10 +15544,10 @@
         <v>10</v>
       </c>
       <c r="AY69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ69" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA69" t="n">
         <v>4</v>
@@ -15741,19 +15741,19 @@
         <v>0.89</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AT70" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="AU70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW70" t="n">
         <v>5</v>
@@ -15762,10 +15762,10 @@
         <v>15</v>
       </c>
       <c r="AY70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ70" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA70" t="n">
         <v>5</v>
@@ -15953,25 +15953,25 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.38</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT71" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="AU71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW71" t="n">
         <v>20</v>
@@ -15980,10 +15980,10 @@
         <v>14</v>
       </c>
       <c r="AY71" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ71" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA71" t="n">
         <v>8</v>
@@ -16177,19 +16177,19 @@
         <v>1.78</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT72" t="n">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="AU72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW72" t="n">
         <v>6</v>
@@ -16198,10 +16198,10 @@
         <v>6</v>
       </c>
       <c r="AY72" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ72" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA72" t="n">
         <v>4</v>
@@ -16392,22 +16392,22 @@
         <v>3</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR73" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AT73" t="n">
-        <v>3.63</v>
+        <v>3.37</v>
       </c>
       <c r="AU73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW73" t="n">
         <v>14</v>
@@ -16416,10 +16416,10 @@
         <v>6</v>
       </c>
       <c r="AY73" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA73" t="n">
         <v>5</v>
@@ -16607,25 +16607,25 @@
         <v>1.25</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.22</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AT74" t="n">
-        <v>3.78</v>
+        <v>3.52</v>
       </c>
       <c r="AU74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW74" t="n">
         <v>6</v>
@@ -16634,10 +16634,10 @@
         <v>7</v>
       </c>
       <c r="AY74" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA74" t="n">
         <v>9</v>
@@ -16825,25 +16825,25 @@
         <v>1.25</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT75" t="n">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="AU75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW75" t="n">
         <v>9</v>
@@ -16852,10 +16852,10 @@
         <v>9</v>
       </c>
       <c r="AY75" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ75" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA75" t="n">
         <v>2</v>
@@ -17046,22 +17046,22 @@
         <v>2.4</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT76" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="AU76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW76" t="n">
         <v>12</v>
@@ -17070,10 +17070,10 @@
         <v>8</v>
       </c>
       <c r="AY76" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ76" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA76" t="n">
         <v>8</v>
@@ -17267,19 +17267,19 @@
         <v>1</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT77" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="AU77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW77" t="n">
         <v>12</v>
@@ -17288,10 +17288,10 @@
         <v>5</v>
       </c>
       <c r="AY77" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA77" t="n">
         <v>6</v>
@@ -17485,19 +17485,19 @@
         <v>2.22</v>
       </c>
       <c r="AR78" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AT78" t="n">
-        <v>2.97</v>
+        <v>2.72</v>
       </c>
       <c r="AU78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV78" t="n">
         <v>3</v>
-      </c>
-      <c r="AV78" t="n">
-        <v>4</v>
       </c>
       <c r="AW78" t="n">
         <v>9</v>
@@ -17506,10 +17506,10 @@
         <v>3</v>
       </c>
       <c r="AY78" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA78" t="n">
         <v>2</v>
@@ -17703,19 +17703,19 @@
         <v>1.25</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT79" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AU79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW79" t="n">
         <v>9</v>
@@ -17724,10 +17724,10 @@
         <v>7</v>
       </c>
       <c r="AY79" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ79" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA79" t="n">
         <v>5</v>
@@ -17918,22 +17918,22 @@
         <v>2</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR80" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT80" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="AU80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV80" t="n">
         <v>3</v>
-      </c>
-      <c r="AV80" t="n">
-        <v>4</v>
       </c>
       <c r="AW80" t="n">
         <v>6</v>
@@ -17942,10 +17942,10 @@
         <v>7</v>
       </c>
       <c r="AY80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ80" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA80" t="n">
         <v>2</v>
@@ -18139,19 +18139,19 @@
         <v>1.78</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT81" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="AU81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW81" t="n">
         <v>4</v>
@@ -18160,10 +18160,10 @@
         <v>9</v>
       </c>
       <c r="AY81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ81" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA81" t="n">
         <v>2</v>
@@ -18357,19 +18357,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR82" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT82" t="n">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="AU82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW82" t="n">
         <v>7</v>
@@ -18378,10 +18378,10 @@
         <v>9</v>
       </c>
       <c r="AY82" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ82" t="n">
         <v>16</v>
-      </c>
-      <c r="AZ82" t="n">
-        <v>17</v>
       </c>
       <c r="BA82" t="n">
         <v>8</v>
@@ -18569,25 +18569,25 @@
         <v>0.2</v>
       </c>
       <c r="AP83" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ83" t="n">
         <v>1</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="AU83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW83" t="n">
         <v>6</v>
@@ -18596,10 +18596,10 @@
         <v>14</v>
       </c>
       <c r="AY83" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ83" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA83" t="n">
         <v>6</v>
@@ -18793,19 +18793,19 @@
         <v>1.38</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT84" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="AU84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW84" t="n">
         <v>14</v>
@@ -18814,10 +18814,10 @@
         <v>6</v>
       </c>
       <c r="AY84" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ84" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA84" t="n">
         <v>11</v>
@@ -19011,19 +19011,19 @@
         <v>0.22</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AU85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW85" t="n">
         <v>19</v>
@@ -19032,10 +19032,10 @@
         <v>5</v>
       </c>
       <c r="AY85" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA85" t="n">
         <v>4</v>
@@ -19229,19 +19229,19 @@
         <v>1.22</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AT86" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AU86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW86" t="n">
         <v>9</v>
@@ -19250,10 +19250,10 @@
         <v>12</v>
       </c>
       <c r="AY86" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ86" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA86" t="n">
         <v>3</v>
@@ -19447,19 +19447,19 @@
         <v>1.38</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AT87" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AU87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW87" t="n">
         <v>18</v>
@@ -19468,10 +19468,10 @@
         <v>5</v>
       </c>
       <c r="AY87" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA87" t="n">
         <v>12</v>
@@ -19665,19 +19665,19 @@
         <v>0.38</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AT88" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="AU88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW88" t="n">
         <v>12</v>
@@ -19686,10 +19686,10 @@
         <v>7</v>
       </c>
       <c r="AY88" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ88" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA88" t="n">
         <v>5</v>
@@ -19877,25 +19877,25 @@
         <v>2.17</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.78</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT89" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="AU89" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW89" t="n">
         <v>5</v>
@@ -19904,10 +19904,10 @@
         <v>7</v>
       </c>
       <c r="AY89" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ89" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA89" t="n">
         <v>7</v>
@@ -20101,19 +20101,19 @@
         <v>1.22</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AT90" t="n">
-        <v>3.48</v>
+        <v>3.21</v>
       </c>
       <c r="AU90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW90" t="n">
         <v>11</v>
@@ -20122,10 +20122,10 @@
         <v>4</v>
       </c>
       <c r="AY90" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA90" t="n">
         <v>6</v>
@@ -20316,22 +20316,22 @@
         <v>2.25</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT91" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="AU91" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV91" t="n">
         <v>7</v>
-      </c>
-      <c r="AV91" t="n">
-        <v>8</v>
       </c>
       <c r="AW91" t="n">
         <v>10</v>
@@ -20340,10 +20340,10 @@
         <v>3</v>
       </c>
       <c r="AY91" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA91" t="n">
         <v>11</v>
@@ -20531,25 +20531,25 @@
         <v>0.4</v>
       </c>
       <c r="AP92" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ92" t="n">
         <v>1</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="AU92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV92" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW92" t="n">
         <v>15</v>
@@ -20558,10 +20558,10 @@
         <v>5</v>
       </c>
       <c r="AY92" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ92" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA92" t="n">
         <v>5</v>
@@ -20755,19 +20755,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT93" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="AU93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW93" t="n">
         <v>11</v>
@@ -20776,10 +20776,10 @@
         <v>5</v>
       </c>
       <c r="AY93" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA93" t="n">
         <v>7</v>
@@ -20973,31 +20973,31 @@
         <v>1.38</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AU94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW94" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX94" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ94" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BA94" t="n">
         <v>0</v>
@@ -21191,28 +21191,28 @@
         <v>2.22</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AT95" t="n">
-        <v>3.07</v>
+        <v>2.82</v>
       </c>
       <c r="AU95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW95" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY95" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ95" t="n">
         <v>14</v>
@@ -21409,28 +21409,28 @@
         <v>1.22</v>
       </c>
       <c r="AR96" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.78</v>
+        <v>3.52</v>
       </c>
       <c r="AU96" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW96" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX96" t="n">
         <v>7</v>
       </c>
-      <c r="AX96" t="n">
-        <v>6</v>
-      </c>
       <c r="AY96" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ96" t="n">
         <v>10</v>
@@ -21627,31 +21627,31 @@
         <v>1.25</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT97" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="AU97" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV97" t="n">
         <v>4</v>
       </c>
-      <c r="AV97" t="n">
+      <c r="AW97" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX97" t="n">
         <v>5</v>
       </c>
-      <c r="AW97" t="n">
+      <c r="AY97" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ97" t="n">
         <v>9</v>
-      </c>
-      <c r="AX97" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY97" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ97" t="n">
-        <v>8</v>
       </c>
       <c r="BA97" t="n">
         <v>4</v>
@@ -21842,31 +21842,31 @@
         <v>2</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT98" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="AU98" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX98" t="n">
         <v>5</v>
       </c>
-      <c r="AV98" t="n">
+      <c r="AY98" t="n">
         <v>8</v>
-      </c>
-      <c r="AW98" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX98" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY98" t="n">
-        <v>7</v>
       </c>
       <c r="AZ98" t="n">
         <v>12</v>
@@ -22063,28 +22063,28 @@
         <v>0.89</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AT99" t="n">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="AU99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW99" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AX99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY99" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ99" t="n">
         <v>3</v>
@@ -22281,31 +22281,31 @@
         <v>0.22</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AT100" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="AU100" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW100" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX100" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AY100" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ100" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA100" t="n">
         <v>7</v>
@@ -22493,37 +22493,37 @@
         <v>0.2</v>
       </c>
       <c r="AP101" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT101" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="AU101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW101" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY101" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ101" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA101" t="n">
         <v>10</v>
@@ -22711,31 +22711,31 @@
         <v>1.5</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.89</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AT102" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="AU102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW102" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX102" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY102" t="n">
         <v>11</v>
@@ -22935,31 +22935,31 @@
         <v>1</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT103" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="AU103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW103" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX103" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY103" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ103" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA103" t="n">
         <v>5</v>
@@ -23150,22 +23150,22 @@
         <v>2</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT104" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="AU104" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW104" t="n">
         <v>8</v>
@@ -23174,10 +23174,10 @@
         <v>8</v>
       </c>
       <c r="AY104" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ104" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA104" t="n">
         <v>7</v>
@@ -23371,28 +23371,28 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT105" t="n">
-        <v>3.03</v>
+        <v>2.77</v>
       </c>
       <c r="AU105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW105" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY105" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ105" t="n">
         <v>8</v>
@@ -23589,31 +23589,31 @@
         <v>0.38</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AT106" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="AU106" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW106" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX106" t="n">
         <v>6</v>
       </c>
-      <c r="AV106" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW106" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX106" t="n">
+      <c r="AY106" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ106" t="n">
         <v>7</v>
-      </c>
-      <c r="AY106" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ106" t="n">
-        <v>9</v>
       </c>
       <c r="BA106" t="n">
         <v>6</v>
@@ -23801,37 +23801,37 @@
         <v>0.8</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.22</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AT107" t="n">
-        <v>3.73</v>
+        <v>3.47</v>
       </c>
       <c r="AU107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY107" t="n">
         <v>3</v>
       </c>
-      <c r="AV107" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW107" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX107" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY107" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ107" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA107" t="n">
         <v>1</v>
@@ -24025,19 +24025,19 @@
         <v>1.25</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="AU108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV108" t="n">
         <v>4</v>
-      </c>
-      <c r="AV108" t="n">
-        <v>5</v>
       </c>
       <c r="AW108" t="n">
         <v>15</v>
@@ -24046,10 +24046,10 @@
         <v>5</v>
       </c>
       <c r="AY108" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ108" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA108" t="n">
         <v>8</v>
@@ -24237,37 +24237,37 @@
         <v>0.67</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ109" t="n">
         <v>1</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT109" t="n">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="AU109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW109" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY109" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ109" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA109" t="n">
         <v>4</v>
@@ -24461,31 +24461,31 @@
         <v>1.38</v>
       </c>
       <c r="AR110" t="n">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AT110" t="n">
-        <v>3.65</v>
+        <v>3.39</v>
       </c>
       <c r="AU110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW110" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ110" t="n">
         <v>10</v>
-      </c>
-      <c r="AX110" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY110" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ110" t="n">
-        <v>13</v>
       </c>
       <c r="BA110" t="n">
         <v>8</v>
@@ -24676,34 +24676,34 @@
         <v>1.56</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="AU111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX111" t="n">
         <v>7</v>
       </c>
       <c r="AY111" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ111" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA111" t="n">
         <v>7</v>
@@ -24891,37 +24891,37 @@
         <v>2</v>
       </c>
       <c r="AP112" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ112" t="n">
         <v>2.22</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AT112" t="n">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="AU112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV112" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW112" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX112" t="n">
         <v>10</v>
-      </c>
-      <c r="AW112" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX112" t="n">
-        <v>11</v>
       </c>
       <c r="AY112" t="n">
         <v>6</v>
       </c>
       <c r="AZ112" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA112" t="n">
         <v>2</v>
@@ -25115,31 +25115,31 @@
         <v>0.22</v>
       </c>
       <c r="AR113" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AT113" t="n">
-        <v>3.44</v>
+        <v>3.17</v>
       </c>
       <c r="AU113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW113" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY113" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AZ113" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA113" t="n">
         <v>7</v>
@@ -25333,28 +25333,28 @@
         <v>1.78</v>
       </c>
       <c r="AR114" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS114" t="n">
         <v>1.4</v>
       </c>
-      <c r="AS114" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AT114" t="n">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="AU114" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW114" t="n">
         <v>10</v>
       </c>
-      <c r="AV114" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW114" t="n">
-        <v>11</v>
-      </c>
       <c r="AX114" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY114" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ114" t="n">
         <v>11</v>
@@ -25548,34 +25548,34 @@
         <v>1.63</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AT115" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="AU115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW115" t="n">
         <v>12</v>
       </c>
       <c r="AX115" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY115" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ115" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA115" t="n">
         <v>2</v>
@@ -25769,31 +25769,31 @@
         <v>0.89</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AT116" t="n">
-        <v>3.63</v>
+        <v>3.39</v>
       </c>
       <c r="AU116" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV116" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW116" t="n">
         <v>8</v>
       </c>
       <c r="AX116" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY116" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ116" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BA116" t="n">
         <v>2</v>
@@ -25987,31 +25987,31 @@
         <v>1.38</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="AU117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV117" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW117" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX117" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY117" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ117" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA117" t="n">
         <v>3</v>
@@ -26205,31 +26205,31 @@
         <v>1.22</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT118" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AU118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV118" t="n">
         <v>3</v>
-      </c>
-      <c r="AV118" t="n">
-        <v>4</v>
       </c>
       <c r="AW118" t="n">
         <v>9</v>
       </c>
       <c r="AX118" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY118" t="n">
         <v>11</v>
       </c>
-      <c r="AY118" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA118" t="n">
         <v>3</v>
@@ -26417,37 +26417,37 @@
         <v>0.67</v>
       </c>
       <c r="AP119" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.22</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="AU119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW119" t="n">
         <v>6</v>
       </c>
       <c r="AX119" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY119" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA119" t="n">
         <v>4</v>
@@ -26641,31 +26641,31 @@
         <v>0.89</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AS120" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AT120" t="n">
-        <v>3.87</v>
+        <v>3.57</v>
       </c>
       <c r="AU120" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV120" t="n">
         <v>0</v>
       </c>
       <c r="AW120" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AX120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY120" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA120" t="n">
         <v>3</v>
@@ -26859,28 +26859,28 @@
         <v>0.89</v>
       </c>
       <c r="AR121" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AT121" t="n">
-        <v>3.97</v>
+        <v>3.76</v>
       </c>
       <c r="AU121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW121" t="n">
         <v>6</v>
       </c>
       <c r="AX121" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY121" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ121" t="n">
         <v>11</v>
@@ -27074,34 +27074,34 @@
         <v>1.1</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AT122" t="n">
-        <v>3.33</v>
+        <v>3.07</v>
       </c>
       <c r="AU122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV122" t="n">
         <v>0</v>
       </c>
       <c r="AW122" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AX122" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY122" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ122" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA122" t="n">
         <v>6</v>
@@ -27289,37 +27289,37 @@
         <v>1.14</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AQ123" t="n">
         <v>1</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AU123" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW123" t="n">
         <v>8</v>
       </c>
       <c r="AX123" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY123" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ123" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA123" t="n">
         <v>10</v>
@@ -27510,34 +27510,34 @@
         <v>2.13</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR124" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT124" t="n">
-        <v>3.41</v>
+        <v>3.18</v>
       </c>
       <c r="AU124" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV124" t="n">
         <v>7</v>
-      </c>
-      <c r="AV124" t="n">
-        <v>8</v>
       </c>
       <c r="AW124" t="n">
         <v>12</v>
       </c>
       <c r="AX124" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY124" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ124" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA124" t="n">
         <v>7</v>
@@ -27725,25 +27725,25 @@
         <v>0.25</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.22</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.94</v>
+        <v>2.67</v>
       </c>
       <c r="AU125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW125" t="n">
         <v>6</v>
@@ -27752,10 +27752,10 @@
         <v>9</v>
       </c>
       <c r="AY125" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ125" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA125" t="n">
         <v>6</v>
@@ -27946,34 +27946,34 @@
         <v>2.4</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT126" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="AU126" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW126" t="n">
         <v>5</v>
       </c>
-      <c r="AV126" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW126" t="n">
-        <v>7</v>
-      </c>
       <c r="AX126" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY126" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ126" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA126" t="n">
         <v>2</v>
@@ -28167,25 +28167,25 @@
         <v>1.22</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AT127" t="n">
-        <v>3.53</v>
+        <v>3.26</v>
       </c>
       <c r="AU127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV127" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW127" t="n">
         <v>6</v>
       </c>
-      <c r="AW127" t="n">
-        <v>5</v>
-      </c>
       <c r="AX127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY127" t="n">
         <v>9</v>
@@ -28385,31 +28385,31 @@
         <v>1.22</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="AU128" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV128" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW128" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX128" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY128" t="n">
         <v>14</v>
       </c>
       <c r="AZ128" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA128" t="n">
         <v>6</v>
@@ -28603,22 +28603,22 @@
         <v>1.38</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.84</v>
+        <v>2.53</v>
       </c>
       <c r="AU129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW129" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX129" t="n">
         <v>16</v>
@@ -28627,7 +28627,7 @@
         <v>15</v>
       </c>
       <c r="AZ129" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA129" t="n">
         <v>4</v>
@@ -28821,28 +28821,28 @@
         <v>1.38</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AT130" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="AU130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW130" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX130" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY130" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ130" t="n">
         <v>13</v>
@@ -29039,22 +29039,22 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="AU131" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW131" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX131" t="n">
         <v>3</v>
@@ -29063,7 +29063,7 @@
         <v>18</v>
       </c>
       <c r="AZ131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA131" t="n">
         <v>4</v>
@@ -29257,22 +29257,22 @@
         <v>0.89</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AT132" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="AU132" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW132" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX132" t="n">
         <v>0</v>
@@ -29281,7 +29281,7 @@
         <v>18</v>
       </c>
       <c r="AZ132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA132" t="n">
         <v>4</v>
@@ -29475,31 +29475,31 @@
         <v>0.38</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AT133" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="AU133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV133" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW133" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX133" t="n">
         <v>8</v>
-      </c>
-      <c r="AX133" t="n">
-        <v>9</v>
       </c>
       <c r="AY133" t="n">
         <v>15</v>
       </c>
       <c r="AZ133" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA133" t="n">
         <v>7</v>
@@ -29693,31 +29693,31 @@
         <v>2.22</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT134" t="n">
-        <v>3.31</v>
+        <v>3.01</v>
       </c>
       <c r="AU134" t="n">
         <v>0</v>
       </c>
       <c r="AV134" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX134" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ134" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA134" t="n">
         <v>1</v>
@@ -29905,37 +29905,37 @@
         <v>1.43</v>
       </c>
       <c r="AP135" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.25</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AU135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW135" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX135" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY135" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ135" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA135" t="n">
         <v>2</v>
@@ -30129,28 +30129,28 @@
         <v>1.22</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AT136" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="AU136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV136" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW136" t="n">
         <v>2</v>
       </c>
       <c r="AX136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY136" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ136" t="n">
         <v>17</v>
@@ -30347,31 +30347,31 @@
         <v>1.78</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT137" t="n">
-        <v>3.21</v>
+        <v>2.93</v>
       </c>
       <c r="AU137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW137" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX137" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AY137" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ137" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BA137" t="n">
         <v>5</v>
@@ -30419,6 +30419,660 @@
         <v>0</v>
       </c>
       <c r="BP137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>7818948</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>45871.5625</v>
+      </c>
+      <c r="F138" t="n">
+        <v>18</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R138" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S138" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U138" t="n">
+        <v>3</v>
+      </c>
+      <c r="V138" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W138" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X138" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>7818946</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>45871.66666666666</v>
+      </c>
+      <c r="F139" t="n">
+        <v>18</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1</v>
+      </c>
+      <c r="L139" t="n">
+        <v>2</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" t="n">
+        <v>3</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>['59', '71']</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R139" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S139" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T139" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U139" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V139" t="n">
+        <v>3</v>
+      </c>
+      <c r="W139" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X139" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>7818945</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>45871.77083333334</v>
+      </c>
+      <c r="F140" t="n">
+        <v>18</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" t="n">
+        <v>2</v>
+      </c>
+      <c r="K140" t="n">
+        <v>3</v>
+      </c>
+      <c r="L140" t="n">
+        <v>2</v>
+      </c>
+      <c r="M140" t="n">
+        <v>2</v>
+      </c>
+      <c r="N140" t="n">
+        <v>4</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>['35', '86']</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>['26', '44']</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>4</v>
+      </c>
+      <c r="R140" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S140" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T140" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U140" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V140" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W140" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X140" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP140" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP140"/>
+  <dimension ref="A1:BP143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.44</v>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR16" t="n">
         <v>3.3</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.22</v>
@@ -6146,7 +6146,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR26" t="n">
         <v>1.26</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.9</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.4</v>
@@ -7451,10 +7451,10 @@
         <v>0.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR32" t="n">
         <v>1.58</v>
@@ -7890,7 +7890,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR34" t="n">
         <v>1.39</v>
@@ -8326,7 +8326,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR36" t="n">
         <v>1.41</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.78</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.22</v>
@@ -10067,7 +10067,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.44</v>
@@ -10942,7 +10942,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR48" t="n">
         <v>1.87</v>
@@ -11596,7 +11596,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR51" t="n">
         <v>1.38</v>
@@ -11814,7 +11814,7 @@
         <v>2</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR52" t="n">
         <v>1.64</v>
@@ -13340,7 +13340,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR59" t="n">
         <v>1.79</v>
@@ -13555,7 +13555,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.78</v>
@@ -13773,7 +13773,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ61" t="n">
         <v>2.22</v>
@@ -14209,7 +14209,7 @@
         <v>0.25</v>
       </c>
       <c r="AP63" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.4</v>
@@ -14430,7 +14430,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR64" t="n">
         <v>1.5</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ66" t="n">
         <v>2.22</v>
@@ -15081,7 +15081,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.22</v>
@@ -16828,7 +16828,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR75" t="n">
         <v>1.64</v>
@@ -17261,10 +17261,10 @@
         <v>0.25</v>
       </c>
       <c r="AP77" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR77" t="n">
         <v>1.61</v>
@@ -17915,7 +17915,7 @@
         <v>1</v>
       </c>
       <c r="AP80" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.9</v>
@@ -18354,7 +18354,7 @@
         <v>3</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR82" t="n">
         <v>2.05</v>
@@ -18572,7 +18572,7 @@
         <v>1</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR83" t="n">
         <v>1.52</v>
@@ -18787,7 +18787,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.38</v>
@@ -19659,7 +19659,7 @@
         <v>0.6</v>
       </c>
       <c r="AP88" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.38</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.22</v>
@@ -20534,7 +20534,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR92" t="n">
         <v>1.54</v>
@@ -20752,7 +20752,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR93" t="n">
         <v>1.6</v>
@@ -22932,7 +22932,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR103" t="n">
         <v>1.35</v>
@@ -23368,7 +23368,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR105" t="n">
         <v>1.61</v>
@@ -23583,7 +23583,7 @@
         <v>0.5</v>
       </c>
       <c r="AP106" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.38</v>
@@ -24019,7 +24019,7 @@
         <v>1.17</v>
       </c>
       <c r="AP108" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.25</v>
@@ -24240,7 +24240,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AR109" t="n">
         <v>1.47</v>
@@ -24455,7 +24455,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.38</v>
@@ -27292,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR123" t="n">
         <v>1.37</v>
@@ -27507,7 +27507,7 @@
         <v>0.5</v>
       </c>
       <c r="AP124" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.4</v>
@@ -28161,7 +28161,7 @@
         <v>1</v>
       </c>
       <c r="AP127" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.22</v>
@@ -29036,7 +29036,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AR131" t="n">
         <v>1.57</v>
@@ -29251,7 +29251,7 @@
         <v>0.88</v>
       </c>
       <c r="AP132" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.89</v>
@@ -31074,6 +31074,660 @@
       </c>
       <c r="BP140" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>7818949</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>45872.5625</v>
+      </c>
+      <c r="F141" t="n">
+        <v>18</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R141" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S141" t="n">
+        <v>5</v>
+      </c>
+      <c r="T141" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U141" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V141" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W141" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X141" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>7818944</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>45872.66666666666</v>
+      </c>
+      <c r="F142" t="n">
+        <v>18</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" t="n">
+        <v>2</v>
+      </c>
+      <c r="M142" t="n">
+        <v>2</v>
+      </c>
+      <c r="N142" t="n">
+        <v>4</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>['52', '79']</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>['32', '68']</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R142" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S142" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U142" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V142" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X142" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>7818950</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>45872.77083333334</v>
+      </c>
+      <c r="F143" t="n">
+        <v>18</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R143" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S143" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T143" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U143" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V143" t="n">
+        <v>3</v>
+      </c>
+      <c r="W143" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X143" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP143"/>
+  <dimension ref="A1:BP144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.38</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.89</v>
@@ -7018,7 +7018,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR30" t="n">
         <v>1.71</v>
@@ -10724,7 +10724,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR47" t="n">
         <v>1.59</v>
@@ -12465,7 +12465,7 @@
         <v>0.33</v>
       </c>
       <c r="AP55" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.4</v>
@@ -12904,7 +12904,7 @@
         <v>2</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR57" t="n">
         <v>1.21</v>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR71" t="n">
         <v>1.35</v>
@@ -16389,7 +16389,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.9</v>
@@ -18351,7 +18351,7 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.6</v>
@@ -19444,7 +19444,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR87" t="n">
         <v>1.56</v>
@@ -21403,7 +21403,7 @@
         <v>1.33</v>
       </c>
       <c r="AP96" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.22</v>
@@ -24458,7 +24458,7 @@
         <v>2</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR110" t="n">
         <v>2.03</v>
@@ -25109,7 +25109,7 @@
         <v>0.29</v>
       </c>
       <c r="AP113" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.22</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.89</v>
@@ -28818,7 +28818,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR130" t="n">
         <v>1.59</v>
@@ -31728,6 +31728,224 @@
       </c>
       <c r="BP143" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>7818943</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>45873.79166666666</v>
+      </c>
+      <c r="F144" t="n">
+        <v>18</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>1</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1</v>
+      </c>
+      <c r="N144" t="n">
+        <v>1</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S144" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T144" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U144" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V144" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W144" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X144" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO144" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP144" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.38</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.89</v>
@@ -2440,7 +2440,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.88</v>
@@ -3963,10 +3963,10 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR16" t="n">
         <v>3.3</v>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR19" t="n">
         <v>0.91</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.89</v>
@@ -5928,7 +5928,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR25" t="n">
         <v>1.2</v>
@@ -8323,10 +8323,10 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR36" t="n">
         <v>1.41</v>
@@ -8762,7 +8762,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR38" t="n">
         <v>1.87</v>
@@ -8980,7 +8980,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR39" t="n">
         <v>1.51</v>
@@ -10285,7 +10285,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.4</v>
@@ -11378,7 +11378,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR50" t="n">
         <v>1.4</v>
@@ -11593,7 +11593,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.88</v>
@@ -11814,7 +11814,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR52" t="n">
         <v>1.64</v>
@@ -12465,7 +12465,7 @@
         <v>0.33</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.4</v>
@@ -12686,7 +12686,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR56" t="n">
         <v>1.47</v>
@@ -12901,7 +12901,7 @@
         <v>0.33</v>
       </c>
       <c r="AP57" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.56</v>
@@ -13340,7 +13340,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR59" t="n">
         <v>1.79</v>
@@ -15517,10 +15517,10 @@
         <v>0.75</v>
       </c>
       <c r="AP69" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR69" t="n">
         <v>1.32</v>
@@ -16389,7 +16389,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.9</v>
@@ -16610,7 +16610,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR74" t="n">
         <v>1.8</v>
@@ -17264,7 +17264,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR77" t="n">
         <v>1.61</v>
@@ -18351,7 +18351,7 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.6</v>
@@ -19005,7 +19005,7 @@
         <v>0.4</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.2</v>
@@ -19662,7 +19662,7 @@
         <v>2</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR88" t="n">
         <v>1.94</v>
@@ -20098,7 +20098,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR90" t="n">
         <v>1.67</v>
@@ -20534,7 +20534,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR92" t="n">
         <v>1.54</v>
@@ -20967,7 +20967,7 @@
         <v>0.8</v>
       </c>
       <c r="AP94" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.38</v>
@@ -21185,7 +21185,7 @@
         <v>1.83</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ95" t="n">
         <v>2.22</v>
@@ -21403,10 +21403,10 @@
         <v>1.33</v>
       </c>
       <c r="AP96" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR96" t="n">
         <v>2</v>
@@ -22932,7 +22932,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR103" t="n">
         <v>1.35</v>
@@ -23586,7 +23586,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR106" t="n">
         <v>1.74</v>
@@ -25109,7 +25109,7 @@
         <v>0.29</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.2</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.78</v>
@@ -25545,7 +25545,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.44</v>
@@ -26202,7 +26202,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR118" t="n">
         <v>1.68</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.89</v>
@@ -27292,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR123" t="n">
         <v>1.37</v>
@@ -28379,10 +28379,10 @@
         <v>1.38</v>
       </c>
       <c r="AP128" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR128" t="n">
         <v>1.4</v>
@@ -28815,7 +28815,7 @@
         <v>1.14</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.56</v>
@@ -29472,7 +29472,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR133" t="n">
         <v>1.67</v>
@@ -31216,7 +31216,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR141" t="n">
         <v>1.78</v>
@@ -31867,7 +31867,7 @@
         <v>1.38</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.56</v>
@@ -32164,6 +32164,660 @@
       </c>
       <c r="BP145" t="n">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>7818958</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>45878.5625</v>
+      </c>
+      <c r="F146" t="n">
+        <v>19</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R146" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S146" t="n">
+        <v>4</v>
+      </c>
+      <c r="T146" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V146" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W146" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X146" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI146" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ146" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK146" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO146" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP146" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>7818951</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>45878.66666666666</v>
+      </c>
+      <c r="F147" t="n">
+        <v>19</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1</v>
+      </c>
+      <c r="K147" t="n">
+        <v>2</v>
+      </c>
+      <c r="L147" t="n">
+        <v>4</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>5</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>['28', '56', '78', '84']</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R147" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S147" t="n">
+        <v>7</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U147" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V147" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X147" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO147" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BP147" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>7818954</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>45878.77083333334</v>
+      </c>
+      <c r="F148" t="n">
+        <v>19</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3</v>
+      </c>
+      <c r="M148" t="n">
+        <v>3</v>
+      </c>
+      <c r="N148" t="n">
+        <v>6</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>['45+1', '54', '90+1']</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>['60', '82', '90+6']</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R148" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S148" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T148" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U148" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V148" t="n">
+        <v>3</v>
+      </c>
+      <c r="W148" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X148" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP148" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP148"/>
+  <dimension ref="A1:BP150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.4</v>
@@ -4402,7 +4402,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR18" t="n">
         <v>1.71</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.38</v>
@@ -5492,7 +5492,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR23" t="n">
         <v>1.3</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.22</v>
@@ -8105,10 +8105,10 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ35" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR35" t="n">
         <v>2.16</v>
@@ -8759,7 +8759,7 @@
         <v>2</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.2</v>
@@ -9413,7 +9413,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.22</v>
@@ -11157,7 +11157,7 @@
         <v>1.33</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ49" t="n">
         <v>0.9</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.8</v>
@@ -13776,7 +13776,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR61" t="n">
         <v>1.76</v>
@@ -14645,7 +14645,7 @@
         <v>0.25</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.44</v>
@@ -14866,7 +14866,7 @@
         <v>2</v>
       </c>
       <c r="AQ66" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR66" t="n">
         <v>2.05</v>
@@ -15738,7 +15738,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR70" t="n">
         <v>1.42</v>
@@ -16171,7 +16171,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.78</v>
@@ -17482,7 +17482,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ78" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR78" t="n">
         <v>1.38</v>
@@ -17697,7 +17697,7 @@
         <v>0.75</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.25</v>
@@ -19441,7 +19441,7 @@
         <v>1.4</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.56</v>
@@ -21188,7 +21188,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ95" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR95" t="n">
         <v>1.55</v>
@@ -21621,7 +21621,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.25</v>
@@ -22060,7 +22060,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR99" t="n">
         <v>1.34</v>
@@ -22275,7 +22275,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.2</v>
@@ -22714,7 +22714,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR102" t="n">
         <v>1.56</v>
@@ -24894,7 +24894,7 @@
         <v>1</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR112" t="n">
         <v>1.53</v>
@@ -25766,7 +25766,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR116" t="n">
         <v>1.66</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.38</v>
@@ -26199,7 +26199,7 @@
         <v>1.14</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.2</v>
@@ -26638,7 +26638,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR120" t="n">
         <v>1.63</v>
@@ -26856,7 +26856,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR121" t="n">
         <v>2.07</v>
@@ -27071,7 +27071,7 @@
         <v>0.43</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.44</v>
@@ -29033,7 +29033,7 @@
         <v>0.63</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.6</v>
@@ -29254,7 +29254,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR132" t="n">
         <v>1.75</v>
@@ -29690,7 +29690,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ134" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR134" t="n">
         <v>1.6</v>
@@ -32818,6 +32818,442 @@
       </c>
       <c r="BP148" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>7818955</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>45879.5625</v>
+      </c>
+      <c r="F149" t="n">
+        <v>19</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="n">
+        <v>1</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>1</v>
+      </c>
+      <c r="N149" t="n">
+        <v>2</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>['90+9']</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>4</v>
+      </c>
+      <c r="R149" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S149" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T149" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U149" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V149" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W149" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X149" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>7818953</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>45879.66666666666</v>
+      </c>
+      <c r="F150" t="n">
+        <v>19</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" t="n">
+        <v>2</v>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="n">
+        <v>2</v>
+      </c>
+      <c r="N150" t="n">
+        <v>3</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>['25', '58']</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R150" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S150" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T150" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U150" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V150" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W150" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X150" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI150" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ150" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM150" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BN150" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO150" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP150" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP150"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.88</v>
@@ -2222,7 +2222,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>3</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18" t="n">
         <v>2.3</v>
@@ -5056,7 +5056,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR21" t="n">
         <v>1.78</v>
@@ -7887,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.6</v>
@@ -10506,7 +10506,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR46" t="n">
         <v>2.07</v>
@@ -12247,7 +12247,7 @@
         <v>0.33</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.2</v>
@@ -13994,7 +13994,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR62" t="n">
         <v>1.5</v>
@@ -15735,7 +15735,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.9</v>
@@ -17700,7 +17700,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR79" t="n">
         <v>1.6</v>
@@ -18133,7 +18133,7 @@
         <v>2</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.78</v>
@@ -19223,7 +19223,7 @@
         <v>1</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.22</v>
@@ -21624,7 +21624,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR97" t="n">
         <v>1.68</v>
@@ -22929,7 +22929,7 @@
         <v>0.83</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.8</v>
@@ -24022,7 +24022,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR108" t="n">
         <v>1.65</v>
@@ -28597,7 +28597,7 @@
         <v>1.14</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.38</v>
@@ -29908,7 +29908,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR135" t="n">
         <v>1.49</v>
@@ -33254,6 +33254,224 @@
       </c>
       <c r="BP150" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>7818956</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>45880.83333333334</v>
+      </c>
+      <c r="F151" t="n">
+        <v>19</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" t="n">
+        <v>4</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>4</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>['16', '62', '79', '86']</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R151" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S151" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U151" t="n">
+        <v>3</v>
+      </c>
+      <c r="V151" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W151" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X151" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI151" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM151" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP151" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -28358,7 +28358,7 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>7818941</v>
+        <v>7818935</v>
       </c>
       <c r="C133" t="s">
         <v>68</v>
@@ -28373,190 +28373,190 @@
         <v>17</v>
       </c>
       <c r="G133" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H133" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I133">
         <v>0</v>
       </c>
       <c r="J133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M133">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N133">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O133" t="s">
-        <v>183</v>
+        <v>86</v>
       </c>
       <c r="P133" t="s">
-        <v>86</v>
+        <v>253</v>
       </c>
       <c r="Q133">
+        <v>3.4</v>
+      </c>
+      <c r="R133">
+        <v>1.91</v>
+      </c>
+      <c r="S133">
+        <v>4</v>
+      </c>
+      <c r="T133">
+        <v>1.57</v>
+      </c>
+      <c r="U133">
+        <v>2.25</v>
+      </c>
+      <c r="V133">
+        <v>3.75</v>
+      </c>
+      <c r="W133">
+        <v>1.25</v>
+      </c>
+      <c r="X133">
+        <v>13</v>
+      </c>
+      <c r="Y133">
+        <v>1.04</v>
+      </c>
+      <c r="Z133">
+        <v>2.45</v>
+      </c>
+      <c r="AA133">
+        <v>2.9</v>
+      </c>
+      <c r="AB133">
+        <v>3.1</v>
+      </c>
+      <c r="AC133">
+        <v>1.08</v>
+      </c>
+      <c r="AD133">
+        <v>7</v>
+      </c>
+      <c r="AE133">
+        <v>1.44</v>
+      </c>
+      <c r="AF133">
+        <v>2.65</v>
+      </c>
+      <c r="AG133">
+        <v>2.7</v>
+      </c>
+      <c r="AH133">
+        <v>1.44</v>
+      </c>
+      <c r="AI133">
+        <v>2.2</v>
+      </c>
+      <c r="AJ133">
+        <v>1.62</v>
+      </c>
+      <c r="AK133">
+        <v>1.39</v>
+      </c>
+      <c r="AL133">
+        <v>1.34</v>
+      </c>
+      <c r="AM133">
+        <v>1.52</v>
+      </c>
+      <c r="AN133">
+        <v>2.57</v>
+      </c>
+      <c r="AO133">
+        <v>2.13</v>
+      </c>
+      <c r="AP133">
+        <v>2.25</v>
+      </c>
+      <c r="AQ133">
         <v>2.3</v>
       </c>
-      <c r="R133">
-        <v>2.38</v>
-      </c>
-      <c r="S133">
-        <v>4.5</v>
-      </c>
-      <c r="T133">
-        <v>1.3</v>
-      </c>
-      <c r="U133">
-        <v>3.4</v>
-      </c>
-      <c r="V133">
-        <v>2.5</v>
-      </c>
-      <c r="W133">
-        <v>1.5</v>
-      </c>
-      <c r="X133">
-        <v>6</v>
-      </c>
-      <c r="Y133">
-        <v>1.13</v>
-      </c>
-      <c r="Z133">
-        <v>1.75</v>
-      </c>
-      <c r="AA133">
-        <v>3.4</v>
-      </c>
-      <c r="AB133">
-        <v>4.75</v>
-      </c>
-      <c r="AC133">
-        <v>1.04</v>
-      </c>
-      <c r="AD133">
+      <c r="AR133">
+        <v>1.6</v>
+      </c>
+      <c r="AS133">
+        <v>1.41</v>
+      </c>
+      <c r="AT133">
+        <v>3.01</v>
+      </c>
+      <c r="AU133">
+        <v>0</v>
+      </c>
+      <c r="AV133">
         <v>9</v>
       </c>
-      <c r="AE133">
-        <v>1.25</v>
-      </c>
-      <c r="AF133">
-        <v>3.8</v>
-      </c>
-      <c r="AG133">
-        <v>1.75</v>
-      </c>
-      <c r="AH133">
-        <v>2.05</v>
-      </c>
-      <c r="AI133">
-        <v>1.67</v>
-      </c>
-      <c r="AJ133">
-        <v>2.1</v>
-      </c>
-      <c r="AK133">
-        <v>1.24</v>
-      </c>
-      <c r="AL133">
-        <v>1.25</v>
-      </c>
-      <c r="AM133">
-        <v>1.95</v>
-      </c>
-      <c r="AN133">
-        <v>1.86</v>
-      </c>
-      <c r="AO133">
-        <v>0.43</v>
-      </c>
-      <c r="AP133">
-        <v>2.11</v>
-      </c>
-      <c r="AQ133">
-        <v>0.33</v>
-      </c>
-      <c r="AR133">
-        <v>1.67</v>
-      </c>
-      <c r="AS133">
-        <v>1.45</v>
-      </c>
-      <c r="AT133">
-        <v>3.12</v>
-      </c>
-      <c r="AU133">
-        <v>6</v>
-      </c>
-      <c r="AV133">
-        <v>5</v>
-      </c>
       <c r="AW133">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AX133">
         <v>8</v>
       </c>
       <c r="AY133">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AZ133">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BA133">
+        <v>1</v>
+      </c>
+      <c r="BB133">
+        <v>6</v>
+      </c>
+      <c r="BC133">
         <v>7</v>
       </c>
-      <c r="BB133">
-        <v>2</v>
-      </c>
-      <c r="BC133">
-        <v>9</v>
-      </c>
       <c r="BD133">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="BE133">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="BF133">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="BG133">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="BH133">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="BI133">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="BJ133">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BK133">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="BL133">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="BM133">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="BN133">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="BO133">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="BP133">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="134" spans="1:68">
@@ -28564,7 +28564,7 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>7818935</v>
+        <v>7818941</v>
       </c>
       <c r="C134" t="s">
         <v>68</v>
@@ -28579,190 +28579,190 @@
         <v>17</v>
       </c>
       <c r="G134" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H134" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I134">
         <v>0</v>
       </c>
       <c r="J134">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K134">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N134">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O134" t="s">
+        <v>183</v>
+      </c>
+      <c r="P134" t="s">
         <v>86</v>
       </c>
-      <c r="P134" t="s">
-        <v>253</v>
-      </c>
       <c r="Q134">
+        <v>2.3</v>
+      </c>
+      <c r="R134">
+        <v>2.38</v>
+      </c>
+      <c r="S134">
+        <v>4.5</v>
+      </c>
+      <c r="T134">
+        <v>1.3</v>
+      </c>
+      <c r="U134">
         <v>3.4</v>
       </c>
-      <c r="R134">
-        <v>1.91</v>
-      </c>
-      <c r="S134">
-        <v>4</v>
-      </c>
-      <c r="T134">
-        <v>1.57</v>
-      </c>
-      <c r="U134">
-        <v>2.25</v>
-      </c>
       <c r="V134">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="W134">
+        <v>1.5</v>
+      </c>
+      <c r="X134">
+        <v>6</v>
+      </c>
+      <c r="Y134">
+        <v>1.13</v>
+      </c>
+      <c r="Z134">
+        <v>1.75</v>
+      </c>
+      <c r="AA134">
+        <v>3.4</v>
+      </c>
+      <c r="AB134">
+        <v>4.75</v>
+      </c>
+      <c r="AC134">
+        <v>1.04</v>
+      </c>
+      <c r="AD134">
+        <v>9</v>
+      </c>
+      <c r="AE134">
         <v>1.25</v>
       </c>
-      <c r="X134">
-        <v>13</v>
-      </c>
-      <c r="Y134">
-        <v>1.04</v>
-      </c>
-      <c r="Z134">
-        <v>2.45</v>
-      </c>
-      <c r="AA134">
-        <v>2.9</v>
-      </c>
-      <c r="AB134">
-        <v>3.1</v>
-      </c>
-      <c r="AC134">
-        <v>1.08</v>
-      </c>
-      <c r="AD134">
-        <v>7</v>
-      </c>
-      <c r="AE134">
-        <v>1.44</v>
-      </c>
       <c r="AF134">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="AG134">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH134">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AI134">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ134">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AK134">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AL134">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AM134">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AN134">
-        <v>2.57</v>
+        <v>1.86</v>
       </c>
       <c r="AO134">
-        <v>2.13</v>
+        <v>0.43</v>
       </c>
       <c r="AP134">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ134">
-        <v>2.3</v>
+        <v>0.33</v>
       </c>
       <c r="AR134">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AS134">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AT134">
-        <v>3.01</v>
+        <v>3.12</v>
       </c>
       <c r="AU134">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV134">
+        <v>5</v>
+      </c>
+      <c r="AW134">
         <v>9</v>
-      </c>
-      <c r="AW134">
-        <v>4</v>
       </c>
       <c r="AX134">
         <v>8</v>
       </c>
       <c r="AY134">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AZ134">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA134">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BB134">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC134">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD134">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="BE134">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BF134">
+        <v>2.5</v>
+      </c>
+      <c r="BG134">
+        <v>1.28</v>
+      </c>
+      <c r="BH134">
+        <v>3.15</v>
+      </c>
+      <c r="BI134">
+        <v>1.49</v>
+      </c>
+      <c r="BJ134">
+        <v>2.33</v>
+      </c>
+      <c r="BK134">
+        <v>1.79</v>
+      </c>
+      <c r="BL134">
+        <v>1.85</v>
+      </c>
+      <c r="BM134">
         <v>2.25</v>
       </c>
-      <c r="BG134">
-        <v>1.38</v>
-      </c>
-      <c r="BH134">
-        <v>2.65</v>
-      </c>
-      <c r="BI134">
-        <v>1.67</v>
-      </c>
-      <c r="BJ134">
-        <v>2</v>
-      </c>
-      <c r="BK134">
-        <v>2.07</v>
-      </c>
-      <c r="BL134">
-        <v>1.62</v>
-      </c>
-      <c r="BM134">
-        <v>2.7</v>
-      </c>
       <c r="BN134">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BO134">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="BP134">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="135" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP151"/>
+  <dimension ref="A1:BP153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.33</v>
@@ -2658,7 +2658,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR20" t="n">
         <v>1.19</v>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.2</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.6</v>
@@ -7236,7 +7236,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR31" t="n">
         <v>2.25</v>
@@ -9852,7 +9852,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR43" t="n">
         <v>1.78</v>
@@ -10288,7 +10288,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR45" t="n">
         <v>1.15</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.56</v>
@@ -12250,7 +12250,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR54" t="n">
         <v>1.15</v>
@@ -12468,7 +12468,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR55" t="n">
         <v>2.3</v>
@@ -13991,7 +13991,7 @@
         <v>1</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.11</v>
@@ -14212,7 +14212,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR63" t="n">
         <v>1.64</v>
@@ -15084,7 +15084,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR67" t="n">
         <v>2.02</v>
@@ -17046,7 +17046,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR76" t="n">
         <v>1.52</v>
@@ -17479,7 +17479,7 @@
         <v>1.6</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ78" t="n">
         <v>2.3</v>
@@ -19008,7 +19008,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR85" t="n">
         <v>1.33</v>
@@ -20316,7 +20316,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR91" t="n">
         <v>1.55</v>
@@ -22057,7 +22057,7 @@
         <v>1</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.9</v>
@@ -22278,7 +22278,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR100" t="n">
         <v>1.6</v>
@@ -23150,7 +23150,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR104" t="n">
         <v>1.67</v>
@@ -24673,7 +24673,7 @@
         <v>0.86</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
         <v>0.9</v>
@@ -25112,7 +25112,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR113" t="n">
         <v>2</v>
@@ -27510,7 +27510,7 @@
         <v>2</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR124" t="n">
         <v>2.02</v>
@@ -27728,7 +27728,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR125" t="n">
         <v>1.53</v>
@@ -30123,7 +30123,7 @@
         <v>1</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.22</v>
@@ -30562,7 +30562,7 @@
         <v>1</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AR138" t="n">
         <v>1.38</v>
@@ -32088,7 +32088,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR145" t="n">
         <v>1.69</v>
@@ -33472,6 +33472,442 @@
       </c>
       <c r="BP151" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>7818963</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>45884.66666666666</v>
+      </c>
+      <c r="F152" t="n">
+        <v>20</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K152" t="n">
+        <v>2</v>
+      </c>
+      <c r="L152" t="n">
+        <v>2</v>
+      </c>
+      <c r="M152" t="n">
+        <v>2</v>
+      </c>
+      <c r="N152" t="n">
+        <v>4</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>['42', '87']</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>['10', '78']</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R152" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S152" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T152" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U152" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V152" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W152" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X152" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI152" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO152" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP152" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>7818961</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>45884.875</v>
+      </c>
+      <c r="F153" t="n">
+        <v>20</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1</v>
+      </c>
+      <c r="N153" t="n">
+        <v>2</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R153" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S153" t="n">
+        <v>4</v>
+      </c>
+      <c r="T153" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U153" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V153" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W153" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X153" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI153" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ153" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK153" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO153" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP153" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP153"/>
+  <dimension ref="A1:BP156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.6</v>
@@ -2876,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.44</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.2</v>
@@ -6361,10 +6361,10 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR27" t="n">
         <v>2.05</v>
@@ -6582,7 +6582,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR28" t="n">
         <v>1.14</v>
@@ -7018,7 +7018,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR30" t="n">
         <v>1.71</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.45</v>
@@ -7451,7 +7451,7 @@
         <v>0.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.88</v>
@@ -9195,10 +9195,10 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR40" t="n">
         <v>1.98</v>
@@ -9634,7 +9634,7 @@
         <v>1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR42" t="n">
         <v>1.19</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.27</v>
@@ -10067,7 +10067,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.44</v>
@@ -10724,7 +10724,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR47" t="n">
         <v>1.59</v>
@@ -11160,7 +11160,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR49" t="n">
         <v>1.64</v>
@@ -12904,7 +12904,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR57" t="n">
         <v>1.21</v>
@@ -13555,10 +13555,10 @@
         <v>2.33</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR60" t="n">
         <v>2.1</v>
@@ -13773,7 +13773,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ61" t="n">
         <v>2.3</v>
@@ -14209,7 +14209,7 @@
         <v>0.25</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.45</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ66" t="n">
         <v>2.3</v>
@@ -15081,7 +15081,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.27</v>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR71" t="n">
         <v>1.35</v>
@@ -16174,7 +16174,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR72" t="n">
         <v>1.7</v>
@@ -16392,7 +16392,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR73" t="n">
         <v>2.22</v>
@@ -17261,7 +17261,7 @@
         <v>0.25</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.8</v>
@@ -17915,10 +17915,10 @@
         <v>1</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR80" t="n">
         <v>1.91</v>
@@ -18136,7 +18136,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR81" t="n">
         <v>1.38</v>
@@ -18787,7 +18787,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.38</v>
@@ -19444,7 +19444,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR87" t="n">
         <v>1.56</v>
@@ -19659,7 +19659,7 @@
         <v>0.6</v>
       </c>
       <c r="AP88" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.33</v>
@@ -19880,7 +19880,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR89" t="n">
         <v>1.73</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.2</v>
@@ -21842,7 +21842,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR98" t="n">
         <v>1.67</v>
@@ -23583,7 +23583,7 @@
         <v>0.5</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.33</v>
@@ -24019,7 +24019,7 @@
         <v>1.17</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.11</v>
@@ -24455,10 +24455,10 @@
         <v>1.33</v>
       </c>
       <c r="AP110" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR110" t="n">
         <v>2.03</v>
@@ -24676,7 +24676,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR111" t="n">
         <v>1.34</v>
@@ -25330,7 +25330,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR114" t="n">
         <v>1.26</v>
@@ -27507,7 +27507,7 @@
         <v>0.5</v>
       </c>
       <c r="AP124" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.45</v>
@@ -27946,7 +27946,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR126" t="n">
         <v>1.62</v>
@@ -28161,7 +28161,7 @@
         <v>1</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.22</v>
@@ -28818,7 +28818,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR130" t="n">
         <v>1.59</v>
@@ -29251,7 +29251,7 @@
         <v>0.88</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.9</v>
@@ -30344,7 +30344,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AR137" t="n">
         <v>1.56</v>
@@ -30998,7 +30998,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AR140" t="n">
         <v>1.48</v>
@@ -31213,7 +31213,7 @@
         <v>1</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.8</v>
@@ -31431,7 +31431,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP142" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.6</v>
@@ -31649,7 +31649,7 @@
         <v>1</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.88</v>
@@ -31870,7 +31870,7 @@
         <v>2.7</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR144" t="n">
         <v>1.94</v>
@@ -33211,10 +33211,10 @@
         <v>5</v>
       </c>
       <c r="BB150" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC150" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD150" t="n">
         <v>3.08</v>
@@ -33908,6 +33908,660 @@
       </c>
       <c r="BP153" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>7818965</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>45885.54166666666</v>
+      </c>
+      <c r="F154" t="n">
+        <v>20</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1</v>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>1</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>3</v>
+      </c>
+      <c r="R154" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S154" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T154" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U154" t="n">
+        <v>3</v>
+      </c>
+      <c r="V154" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X154" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>7818959</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>45885.66666666666</v>
+      </c>
+      <c r="F155" t="n">
+        <v>20</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" t="n">
+        <v>3</v>
+      </c>
+      <c r="K155" t="n">
+        <v>4</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="n">
+        <v>4</v>
+      </c>
+      <c r="N155" t="n">
+        <v>5</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>['1', '12', '33', '46']</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R155" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S155" t="n">
+        <v>5</v>
+      </c>
+      <c r="T155" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U155" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V155" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W155" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X155" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP155" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>7818964</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>45885.8125</v>
+      </c>
+      <c r="F156" t="n">
+        <v>20</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>1</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R156" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S156" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U156" t="n">
+        <v>3</v>
+      </c>
+      <c r="V156" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W156" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X156" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>1.63</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP156"/>
+  <dimension ref="A1:BP157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.38</v>
@@ -2222,7 +2222,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.8</v>
@@ -5056,7 +5056,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR21" t="n">
         <v>1.78</v>
@@ -10506,7 +10506,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR46" t="n">
         <v>2.07</v>
@@ -12465,7 +12465,7 @@
         <v>0.33</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.45</v>
@@ -13994,7 +13994,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR62" t="n">
         <v>1.5</v>
@@ -16389,7 +16389,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.09</v>
@@ -17700,7 +17700,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR79" t="n">
         <v>1.6</v>
@@ -18351,7 +18351,7 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.6</v>
@@ -21403,7 +21403,7 @@
         <v>1.33</v>
       </c>
       <c r="AP96" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.2</v>
@@ -21624,7 +21624,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR97" t="n">
         <v>1.68</v>
@@ -24022,7 +24022,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR108" t="n">
         <v>1.65</v>
@@ -25109,7 +25109,7 @@
         <v>0.29</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.27</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.9</v>
@@ -29908,7 +29908,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR135" t="n">
         <v>1.49</v>
@@ -31867,7 +31867,7 @@
         <v>1.38</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.4</v>
@@ -32521,7 +32521,7 @@
         <v>0.38</v>
       </c>
       <c r="AP147" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.33</v>
@@ -33396,7 +33396,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR151" t="n">
         <v>1.38</v>
@@ -34562,6 +34562,224 @@
       </c>
       <c r="BP156" t="n">
         <v>1.63</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>7818842</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>45886.5625</v>
+      </c>
+      <c r="F157" t="n">
+        <v>20</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" t="n">
+        <v>3</v>
+      </c>
+      <c r="N157" t="n">
+        <v>4</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>['60', '62', '90+6']</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R157" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S157" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U157" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V157" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W157" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X157" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP157"/>
+  <dimension ref="A1:BP159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2004,7 +2004,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.09</v>
@@ -3312,7 +3312,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.9</v>
@@ -6800,7 +6800,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR29" t="n">
         <v>1.6</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.4</v>
@@ -7454,7 +7454,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR32" t="n">
         <v>1.58</v>
@@ -10070,7 +10070,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR44" t="n">
         <v>2.35</v>
@@ -10285,7 +10285,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.45</v>
@@ -10503,7 +10503,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.3</v>
@@ -10939,7 +10939,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.6</v>
@@ -11596,7 +11596,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR51" t="n">
         <v>1.38</v>
@@ -12901,7 +12901,7 @@
         <v>0.33</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.4</v>
@@ -13122,7 +13122,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR58" t="n">
         <v>1.28</v>
@@ -14430,7 +14430,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR64" t="n">
         <v>1.5</v>
@@ -14648,7 +14648,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR65" t="n">
         <v>1.58</v>
@@ -15517,7 +15517,7 @@
         <v>0.75</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.33</v>
@@ -16607,7 +16607,7 @@
         <v>1.25</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.2</v>
@@ -18572,7 +18572,7 @@
         <v>1</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR83" t="n">
         <v>1.52</v>
@@ -19877,7 +19877,7 @@
         <v>2.17</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.6</v>
@@ -20967,7 +20967,7 @@
         <v>0.8</v>
       </c>
       <c r="AP94" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.38</v>
@@ -22496,7 +22496,7 @@
         <v>1</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR101" t="n">
         <v>1.43</v>
@@ -23801,7 +23801,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.22</v>
@@ -24240,7 +24240,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR109" t="n">
         <v>1.47</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.6</v>
@@ -25548,7 +25548,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR115" t="n">
         <v>1.55</v>
@@ -27074,7 +27074,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR122" t="n">
         <v>1.59</v>
@@ -27725,7 +27725,7 @@
         <v>0.25</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.27</v>
@@ -28379,7 +28379,7 @@
         <v>1.38</v>
       </c>
       <c r="AP128" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.2</v>
@@ -30777,10 +30777,10 @@
         <v>0.5</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR139" t="n">
         <v>1.57</v>
@@ -31652,7 +31652,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR143" t="n">
         <v>1.61</v>
@@ -32303,7 +32303,7 @@
         <v>0.89</v>
       </c>
       <c r="AP146" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.8</v>
@@ -34780,6 +34780,442 @@
       </c>
       <c r="BP157" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>7818966</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>45886.66666666666</v>
+      </c>
+      <c r="F158" t="n">
+        <v>20</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>1</v>
+      </c>
+      <c r="L158" t="n">
+        <v>4</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>4</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>['45+3', '52', '80', '86']</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R158" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S158" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T158" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U158" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V158" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W158" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X158" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK158" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO158" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP158" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>7818960</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>45886.77083333334</v>
+      </c>
+      <c r="F159" t="n">
+        <v>20</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>3</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>['50', '68']</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R159" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S159" t="n">
+        <v>5</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U159" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V159" t="n">
+        <v>3</v>
+      </c>
+      <c r="W159" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X159" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -34716,13 +34716,13 @@
         <v>3.15</v>
       </c>
       <c r="AU157" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV157" t="n">
         <v>7</v>
       </c>
       <c r="AW157" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX157" t="n">
         <v>6</v>
@@ -35152,13 +35152,13 @@
         <v>2.9</v>
       </c>
       <c r="AU159" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV159" t="n">
         <v>2</v>
       </c>
       <c r="AW159" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX159" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -34716,13 +34716,13 @@
         <v>3.15</v>
       </c>
       <c r="AU157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV157" t="n">
         <v>7</v>
       </c>
       <c r="AW157" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX157" t="n">
         <v>6</v>
@@ -35152,13 +35152,13 @@
         <v>2.9</v>
       </c>
       <c r="AU159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV159" t="n">
         <v>2</v>
       </c>
       <c r="AW159" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX159" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -19238,22 +19238,22 @@
         <v>2.99</v>
       </c>
       <c r="AU86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV86" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY86" t="n">
         <v>9</v>
       </c>
-      <c r="AW86" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX86" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY86" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ86" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BA86" t="n">
         <v>3</v>
@@ -19456,19 +19456,19 @@
         <v>2.97</v>
       </c>
       <c r="AU87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV87" t="n">
         <v>5</v>
       </c>
-      <c r="AV87" t="n">
+      <c r="AW87" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX87" t="n">
         <v>4</v>
       </c>
-      <c r="AW87" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX87" t="n">
-        <v>5</v>
-      </c>
       <c r="AY87" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ87" t="n">
         <v>9</v>
@@ -19677,19 +19677,19 @@
         <v>9</v>
       </c>
       <c r="AV88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW88" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AX88" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY88" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ88" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA88" t="n">
         <v>5</v>
@@ -19892,22 +19892,22 @@
         <v>3.18</v>
       </c>
       <c r="AU89" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV89" t="n">
         <v>3</v>
       </c>
       <c r="AW89" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX89" t="n">
         <v>5</v>
       </c>
-      <c r="AX89" t="n">
-        <v>7</v>
-      </c>
       <c r="AY89" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ89" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA89" t="n">
         <v>7</v>
@@ -20113,19 +20113,19 @@
         <v>3</v>
       </c>
       <c r="AV90" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW90" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AX90" t="n">
         <v>4</v>
       </c>
       <c r="AY90" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ90" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA90" t="n">
         <v>6</v>
@@ -20328,22 +20328,22 @@
         <v>2.69</v>
       </c>
       <c r="AU91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV91" t="n">
         <v>7</v>
       </c>
       <c r="AW91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AX91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY91" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA91" t="n">
         <v>11</v>
@@ -20546,22 +20546,22 @@
         <v>2.58</v>
       </c>
       <c r="AU92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV92" t="n">
         <v>6</v>
       </c>
       <c r="AW92" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AX92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY92" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ92" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA92" t="n">
         <v>5</v>
@@ -20764,31 +20764,31 @@
         <v>2.8</v>
       </c>
       <c r="AU93" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW93" t="n">
         <v>11</v>
       </c>
       <c r="AX93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY93" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ93" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA93" t="n">
         <v>7</v>
       </c>
       <c r="BB93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC93" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD93" t="n">
         <v>1.72</v>
@@ -21412,10 +21412,10 @@
         <v>2</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="AU96" t="n">
         <v>7</v>
@@ -21627,13 +21627,13 @@
         <v>1.3</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AS97" t="n">
         <v>1.08</v>
       </c>
       <c r="AT97" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AU97" t="n">
         <v>3</v>
@@ -22508,16 +22508,16 @@
         <v>2.96</v>
       </c>
       <c r="AU101" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW101" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX101" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY101" t="n">
         <v>20</v>
@@ -22717,25 +22717,25 @@
         <v>0.9</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AT102" t="n">
-        <v>3.32</v>
+        <v>2.95</v>
       </c>
       <c r="AU102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY102" t="n">
         <v>11</v>
@@ -22935,22 +22935,22 @@
         <v>0.8</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AT103" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AU103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV103" t="n">
         <v>2</v>
       </c>
       <c r="AW103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX103" t="n">
         <v>8</v>
@@ -23153,25 +23153,25 @@
         <v>0.45</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AU104" t="n">
         <v>6</v>
       </c>
       <c r="AV104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW104" t="n">
         <v>8</v>
       </c>
       <c r="AX104" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY104" t="n">
         <v>14</v>
@@ -23371,22 +23371,22 @@
         <v>0.6</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AT105" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="AU105" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV105" t="n">
         <v>3</v>
       </c>
       <c r="AW105" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AX105" t="n">
         <v>5</v>
@@ -23592,19 +23592,19 @@
         <v>1.74</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AT106" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AU106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV106" t="n">
         <v>1</v>
       </c>
       <c r="AW106" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX106" t="n">
         <v>6</v>
@@ -23807,25 +23807,25 @@
         <v>1.22</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AT107" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="AU107" t="n">
         <v>2</v>
       </c>
       <c r="AV107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW107" t="n">
         <v>1</v>
       </c>
       <c r="AX107" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY107" t="n">
         <v>3</v>
@@ -23837,10 +23837,10 @@
         <v>1</v>
       </c>
       <c r="BB107" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC107" t="n">
         <v>5</v>
-      </c>
-      <c r="BC107" t="n">
-        <v>6</v>
       </c>
       <c r="BD107" t="n">
         <v>1.97</v>
@@ -24025,40 +24025,40 @@
         <v>1.3</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AS108" t="n">
         <v>1.08</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="AU108" t="n">
         <v>3</v>
       </c>
       <c r="AV108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW108" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AX108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY108" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ108" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA108" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC108" t="n">
         <v>8</v>
-      </c>
-      <c r="BB108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC108" t="n">
-        <v>9</v>
       </c>
       <c r="BD108" t="n">
         <v>1.64</v>
@@ -24243,22 +24243,22 @@
         <v>0.78</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AS109" t="n">
         <v>1.34</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AU109" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV109" t="n">
         <v>5</v>
       </c>
       <c r="AW109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX109" t="n">
         <v>5</v>
@@ -24461,25 +24461,25 @@
         <v>1.4</v>
       </c>
       <c r="AR110" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AT110" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="AU110" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX110" t="n">
         <v>6</v>
-      </c>
-      <c r="AV110" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW110" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX110" t="n">
-        <v>5</v>
       </c>
       <c r="AY110" t="n">
         <v>19</v>
@@ -24679,22 +24679,22 @@
         <v>1.09</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AU111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV111" t="n">
         <v>5</v>
       </c>
       <c r="AW111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX111" t="n">
         <v>7</v>
@@ -24897,13 +24897,13 @@
         <v>2.3</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AU112" t="n">
         <v>1</v>
@@ -25115,25 +25115,25 @@
         <v>0.27</v>
       </c>
       <c r="AR113" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AT113" t="n">
-        <v>3.17</v>
+        <v>3.24</v>
       </c>
       <c r="AU113" t="n">
         <v>9</v>
       </c>
       <c r="AV113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW113" t="n">
         <v>13</v>
       </c>
       <c r="AX113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY113" t="n">
         <v>22</v>
@@ -25333,22 +25333,22 @@
         <v>1.6</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="AU114" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV114" t="n">
         <v>4</v>
       </c>
       <c r="AW114" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX114" t="n">
         <v>7</v>
@@ -25551,25 +25551,25 @@
         <v>0.4</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AT115" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="AU115" t="n">
         <v>5</v>
       </c>
       <c r="AV115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW115" t="n">
         <v>12</v>
       </c>
       <c r="AX115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY115" t="n">
         <v>17</v>
@@ -25772,22 +25772,22 @@
         <v>1.66</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AT116" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="AU116" t="n">
         <v>4</v>
       </c>
       <c r="AV116" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW116" t="n">
         <v>8</v>
       </c>
       <c r="AX116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY116" t="n">
         <v>12</v>
@@ -25987,25 +25987,25 @@
         <v>1.38</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="AU117" t="n">
         <v>5</v>
       </c>
       <c r="AV117" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW117" t="n">
         <v>8</v>
       </c>
       <c r="AX117" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY117" t="n">
         <v>13</v>
@@ -26017,10 +26017,10 @@
         <v>3</v>
       </c>
       <c r="BB117" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC117" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD117" t="n">
         <v>1.75</v>
@@ -26205,25 +26205,25 @@
         <v>1.2</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AT118" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AU118" t="n">
         <v>2</v>
       </c>
       <c r="AV118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW118" t="n">
         <v>9</v>
       </c>
       <c r="AX118" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY118" t="n">
         <v>11</v>
@@ -26423,25 +26423,25 @@
         <v>1.22</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AU119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV119" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW119" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX119" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY119" t="n">
         <v>9</v>
@@ -26641,25 +26641,25 @@
         <v>0.9</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AT120" t="n">
-        <v>3.57</v>
+        <v>3.23</v>
       </c>
       <c r="AU120" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY120" t="n">
         <v>9</v>
@@ -26859,13 +26859,13 @@
         <v>0.9</v>
       </c>
       <c r="AR121" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="AT121" t="n">
-        <v>3.76</v>
+        <v>3.56</v>
       </c>
       <c r="AU121" t="n">
         <v>4</v>
@@ -27077,22 +27077,22 @@
         <v>0.4</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AS122" t="n">
         <v>1.48</v>
       </c>
       <c r="AT122" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="AU122" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV122" t="n">
         <v>0</v>
       </c>
       <c r="AW122" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX122" t="n">
         <v>7</v>
@@ -27295,13 +27295,13 @@
         <v>0.8</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AU123" t="n">
         <v>4</v>
@@ -27513,25 +27513,25 @@
         <v>0.45</v>
       </c>
       <c r="AR124" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AT124" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="AU124" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV124" t="n">
         <v>6</v>
       </c>
-      <c r="AV124" t="n">
-        <v>7</v>
-      </c>
       <c r="AW124" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY124" t="n">
         <v>18</v>
@@ -27731,25 +27731,25 @@
         <v>0.27</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AU125" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW125" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY125" t="n">
         <v>15</v>
@@ -27952,19 +27952,19 @@
         <v>1.62</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AT126" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="AU126" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV126" t="n">
         <v>3</v>
       </c>
       <c r="AW126" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX126" t="n">
         <v>10</v>
@@ -28167,22 +28167,22 @@
         <v>1.22</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AT127" t="n">
-        <v>3.26</v>
+        <v>3.13</v>
       </c>
       <c r="AU127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV127" t="n">
         <v>5</v>
       </c>
       <c r="AW127" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX127" t="n">
         <v>6</v>
@@ -28385,25 +28385,25 @@
         <v>1.2</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AT128" t="n">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="AU128" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW128" t="n">
         <v>6</v>
       </c>
-      <c r="AV128" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW128" t="n">
-        <v>8</v>
-      </c>
       <c r="AX128" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY128" t="n">
         <v>14</v>
@@ -28412,13 +28412,13 @@
         <v>18</v>
       </c>
       <c r="BA128" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB128" t="n">
         <v>4</v>
       </c>
       <c r="BC128" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD128" t="n">
         <v>1.91</v>
@@ -28603,25 +28603,25 @@
         <v>1.38</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="AU129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW129" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX129" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY129" t="n">
         <v>15</v>
@@ -28821,22 +28821,22 @@
         <v>1.4</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AS130" t="n">
         <v>1.32</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="AU130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV130" t="n">
         <v>5</v>
       </c>
       <c r="AW130" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX130" t="n">
         <v>8</v>
@@ -29039,13 +29039,13 @@
         <v>0.6</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AU131" t="n">
         <v>7</v>
@@ -29257,22 +29257,22 @@
         <v>0.9</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AT132" t="n">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="AU132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV132" t="n">
         <v>1</v>
       </c>
       <c r="AW132" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX132" t="n">
         <v>0</v>
@@ -29475,25 +29475,25 @@
         <v>2.3</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AT133" t="n">
-        <v>3.01</v>
+        <v>2.96</v>
       </c>
       <c r="AU133" t="n">
         <v>0</v>
       </c>
       <c r="AV133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW133" t="n">
         <v>4</v>
       </c>
       <c r="AX133" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY133" t="n">
         <v>4</v>
@@ -29693,25 +29693,25 @@
         <v>0.33</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AT134" t="n">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="AU134" t="n">
         <v>6</v>
       </c>
       <c r="AV134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW134" t="n">
         <v>9</v>
       </c>
       <c r="AX134" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY134" t="n">
         <v>15</v>
@@ -29911,25 +29911,25 @@
         <v>1.3</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="AU135" t="n">
         <v>3</v>
       </c>
       <c r="AV135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW135" t="n">
         <v>10</v>
       </c>
       <c r="AX135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY135" t="n">
         <v>13</v>
@@ -30129,25 +30129,25 @@
         <v>1.22</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AU136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV136" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY136" t="n">
         <v>3</v>
@@ -30347,13 +30347,13 @@
         <v>1.6</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AT137" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="AU137" t="n">
         <v>3</v>
@@ -30383,43 +30383,43 @@
         <v>12</v>
       </c>
       <c r="BD137" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BE137" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="BF137" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BG137" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BH137" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BI137" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BJ137" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BK137" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BL137" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BM137" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BN137" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BO137" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BP137" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="138">
@@ -30568,22 +30568,22 @@
         <v>1.38</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="AU138" t="n">
         <v>6</v>
       </c>
       <c r="AV138" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW138" t="n">
         <v>19</v>
       </c>
       <c r="AX138" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY138" t="n">
         <v>25</v>
@@ -30601,43 +30601,43 @@
         <v>13</v>
       </c>
       <c r="BD138" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BE138" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF138" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="BG138" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BH138" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BI138" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BJ138" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="BK138" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BL138" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BM138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BN138" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BO138" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BP138" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="139">
@@ -30783,25 +30783,25 @@
         <v>0.4</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AS139" t="n">
         <v>1.37</v>
       </c>
       <c r="AT139" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AU139" t="n">
         <v>3</v>
       </c>
       <c r="AV139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW139" t="n">
         <v>10</v>
       </c>
       <c r="AX139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY139" t="n">
         <v>13</v>
@@ -30819,43 +30819,43 @@
         <v>8</v>
       </c>
       <c r="BD139" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BE139" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BF139" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="BG139" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BH139" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BI139" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BJ139" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="BK139" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BL139" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BM139" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BN139" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BO139" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BP139" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="140">
@@ -31001,25 +31001,25 @@
         <v>1.09</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AT140" t="n">
         <v>2.63</v>
       </c>
       <c r="AU140" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV140" t="n">
         <v>4</v>
       </c>
-      <c r="AV140" t="n">
-        <v>3</v>
-      </c>
       <c r="AW140" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX140" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY140" t="n">
         <v>14</v>
@@ -31037,43 +31037,43 @@
         <v>9</v>
       </c>
       <c r="BD140" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BE140" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="BF140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG140" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BH140" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BI140" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BJ140" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BK140" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BL140" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BM140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BN140" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BO140" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="BP140" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="141">
@@ -31219,22 +31219,22 @@
         <v>0.8</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AS141" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AU141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV141" t="n">
         <v>1</v>
       </c>
       <c r="AW141" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX141" t="n">
         <v>6</v>
@@ -31437,25 +31437,25 @@
         <v>0.6</v>
       </c>
       <c r="AR142" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AT142" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AU142" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV142" t="n">
         <v>5</v>
       </c>
-      <c r="AV142" t="n">
-        <v>6</v>
-      </c>
       <c r="AW142" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AX142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY142" t="n">
         <v>23</v>
@@ -31655,22 +31655,22 @@
         <v>0.78</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AS143" t="n">
         <v>1.32</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="AU143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV143" t="n">
         <v>4</v>
       </c>
       <c r="AW143" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX143" t="n">
         <v>10</v>
@@ -31873,22 +31873,22 @@
         <v>1.4</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AS144" t="n">
         <v>1.33</v>
       </c>
       <c r="AT144" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="AU144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV144" t="n">
         <v>4</v>
       </c>
       <c r="AW144" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX144" t="n">
         <v>3</v>
@@ -32091,13 +32091,13 @@
         <v>0.27</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="AU145" t="n">
         <v>7</v>
@@ -32309,22 +32309,22 @@
         <v>0.8</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AS146" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AU146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV146" t="n">
         <v>0</v>
       </c>
       <c r="AW146" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AX146" t="n">
         <v>0</v>
@@ -32530,22 +32530,22 @@
         <v>1.96</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AT147" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="AU147" t="n">
         <v>8</v>
       </c>
       <c r="AV147" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW147" t="n">
         <v>13</v>
       </c>
       <c r="AX147" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY147" t="n">
         <v>21</v>
@@ -32554,13 +32554,13 @@
         <v>9</v>
       </c>
       <c r="BA147" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB147" t="n">
         <v>2</v>
       </c>
       <c r="BC147" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD147" t="n">
         <v>1.28</v>
@@ -32572,10 +32572,10 @@
         <v>4.9</v>
       </c>
       <c r="BG147" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BH147" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="BI147" t="n">
         <v>1.26</v>
@@ -32745,25 +32745,25 @@
         <v>1.2</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AT148" t="n">
-        <v>3.19</v>
+        <v>3.07</v>
       </c>
       <c r="AU148" t="n">
         <v>6</v>
       </c>
       <c r="AV148" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW148" t="n">
         <v>5</v>
       </c>
       <c r="AX148" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY148" t="n">
         <v>11</v>
@@ -32963,22 +32963,22 @@
         <v>0.9</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AT149" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="AU149" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV149" t="n">
         <v>2</v>
       </c>
       <c r="AW149" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX149" t="n">
         <v>4</v>
@@ -33181,25 +33181,25 @@
         <v>2.3</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AT150" t="n">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="AU150" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV150" t="n">
         <v>7</v>
       </c>
-      <c r="AV150" t="n">
-        <v>4</v>
-      </c>
       <c r="AW150" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX150" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY150" t="n">
         <v>16</v>
@@ -33399,13 +33399,13 @@
         <v>1.3</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="AU151" t="n">
         <v>6</v>
@@ -33617,25 +33617,25 @@
         <v>0.27</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AT152" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AU152" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV152" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW152" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX152" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY152" t="n">
         <v>19</v>
@@ -33835,22 +33835,22 @@
         <v>0.45</v>
       </c>
       <c r="AR153" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS153" t="n">
         <v>1.16</v>
       </c>
-      <c r="AS153" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AT153" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AU153" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV153" t="n">
         <v>5</v>
       </c>
       <c r="AW153" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX153" t="n">
         <v>12</v>
@@ -34053,25 +34053,25 @@
         <v>1.6</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AT154" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="AU154" t="n">
         <v>6</v>
       </c>
       <c r="AV154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW154" t="n">
         <v>3</v>
       </c>
       <c r="AX154" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY154" t="n">
         <v>9</v>
@@ -34271,22 +34271,22 @@
         <v>1.09</v>
       </c>
       <c r="AR155" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AT155" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AU155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV155" t="n">
         <v>6</v>
       </c>
       <c r="AW155" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX155" t="n">
         <v>3</v>
@@ -34489,25 +34489,25 @@
         <v>1.4</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AS156" t="n">
         <v>1.28</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="AU156" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV156" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW156" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX156" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY156" t="n">
         <v>17</v>
@@ -34710,19 +34710,19 @@
         <v>1.98</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AT157" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="AU157" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV157" t="n">
         <v>7</v>
       </c>
       <c r="AW157" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX157" t="n">
         <v>6</v>
@@ -34925,13 +34925,13 @@
         <v>0.4</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="AU158" t="n">
         <v>6</v>
@@ -35143,22 +35143,22 @@
         <v>0.78</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AS159" t="n">
         <v>1.34</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AU159" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV159" t="n">
         <v>2</v>
       </c>
       <c r="AW159" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX159" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP159"/>
+  <dimension ref="A1:BP160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.4</v>
@@ -1786,7 +1786,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.3</v>
@@ -5492,7 +5492,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR23" t="n">
         <v>1.3</v>
@@ -8541,7 +8541,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.38</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.8</v>
@@ -15299,7 +15299,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.22</v>
@@ -15738,7 +15738,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR70" t="n">
         <v>1.42</v>
@@ -21839,7 +21839,7 @@
         <v>0.83</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.09</v>
@@ -22060,7 +22060,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR99" t="n">
         <v>1.34</v>
@@ -22714,7 +22714,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR102" t="n">
         <v>1.51</v>
@@ -23147,7 +23147,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.45</v>
@@ -25766,7 +25766,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR116" t="n">
         <v>1.66</v>
@@ -26638,7 +26638,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR120" t="n">
         <v>1.56</v>
@@ -26856,7 +26856,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR121" t="n">
         <v>2.05</v>
@@ -29254,7 +29254,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR132" t="n">
         <v>1.73</v>
@@ -29687,7 +29687,7 @@
         <v>0.43</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.33</v>
@@ -32085,7 +32085,7 @@
         <v>0.22</v>
       </c>
       <c r="AP145" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.27</v>
@@ -32960,7 +32960,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR149" t="n">
         <v>1.58</v>
@@ -35216,6 +35216,224 @@
       </c>
       <c r="BP159" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>7818974</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>45891.66666666666</v>
+      </c>
+      <c r="F160" t="n">
+        <v>21</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2</v>
+      </c>
+      <c r="S160" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V160" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X160" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -35370,13 +35370,13 @@
         <v>2.95</v>
       </c>
       <c r="AU160" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV160" t="n">
         <v>1</v>
       </c>
       <c r="AW160" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX160" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -35370,13 +35370,13 @@
         <v>2.95</v>
       </c>
       <c r="AU160" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV160" t="n">
         <v>1</v>
       </c>
       <c r="AW160" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX160" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP160"/>
+  <dimension ref="A1:BP161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.78</v>
@@ -4184,7 +4184,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>3</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ18" t="n">
         <v>2.3</v>
@@ -5928,7 +5928,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR25" t="n">
         <v>1.2</v>
@@ -7887,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.6</v>
@@ -8762,7 +8762,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR38" t="n">
         <v>1.87</v>
@@ -11378,7 +11378,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR50" t="n">
         <v>1.4</v>
@@ -12247,7 +12247,7 @@
         <v>0.33</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.27</v>
@@ -15735,7 +15735,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.91</v>
@@ -16610,7 +16610,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR74" t="n">
         <v>1.8</v>
@@ -18133,7 +18133,7 @@
         <v>2</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.6</v>
@@ -19223,7 +19223,7 @@
         <v>1</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.22</v>
@@ -20098,7 +20098,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR90" t="n">
         <v>1.67</v>
@@ -21406,7 +21406,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR96" t="n">
         <v>2</v>
@@ -22929,7 +22929,7 @@
         <v>0.83</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.8</v>
@@ -26202,7 +26202,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR118" t="n">
         <v>1.6</v>
@@ -28382,7 +28382,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR128" t="n">
         <v>1.34</v>
@@ -28597,7 +28597,7 @@
         <v>1.14</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.38</v>
@@ -32742,7 +32742,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AR148" t="n">
         <v>1.58</v>
@@ -33393,7 +33393,7 @@
         <v>1.25</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.3</v>
@@ -35434,6 +35434,224 @@
       </c>
       <c r="BP160" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>7818972</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>45891.89583333334</v>
+      </c>
+      <c r="F161" t="n">
+        <v>21</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L161" t="n">
+        <v>2</v>
+      </c>
+      <c r="M161" t="n">
+        <v>2</v>
+      </c>
+      <c r="N161" t="n">
+        <v>4</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>['36', '90+6']</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>['87', '90+3']</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R161" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S161" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U161" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V161" t="n">
+        <v>3</v>
+      </c>
+      <c r="W161" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X161" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP161"/>
+  <dimension ref="A1:BP164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.3</v>
@@ -2440,7 +2440,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.27</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.45</v>
@@ -3966,7 +3966,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR16" t="n">
         <v>3.3</v>
@@ -4402,7 +4402,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR18" t="n">
         <v>1.71</v>
@@ -4620,7 +4620,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR19" t="n">
         <v>0.91</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.27</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.22</v>
@@ -6797,7 +6797,7 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.4</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.22</v>
@@ -8108,7 +8108,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ35" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR35" t="n">
         <v>2.16</v>
@@ -8326,7 +8326,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR36" t="n">
         <v>1.41</v>
@@ -8759,7 +8759,7 @@
         <v>2</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.18</v>
@@ -8980,7 +8980,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR39" t="n">
         <v>1.51</v>
@@ -11157,7 +11157,7 @@
         <v>1.33</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.09</v>
@@ -11375,7 +11375,7 @@
         <v>1.67</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.18</v>
@@ -11814,7 +11814,7 @@
         <v>2</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR52" t="n">
         <v>1.64</v>
@@ -12683,10 +12683,10 @@
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR56" t="n">
         <v>1.47</v>
@@ -13119,7 +13119,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.4</v>
@@ -13340,7 +13340,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR59" t="n">
         <v>1.79</v>
@@ -13776,7 +13776,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR61" t="n">
         <v>1.76</v>
@@ -14427,7 +14427,7 @@
         <v>0.25</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.78</v>
@@ -14645,7 +14645,7 @@
         <v>0.25</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.4</v>
@@ -14866,7 +14866,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ66" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR66" t="n">
         <v>2.05</v>
@@ -15520,7 +15520,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR69" t="n">
         <v>1.32</v>
@@ -17043,7 +17043,7 @@
         <v>0.2</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.45</v>
@@ -17264,7 +17264,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR77" t="n">
         <v>1.61</v>
@@ -17482,7 +17482,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ78" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR78" t="n">
         <v>1.38</v>
@@ -17697,7 +17697,7 @@
         <v>0.75</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.3</v>
@@ -19662,7 +19662,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR88" t="n">
         <v>1.94</v>
@@ -20313,7 +20313,7 @@
         <v>0.17</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.45</v>
@@ -20534,7 +20534,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR92" t="n">
         <v>1.54</v>
@@ -20749,7 +20749,7 @@
         <v>0.83</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.6</v>
@@ -21188,7 +21188,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ95" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR95" t="n">
         <v>1.55</v>
@@ -22275,7 +22275,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.27</v>
@@ -22932,7 +22932,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR103" t="n">
         <v>1.3</v>
@@ -23365,7 +23365,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.6</v>
@@ -23586,7 +23586,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR106" t="n">
         <v>1.74</v>
@@ -24894,7 +24894,7 @@
         <v>1</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR112" t="n">
         <v>1.55</v>
@@ -25763,7 +25763,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.91</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.38</v>
@@ -26635,7 +26635,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.91</v>
@@ -27292,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR123" t="n">
         <v>1.38</v>
@@ -27943,7 +27943,7 @@
         <v>0.88</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.09</v>
@@ -29469,10 +29469,10 @@
         <v>2.13</v>
       </c>
       <c r="AP133" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ133" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR133" t="n">
         <v>1.52</v>
@@ -29690,7 +29690,7 @@
         <v>2</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR134" t="n">
         <v>1.58</v>
@@ -30341,7 +30341,7 @@
         <v>1.88</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.6</v>
@@ -31216,7 +31216,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR141" t="n">
         <v>1.76</v>
@@ -32306,7 +32306,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR146" t="n">
         <v>1.39</v>
@@ -32524,7 +32524,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR147" t="n">
         <v>1.96</v>
@@ -33175,10 +33175,10 @@
         <v>2.22</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ150" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR150" t="n">
         <v>1.66</v>
@@ -35652,6 +35652,660 @@
       </c>
       <c r="BP161" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>7818970</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>45892.66666666666</v>
+      </c>
+      <c r="F162" t="n">
+        <v>21</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R162" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S162" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U162" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V162" t="n">
+        <v>3</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X162" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>7818973</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>45892.77083333334</v>
+      </c>
+      <c r="F163" t="n">
+        <v>21</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>1</v>
+      </c>
+      <c r="N163" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R163" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S163" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T163" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U163" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V163" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W163" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X163" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>7818968</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>45892.875</v>
+      </c>
+      <c r="F164" t="n">
+        <v>21</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>1</v>
+      </c>
+      <c r="L164" t="n">
+        <v>2</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>['31', '90+4']</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S164" t="n">
+        <v>4</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U164" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V164" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X164" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -35997,7 +35997,7 @@
         <v>1.3</v>
       </c>
       <c r="AL163" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AM163" t="n">
         <v>1.38</v>
@@ -36215,7 +36215,7 @@
         <v>1.26</v>
       </c>
       <c r="AL164" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AM164" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP164"/>
+  <dimension ref="A1:BP165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.91</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.3</v>
@@ -6146,7 +6146,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR26" t="n">
         <v>1.26</v>
@@ -7890,7 +7890,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR34" t="n">
         <v>1.39</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.73</v>
@@ -10942,7 +10942,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR48" t="n">
         <v>1.87</v>
@@ -11593,7 +11593,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.78</v>
@@ -16828,7 +16828,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR75" t="n">
         <v>1.64</v>
@@ -18354,7 +18354,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR82" t="n">
         <v>2.05</v>
@@ -19005,7 +19005,7 @@
         <v>0.4</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.27</v>
@@ -20752,7 +20752,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR93" t="n">
         <v>1.6</v>
@@ -21185,7 +21185,7 @@
         <v>1.83</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ95" t="n">
         <v>2.36</v>
@@ -23368,7 +23368,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR105" t="n">
         <v>1.56</v>
@@ -25545,7 +25545,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.4</v>
@@ -28815,7 +28815,7 @@
         <v>1.14</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.4</v>
@@ -29036,7 +29036,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR131" t="n">
         <v>1.53</v>
@@ -31434,7 +31434,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="AR142" t="n">
         <v>2.02</v>
@@ -32739,7 +32739,7 @@
         <v>1.22</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.18</v>
@@ -35806,16 +35806,16 @@
         <v>2.62</v>
       </c>
       <c r="AU162" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW162" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX162" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY162" t="n">
         <v>18</v>
@@ -36024,16 +36024,16 @@
         <v>2.98</v>
       </c>
       <c r="AU163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW163" t="n">
         <v>3</v>
       </c>
-      <c r="AW163" t="n">
-        <v>4</v>
-      </c>
       <c r="AX163" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY163" t="n">
         <v>5</v>
@@ -36245,13 +36245,13 @@
         <v>7</v>
       </c>
       <c r="AV164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW164" t="n">
         <v>11</v>
       </c>
       <c r="AX164" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY164" t="n">
         <v>18</v>
@@ -36306,6 +36306,224 @@
       </c>
       <c r="BP164" t="n">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>7818971</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>45893.5625</v>
+      </c>
+      <c r="F165" t="n">
+        <v>21</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>2</v>
+      </c>
+      <c r="N165" t="n">
+        <v>2</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>['50', '90+7']</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R165" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S165" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U165" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V165" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W165" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X165" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP165" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP165"/>
+  <dimension ref="A1:BP166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>2.36</v>
@@ -1568,7 +1568,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.6</v>
@@ -8544,7 +8544,7 @@
         <v>2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR37" t="n">
         <v>1.65</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.3</v>
@@ -12032,7 +12032,7 @@
         <v>1</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR53" t="n">
         <v>1.34</v>
@@ -16825,7 +16825,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.82</v>
@@ -18790,7 +18790,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR84" t="n">
         <v>1.82</v>
@@ -20531,7 +20531,7 @@
         <v>0.4</v>
       </c>
       <c r="AP92" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.73</v>
@@ -20970,7 +20970,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR94" t="n">
         <v>1.26</v>
@@ -22711,7 +22711,7 @@
         <v>1.5</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.91</v>
@@ -24237,7 +24237,7 @@
         <v>0.67</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.78</v>
@@ -25984,7 +25984,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR117" t="n">
         <v>1.69</v>
@@ -28600,7 +28600,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR129" t="n">
         <v>1.32</v>
@@ -29905,7 +29905,7 @@
         <v>1.43</v>
       </c>
       <c r="AP135" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.3</v>
@@ -30995,7 +30995,7 @@
         <v>0.89</v>
       </c>
       <c r="AP140" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.09</v>
@@ -36524,6 +36524,224 @@
       </c>
       <c r="BP165" t="n">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>7818969</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>45893.77083333334</v>
+      </c>
+      <c r="F166" t="n">
+        <v>21</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1</v>
+      </c>
+      <c r="K166" t="n">
+        <v>1</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>2</v>
+      </c>
+      <c r="N166" t="n">
+        <v>2</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>['36', '56']</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R166" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S166" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T166" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U166" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V166" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W166" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X166" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -35806,16 +35806,16 @@
         <v>2.62</v>
       </c>
       <c r="AU162" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW162" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX162" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY162" t="n">
         <v>18</v>
@@ -36024,16 +36024,16 @@
         <v>2.98</v>
       </c>
       <c r="AU163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW163" t="n">
         <v>4</v>
       </c>
-      <c r="AW163" t="n">
-        <v>3</v>
-      </c>
       <c r="AX163" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY163" t="n">
         <v>5</v>
@@ -36245,13 +36245,13 @@
         <v>7</v>
       </c>
       <c r="AV164" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW164" t="n">
         <v>11</v>
       </c>
       <c r="AX164" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY164" t="n">
         <v>18</v>
@@ -36687,13 +36687,13 @@
         <v>6</v>
       </c>
       <c r="AX166" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY166" t="n">
         <v>10</v>
       </c>
       <c r="AZ166" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA166" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -36460,13 +36460,13 @@
         <v>2.62</v>
       </c>
       <c r="AU165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV165" t="n">
         <v>6</v>
       </c>
       <c r="AW165" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX165" t="n">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP166"/>
+  <dimension ref="A1:BP167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3748,7 +3748,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.56</v>
@@ -7236,7 +7236,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR31" t="n">
         <v>2.25</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ35" t="n">
         <v>2.36</v>
@@ -9413,7 +9413,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.22</v>
@@ -10288,7 +10288,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR45" t="n">
         <v>1.15</v>
@@ -12468,7 +12468,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR55" t="n">
         <v>2.3</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.73</v>
@@ -14212,7 +14212,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR63" t="n">
         <v>1.64</v>
@@ -16171,7 +16171,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.6</v>
@@ -17046,7 +17046,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR76" t="n">
         <v>1.52</v>
@@ -19441,7 +19441,7 @@
         <v>1.4</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.4</v>
@@ -20316,7 +20316,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR91" t="n">
         <v>1.55</v>
@@ -21621,7 +21621,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.3</v>
@@ -23150,7 +23150,7 @@
         <v>2</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR104" t="n">
         <v>1.56</v>
@@ -26199,7 +26199,7 @@
         <v>1.14</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.18</v>
@@ -27071,7 +27071,7 @@
         <v>0.43</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.4</v>
@@ -27510,7 +27510,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR124" t="n">
         <v>2</v>
@@ -29033,7 +29033,7 @@
         <v>0.63</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.82</v>
@@ -30562,7 +30562,7 @@
         <v>1</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR138" t="n">
         <v>1.38</v>
@@ -32957,7 +32957,7 @@
         <v>0.89</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.91</v>
@@ -33832,7 +33832,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR153" t="n">
         <v>1.24</v>
@@ -36742,6 +36742,224 @@
       </c>
       <c r="BP166" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>7818979</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>45897.83333333334</v>
+      </c>
+      <c r="F167" t="n">
+        <v>22</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>2</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>2</v>
+      </c>
+      <c r="L167" t="n">
+        <v>3</v>
+      </c>
+      <c r="M167" t="n">
+        <v>1</v>
+      </c>
+      <c r="N167" t="n">
+        <v>4</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>['13', '27', '71']</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R167" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S167" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T167" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U167" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V167" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="W167" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X167" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN167" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO167" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BP167" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -36896,13 +36896,13 @@
         <v>2.78</v>
       </c>
       <c r="AU167" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV167" t="n">
         <v>3</v>
       </c>
       <c r="AW167" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX167" t="n">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP167"/>
+  <dimension ref="A1:BP168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.3</v>
@@ -2876,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.18</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.82</v>
@@ -6582,7 +6582,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR28" t="n">
         <v>1.14</v>
@@ -9198,7 +9198,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR40" t="n">
         <v>1.98</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.4</v>
@@ -13558,7 +13558,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR60" t="n">
         <v>2.1</v>
@@ -13991,7 +13991,7 @@
         <v>1</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.3</v>
@@ -16174,7 +16174,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR72" t="n">
         <v>1.7</v>
@@ -17479,7 +17479,7 @@
         <v>1.6</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ78" t="n">
         <v>2.36</v>
@@ -18136,7 +18136,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR81" t="n">
         <v>1.38</v>
@@ -19880,7 +19880,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR89" t="n">
         <v>1.73</v>
@@ -22057,7 +22057,7 @@
         <v>1</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.91</v>
@@ -24673,7 +24673,7 @@
         <v>0.86</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.09</v>
@@ -25330,7 +25330,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR114" t="n">
         <v>1.23</v>
@@ -30123,7 +30123,7 @@
         <v>1</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.22</v>
@@ -30344,7 +30344,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR137" t="n">
         <v>1.55</v>
@@ -33829,7 +33829,7 @@
         <v>0.4</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.42</v>
@@ -34050,7 +34050,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AR154" t="n">
         <v>1.47</v>
@@ -36896,13 +36896,13 @@
         <v>2.78</v>
       </c>
       <c r="AU167" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AV167" t="n">
         <v>3</v>
       </c>
       <c r="AW167" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX167" t="n">
         <v>11</v>
@@ -36960,6 +36960,224 @@
       </c>
       <c r="BP167" t="n">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>7818978</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>45898.83333333334</v>
+      </c>
+      <c r="F168" t="n">
+        <v>22</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>1</v>
+      </c>
+      <c r="K168" t="n">
+        <v>1</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>2</v>
+      </c>
+      <c r="N168" t="n">
+        <v>3</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>['21', '89']</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R168" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S168" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U168" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V168" t="n">
+        <v>3</v>
+      </c>
+      <c r="W168" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X168" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -37114,13 +37114,13 @@
         <v>2.7</v>
       </c>
       <c r="AU168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV168" t="n">
         <v>4</v>
       </c>
       <c r="AW168" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX168" t="n">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP168"/>
+  <dimension ref="A1:BP171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.82</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.78</v>
@@ -4402,7 +4402,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR18" t="n">
         <v>1.71</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ20" t="n">
         <v>0.27</v>
@@ -5056,7 +5056,7 @@
         <v>2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR21" t="n">
         <v>1.78</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.91</v>
@@ -7018,7 +7018,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR30" t="n">
         <v>1.71</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.42</v>
@@ -8108,7 +8108,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ35" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR35" t="n">
         <v>2.16</v>
@@ -10067,7 +10067,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.4</v>
@@ -10285,7 +10285,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.42</v>
@@ -10506,7 +10506,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR46" t="n">
         <v>2.07</v>
@@ -10724,7 +10724,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR47" t="n">
         <v>1.59</v>
@@ -12901,10 +12901,10 @@
         <v>0.33</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR57" t="n">
         <v>1.21</v>
@@ -13119,7 +13119,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.4</v>
@@ -13555,7 +13555,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.73</v>
@@ -13776,7 +13776,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR61" t="n">
         <v>1.76</v>
@@ -13994,7 +13994,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR62" t="n">
         <v>1.5</v>
@@ -14427,7 +14427,7 @@
         <v>0.25</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.78</v>
@@ -14866,7 +14866,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ66" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR66" t="n">
         <v>2.05</v>
@@ -15081,7 +15081,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.27</v>
@@ -15517,7 +15517,7 @@
         <v>0.75</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.3</v>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR71" t="n">
         <v>1.35</v>
@@ -17482,7 +17482,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ78" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR78" t="n">
         <v>1.38</v>
@@ -17700,7 +17700,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR79" t="n">
         <v>1.6</v>
@@ -17915,7 +17915,7 @@
         <v>1</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.09</v>
@@ -19444,7 +19444,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR87" t="n">
         <v>1.56</v>
@@ -20313,7 +20313,7 @@
         <v>0.17</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.42</v>
@@ -20967,7 +20967,7 @@
         <v>0.8</v>
       </c>
       <c r="AP94" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.56</v>
@@ -21188,7 +21188,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ95" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR95" t="n">
         <v>1.55</v>
@@ -21624,7 +21624,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR97" t="n">
         <v>1.56</v>
@@ -23365,7 +23365,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.82</v>
@@ -23583,7 +23583,7 @@
         <v>0.5</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.3</v>
@@ -24022,7 +24022,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR108" t="n">
         <v>1.6</v>
@@ -24458,7 +24458,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR110" t="n">
         <v>1.99</v>
@@ -24894,7 +24894,7 @@
         <v>1</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR112" t="n">
         <v>1.55</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.73</v>
@@ -26635,7 +26635,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.91</v>
@@ -28379,7 +28379,7 @@
         <v>1.38</v>
       </c>
       <c r="AP128" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.18</v>
@@ -28818,7 +28818,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR130" t="n">
         <v>1.52</v>
@@ -29251,7 +29251,7 @@
         <v>0.88</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.91</v>
@@ -29469,10 +29469,10 @@
         <v>2.13</v>
       </c>
       <c r="AP133" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ133" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR133" t="n">
         <v>1.52</v>
@@ -29908,7 +29908,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR135" t="n">
         <v>1.44</v>
@@ -31213,7 +31213,7 @@
         <v>1</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.73</v>
@@ -31870,7 +31870,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR144" t="n">
         <v>1.93</v>
@@ -32303,7 +32303,7 @@
         <v>0.89</v>
       </c>
       <c r="AP146" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.73</v>
@@ -33178,7 +33178,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ150" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR150" t="n">
         <v>1.66</v>
@@ -33396,7 +33396,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR151" t="n">
         <v>1.33</v>
@@ -34483,10 +34483,10 @@
         <v>1.56</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR156" t="n">
         <v>1.77</v>
@@ -34704,7 +34704,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR157" t="n">
         <v>1.98</v>
@@ -34919,7 +34919,7 @@
         <v>0.44</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.4</v>
@@ -36012,7 +36012,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ163" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AR163" t="n">
         <v>1.5</v>
@@ -36227,7 +36227,7 @@
         <v>0.33</v>
       </c>
       <c r="AP164" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ164" t="n">
         <v>0.3</v>
@@ -36896,13 +36896,13 @@
         <v>2.78</v>
       </c>
       <c r="AU167" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV167" t="n">
         <v>3</v>
       </c>
       <c r="AW167" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX167" t="n">
         <v>11</v>
@@ -37120,16 +37120,16 @@
         <v>4</v>
       </c>
       <c r="AW168" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX168" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY168" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ168" t="n">
         <v>14</v>
-      </c>
-      <c r="AZ168" t="n">
-        <v>13</v>
       </c>
       <c r="BA168" t="n">
         <v>4</v>
@@ -37178,6 +37178,660 @@
       </c>
       <c r="BP168" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>7818982</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>45899.5625</v>
+      </c>
+      <c r="F169" t="n">
+        <v>22</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1</v>
+      </c>
+      <c r="K169" t="n">
+        <v>1</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>4</v>
+      </c>
+      <c r="R169" t="n">
+        <v>2</v>
+      </c>
+      <c r="S169" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T169" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U169" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V169" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W169" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X169" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>7818980</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>45899.66666666666</v>
+      </c>
+      <c r="F170" t="n">
+        <v>22</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>2</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>2</v>
+      </c>
+      <c r="L170" t="n">
+        <v>3</v>
+      </c>
+      <c r="M170" t="n">
+        <v>2</v>
+      </c>
+      <c r="N170" t="n">
+        <v>5</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>['19', '32', '79']</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>['68', '84']</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R170" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S170" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="T170" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U170" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V170" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X170" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>7818976</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>45899.77083333334</v>
+      </c>
+      <c r="F171" t="n">
+        <v>22</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" t="n">
+        <v>1</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" t="n">
+        <v>3</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>['49', '86']</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R171" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S171" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U171" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V171" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W171" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X171" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -37114,16 +37114,16 @@
         <v>2.7</v>
       </c>
       <c r="AU168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV168" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW168" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX168" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY168" t="n">
         <v>15</v>
@@ -37335,13 +37335,13 @@
         <v>3</v>
       </c>
       <c r="AV169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW169" t="n">
         <v>5</v>
       </c>
       <c r="AX169" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY169" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP171"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
         <v>2.42</v>
@@ -3312,7 +3312,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.73</v>
@@ -6800,7 +6800,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR29" t="n">
         <v>1.6</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.3</v>
@@ -10070,7 +10070,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR44" t="n">
         <v>2.35</v>
@@ -13122,7 +13122,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR58" t="n">
         <v>1.28</v>
@@ -14648,7 +14648,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR65" t="n">
         <v>1.58</v>
@@ -16825,7 +16825,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.82</v>
@@ -20531,7 +20531,7 @@
         <v>0.4</v>
       </c>
       <c r="AP92" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.73</v>
@@ -22496,7 +22496,7 @@
         <v>1</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR101" t="n">
         <v>1.43</v>
@@ -22711,7 +22711,7 @@
         <v>1.5</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.91</v>
@@ -24237,7 +24237,7 @@
         <v>0.67</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.78</v>
@@ -25548,7 +25548,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR115" t="n">
         <v>1.48</v>
@@ -27074,7 +27074,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR122" t="n">
         <v>1.53</v>
@@ -29905,7 +29905,7 @@
         <v>1.43</v>
       </c>
       <c r="AP135" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.18</v>
@@ -30780,7 +30780,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR139" t="n">
         <v>1.52</v>
@@ -30995,7 +30995,7 @@
         <v>0.89</v>
       </c>
       <c r="AP140" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.09</v>
@@ -34922,7 +34922,7 @@
         <v>2</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AR158" t="n">
         <v>1.39</v>
@@ -36663,7 +36663,7 @@
         <v>1.38</v>
       </c>
       <c r="AP166" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.56</v>
@@ -37353,10 +37353,10 @@
         <v>5</v>
       </c>
       <c r="BB169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC169" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD169" t="n">
         <v>2.63</v>
@@ -37832,6 +37832,224 @@
       </c>
       <c r="BP171" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>7818977</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>45899.875</v>
+      </c>
+      <c r="F172" t="n">
+        <v>22</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1</v>
+      </c>
+      <c r="K172" t="n">
+        <v>1</v>
+      </c>
+      <c r="L172" t="n">
+        <v>2</v>
+      </c>
+      <c r="M172" t="n">
+        <v>1</v>
+      </c>
+      <c r="N172" t="n">
+        <v>3</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>['78', '90+5']</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R172" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S172" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T172" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U172" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V172" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W172" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X172" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -37959,7 +37959,7 @@
         <v>1.4</v>
       </c>
       <c r="AL172" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM172" t="n">
         <v>1.57</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.18</v>
@@ -5710,7 +5710,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR24" t="n">
         <v>1.69</v>
@@ -7451,7 +7451,7 @@
         <v>0.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.78</v>
@@ -7672,7 +7672,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR33" t="n">
         <v>1.51</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.73</v>
@@ -9416,7 +9416,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR41" t="n">
         <v>2.04</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ66" t="n">
         <v>2.42</v>
@@ -15302,7 +15302,7 @@
         <v>2</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR68" t="n">
         <v>1.65</v>
@@ -18787,7 +18787,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.56</v>
@@ -19226,7 +19226,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR86" t="n">
         <v>1.38</v>
@@ -19659,7 +19659,7 @@
         <v>0.6</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.3</v>
@@ -23804,7 +23804,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR107" t="n">
         <v>1.63</v>
@@ -24455,7 +24455,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.27</v>
@@ -26420,7 +26420,7 @@
         <v>1</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR119" t="n">
         <v>1.44</v>
@@ -27507,7 +27507,7 @@
         <v>0.5</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.42</v>
@@ -28164,7 +28164,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR127" t="n">
         <v>1.59</v>
@@ -30126,7 +30126,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR136" t="n">
         <v>1.32</v>
@@ -31431,7 +31431,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.82</v>
@@ -34265,7 +34265,7 @@
         <v>0.9</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ155" t="n">
         <v>1.09</v>
@@ -38050,6 +38050,224 @@
       </c>
       <c r="BP172" t="n">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>7818975</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>45900.66666666666</v>
+      </c>
+      <c r="F173" t="n">
+        <v>22</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="n">
+        <v>1</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>3</v>
+      </c>
+      <c r="R173" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S173" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T173" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U173" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V173" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W173" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X173" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM173" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN173" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BO173" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP173" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP173"/>
+  <dimension ref="A1:BP174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,7 +2440,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.36</v>
@@ -4620,7 +4620,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR19" t="n">
         <v>0.91</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.09</v>
@@ -8980,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR39" t="n">
         <v>1.51</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.27</v>
@@ -12686,7 +12686,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR56" t="n">
         <v>1.47</v>
@@ -13773,7 +13773,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ61" t="n">
         <v>2.42</v>
@@ -14209,7 +14209,7 @@
         <v>0.25</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.42</v>
@@ -15520,7 +15520,7 @@
         <v>2</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR69" t="n">
         <v>1.32</v>
@@ -17261,7 +17261,7 @@
         <v>0.25</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.73</v>
@@ -19662,7 +19662,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR88" t="n">
         <v>1.94</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.18</v>
@@ -23586,7 +23586,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR106" t="n">
         <v>1.74</v>
@@ -24019,7 +24019,7 @@
         <v>1.17</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.18</v>
@@ -28161,7 +28161,7 @@
         <v>1</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.1</v>
@@ -29690,7 +29690,7 @@
         <v>2</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR134" t="n">
         <v>1.58</v>
@@ -31649,7 +31649,7 @@
         <v>1</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.78</v>
@@ -32524,7 +32524,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR147" t="n">
         <v>1.96</v>
@@ -34047,7 +34047,7 @@
         <v>1.78</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.73</v>
@@ -36230,7 +36230,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="AR164" t="n">
         <v>1.39</v>
@@ -37335,13 +37335,13 @@
         <v>3</v>
       </c>
       <c r="AV169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW169" t="n">
         <v>5</v>
       </c>
       <c r="AX169" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY169" t="n">
         <v>8</v>
@@ -37353,10 +37353,10 @@
         <v>5</v>
       </c>
       <c r="BB169" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC169" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD169" t="n">
         <v>2.63</v>
@@ -37768,13 +37768,13 @@
         <v>2.71</v>
       </c>
       <c r="AU171" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV171" t="n">
         <v>4</v>
       </c>
       <c r="AW171" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX171" t="n">
         <v>8</v>
@@ -37989,13 +37989,13 @@
         <v>9</v>
       </c>
       <c r="AV172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW172" t="n">
         <v>16</v>
       </c>
       <c r="AX172" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY172" t="n">
         <v>25</v>
@@ -38204,16 +38204,16 @@
         <v>3.67</v>
       </c>
       <c r="AU173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW173" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX173" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY173" t="n">
         <v>21</v>
@@ -38268,6 +38268,224 @@
       </c>
       <c r="BP173" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>7818981</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>45900.8125</v>
+      </c>
+      <c r="F174" t="n">
+        <v>22</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>1</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>2</v>
+      </c>
+      <c r="N174" t="n">
+        <v>3</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>['74', '79']</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="R174" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S174" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T174" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U174" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="V174" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W174" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X174" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO174" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP174" t="n">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -38428,13 +38428,13 @@
         <v>4</v>
       </c>
       <c r="AW174" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX174" t="n">
         <v>16</v>
       </c>
       <c r="AY174" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ174" t="n">
         <v>20</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -37335,13 +37335,13 @@
         <v>3</v>
       </c>
       <c r="AV169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW169" t="n">
         <v>5</v>
       </c>
       <c r="AX169" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY169" t="n">
         <v>8</v>
@@ -37353,10 +37353,10 @@
         <v>5</v>
       </c>
       <c r="BB169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC169" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD169" t="n">
         <v>2.63</v>
@@ -37774,13 +37774,13 @@
         <v>4</v>
       </c>
       <c r="AW171" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX171" t="n">
         <v>8</v>
       </c>
       <c r="AY171" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ171" t="n">
         <v>12</v>
@@ -37989,13 +37989,13 @@
         <v>9</v>
       </c>
       <c r="AV172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW172" t="n">
         <v>16</v>
       </c>
       <c r="AX172" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY172" t="n">
         <v>25</v>
@@ -38204,16 +38204,16 @@
         <v>3.67</v>
       </c>
       <c r="AU173" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW173" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX173" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY173" t="n">
         <v>21</v>
@@ -38422,16 +38422,16 @@
         <v>2.86</v>
       </c>
       <c r="AU174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW174" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX174" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY174" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -38204,16 +38204,16 @@
         <v>3.67</v>
       </c>
       <c r="AU173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW173" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX173" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY173" t="n">
         <v>21</v>
@@ -38422,16 +38422,16 @@
         <v>2.86</v>
       </c>
       <c r="AU174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV174" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW174" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX174" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY174" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -38204,16 +38204,16 @@
         <v>3.67</v>
       </c>
       <c r="AU173" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW173" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX173" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY173" t="n">
         <v>21</v>
@@ -38422,16 +38422,16 @@
         <v>2.86</v>
       </c>
       <c r="AU174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW174" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX174" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY174" t="n">
         <v>12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP174"/>
+  <dimension ref="A1:BP175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2876,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.42</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.1</v>
@@ -6582,7 +6582,7 @@
         <v>1</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR28" t="n">
         <v>1.14</v>
@@ -8759,7 +8759,7 @@
         <v>2</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.18</v>
@@ -9198,7 +9198,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR40" t="n">
         <v>1.98</v>
@@ -11157,7 +11157,7 @@
         <v>1.33</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.09</v>
@@ -13558,7 +13558,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR60" t="n">
         <v>2.1</v>
@@ -14645,7 +14645,7 @@
         <v>0.25</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.36</v>
@@ -16174,7 +16174,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR72" t="n">
         <v>1.7</v>
@@ -17697,7 +17697,7 @@
         <v>0.75</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.18</v>
@@ -18136,7 +18136,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR81" t="n">
         <v>1.38</v>
@@ -19880,7 +19880,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR89" t="n">
         <v>1.73</v>
@@ -22275,7 +22275,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.27</v>
@@ -25330,7 +25330,7 @@
         <v>2</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR114" t="n">
         <v>1.23</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.56</v>
@@ -30344,7 +30344,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR137" t="n">
         <v>1.55</v>
@@ -33175,7 +33175,7 @@
         <v>2.22</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ150" t="n">
         <v>2.42</v>
@@ -34050,7 +34050,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR154" t="n">
         <v>1.47</v>
@@ -35791,7 +35791,7 @@
         <v>0.8</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.73</v>
@@ -37102,7 +37102,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR168" t="n">
         <v>1.28</v>
@@ -38486,6 +38486,224 @@
       </c>
       <c r="BP174" t="n">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>7818928</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>45907.625</v>
+      </c>
+      <c r="F175" t="n">
+        <v>16</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>1</v>
+      </c>
+      <c r="L175" t="n">
+        <v>2</v>
+      </c>
+      <c r="M175" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>3</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>['45', '79']</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>['90+7']</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="R175" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S175" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T175" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U175" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V175" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W175" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X175" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -38640,13 +38640,13 @@
         <v>3.13</v>
       </c>
       <c r="AU175" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV175" t="n">
         <v>2</v>
       </c>
       <c r="AW175" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX175" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP175"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.27</v>
@@ -1350,7 +1350,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.55</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.58</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.42</v>
@@ -4184,7 +4184,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>3</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ18" t="n">
         <v>2.42</v>
@@ -5053,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR21" t="n">
         <v>1.78</v>
@@ -5274,7 +5274,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.1</v>
@@ -5925,10 +5925,10 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR25" t="n">
         <v>1.2</v>
@@ -6143,10 +6143,10 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR26" t="n">
         <v>1.26</v>
@@ -6364,7 +6364,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR27" t="n">
         <v>2.05</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.27</v>
@@ -7454,7 +7454,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR32" t="n">
         <v>1.58</v>
@@ -7887,10 +7887,10 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR34" t="n">
         <v>1.39</v>
@@ -8541,10 +8541,10 @@
         <v>1.5</v>
       </c>
       <c r="AP37" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR37" t="n">
         <v>1.65</v>
@@ -8759,10 +8759,10 @@
         <v>2</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR38" t="n">
         <v>1.87</v>
@@ -9631,10 +9631,10 @@
         <v>0.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR42" t="n">
         <v>1.19</v>
@@ -10503,10 +10503,10 @@
         <v>1.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR46" t="n">
         <v>2.07</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.27</v>
@@ -10939,10 +10939,10 @@
         <v>1.33</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR48" t="n">
         <v>1.87</v>
@@ -11157,10 +11157,10 @@
         <v>1.33</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR49" t="n">
         <v>1.64</v>
@@ -11378,7 +11378,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR50" t="n">
         <v>1.4</v>
@@ -11596,7 +11596,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR51" t="n">
         <v>1.38</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.73</v>
@@ -12029,10 +12029,10 @@
         <v>1</v>
       </c>
       <c r="AP53" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR53" t="n">
         <v>1.34</v>
@@ -12247,7 +12247,7 @@
         <v>0.33</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.27</v>
@@ -13991,10 +13991,10 @@
         <v>1</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR62" t="n">
         <v>1.5</v>
@@ -14430,7 +14430,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR64" t="n">
         <v>1.5</v>
@@ -14645,7 +14645,7 @@
         <v>0.25</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.36</v>
@@ -15299,7 +15299,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.1</v>
@@ -15735,7 +15735,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.91</v>
@@ -15953,7 +15953,7 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.27</v>
@@ -16392,7 +16392,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR73" t="n">
         <v>2.22</v>
@@ -16607,10 +16607,10 @@
         <v>1.25</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR74" t="n">
         <v>1.8</v>
@@ -16828,7 +16828,7 @@
         <v>1</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR75" t="n">
         <v>1.64</v>
@@ -17479,7 +17479,7 @@
         <v>1.6</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ78" t="n">
         <v>2.42</v>
@@ -17697,10 +17697,10 @@
         <v>0.75</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR79" t="n">
         <v>1.6</v>
@@ -17918,7 +17918,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR80" t="n">
         <v>1.91</v>
@@ -18133,7 +18133,7 @@
         <v>2</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.58</v>
@@ -18354,7 +18354,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR82" t="n">
         <v>2.05</v>
@@ -18569,10 +18569,10 @@
         <v>0.2</v>
       </c>
       <c r="AP83" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR83" t="n">
         <v>1.52</v>
@@ -18790,7 +18790,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR84" t="n">
         <v>1.82</v>
@@ -19223,7 +19223,7 @@
         <v>1</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.1</v>
@@ -19877,7 +19877,7 @@
         <v>2.17</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.58</v>
@@ -20098,7 +20098,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR90" t="n">
         <v>1.67</v>
@@ -20752,7 +20752,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR93" t="n">
         <v>1.6</v>
@@ -20970,7 +20970,7 @@
         <v>2</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR94" t="n">
         <v>1.26</v>
@@ -21406,7 +21406,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR96" t="n">
         <v>2</v>
@@ -21624,7 +21624,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR97" t="n">
         <v>1.56</v>
@@ -21839,10 +21839,10 @@
         <v>0.83</v>
       </c>
       <c r="AP98" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR98" t="n">
         <v>1.67</v>
@@ -22057,7 +22057,7 @@
         <v>1</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.91</v>
@@ -22275,7 +22275,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.27</v>
@@ -22493,7 +22493,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ101" t="n">
         <v>0.36</v>
@@ -22929,7 +22929,7 @@
         <v>0.83</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.73</v>
@@ -23147,7 +23147,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.42</v>
@@ -23368,7 +23368,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR105" t="n">
         <v>1.56</v>
@@ -23801,7 +23801,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.1</v>
@@ -24022,7 +24022,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR108" t="n">
         <v>1.6</v>
@@ -24240,7 +24240,7 @@
         <v>1</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR109" t="n">
         <v>1.42</v>
@@ -24673,10 +24673,10 @@
         <v>0.86</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR111" t="n">
         <v>1.4</v>
@@ -24891,7 +24891,7 @@
         <v>2</v>
       </c>
       <c r="AP112" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ112" t="n">
         <v>2.42</v>
@@ -25981,10 +25981,10 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR117" t="n">
         <v>1.69</v>
@@ -26202,7 +26202,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR118" t="n">
         <v>1.6</v>
@@ -26417,7 +26417,7 @@
         <v>0.67</v>
       </c>
       <c r="AP119" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.1</v>
@@ -27289,7 +27289,7 @@
         <v>1.14</v>
       </c>
       <c r="AP123" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.73</v>
@@ -27725,7 +27725,7 @@
         <v>0.25</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.27</v>
@@ -27946,7 +27946,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR126" t="n">
         <v>1.62</v>
@@ -28382,7 +28382,7 @@
         <v>2</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR128" t="n">
         <v>1.34</v>
@@ -28597,10 +28597,10 @@
         <v>1.14</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR129" t="n">
         <v>1.32</v>
@@ -29036,7 +29036,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR131" t="n">
         <v>1.53</v>
@@ -29687,7 +29687,7 @@
         <v>0.43</v>
       </c>
       <c r="AP134" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.55</v>
@@ -29908,7 +29908,7 @@
         <v>1</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR135" t="n">
         <v>1.44</v>
@@ -30123,7 +30123,7 @@
         <v>1</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.1</v>
@@ -30559,7 +30559,7 @@
         <v>0.44</v>
       </c>
       <c r="AP138" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.42</v>
@@ -30777,7 +30777,7 @@
         <v>0.5</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.36</v>
@@ -30998,7 +30998,7 @@
         <v>1</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR140" t="n">
         <v>1.43</v>
@@ -31434,7 +31434,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR142" t="n">
         <v>2.02</v>
@@ -31652,7 +31652,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR143" t="n">
         <v>1.53</v>
@@ -32085,7 +32085,7 @@
         <v>0.22</v>
       </c>
       <c r="AP145" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.27</v>
@@ -32742,7 +32742,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR148" t="n">
         <v>1.58</v>
@@ -33175,7 +33175,7 @@
         <v>2.22</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ150" t="n">
         <v>2.42</v>
@@ -33393,10 +33393,10 @@
         <v>1.25</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR151" t="n">
         <v>1.33</v>
@@ -33611,7 +33611,7 @@
         <v>0.2</v>
       </c>
       <c r="AP152" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.27</v>
@@ -33829,7 +33829,7 @@
         <v>0.4</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.42</v>
@@ -34268,7 +34268,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AR155" t="n">
         <v>2.08</v>
@@ -34704,7 +34704,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR157" t="n">
         <v>1.98</v>
@@ -35137,10 +35137,10 @@
         <v>0.88</v>
       </c>
       <c r="AP159" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR159" t="n">
         <v>1.51</v>
@@ -35355,7 +35355,7 @@
         <v>0.9</v>
       </c>
       <c r="AP160" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.91</v>
@@ -35573,10 +35573,10 @@
         <v>1.2</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR161" t="n">
         <v>1.36</v>
@@ -35791,7 +35791,7 @@
         <v>0.8</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.73</v>
@@ -36448,7 +36448,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR165" t="n">
         <v>1.55</v>
@@ -36666,7 +36666,7 @@
         <v>1</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR166" t="n">
         <v>1.46</v>
@@ -37099,7 +37099,7 @@
         <v>1.6</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.58</v>
@@ -37538,7 +37538,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AR170" t="n">
         <v>1.8</v>
@@ -38625,7 +38625,7 @@
         <v>1.73</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AQ175" t="n">
         <v>1.58</v>
@@ -38704,6 +38704,1314 @@
       </c>
       <c r="BP175" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="n">
+        <v>7818986</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>45912.75</v>
+      </c>
+      <c r="F176" t="n">
+        <v>23</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
+        <v>2</v>
+      </c>
+      <c r="M176" t="n">
+        <v>1</v>
+      </c>
+      <c r="N176" t="n">
+        <v>3</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>['82', '90+3']</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R176" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S176" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="T176" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U176" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V176" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="W176" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X176" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI176" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ176" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK176" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL176" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM176" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN176" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO176" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP176" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="n">
+        <v>7818987</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>45912.85416666666</v>
+      </c>
+      <c r="F177" t="n">
+        <v>23</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>1</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R177" t="n">
+        <v>2</v>
+      </c>
+      <c r="S177" t="n">
+        <v>3</v>
+      </c>
+      <c r="T177" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U177" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V177" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="W177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X177" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI177" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BM177" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BN177" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO177" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BP177" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="n">
+        <v>7818989</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>45913.52083333334</v>
+      </c>
+      <c r="F178" t="n">
+        <v>23</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>2</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>2</v>
+      </c>
+      <c r="L178" t="n">
+        <v>3</v>
+      </c>
+      <c r="M178" t="n">
+        <v>4</v>
+      </c>
+      <c r="N178" t="n">
+        <v>7</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>['25', '30', '70']</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>['47', '54', '87', '90+1']</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R178" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S178" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T178" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U178" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V178" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W178" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X178" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF178" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG178" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH178" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI178" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BM178" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="n">
+        <v>7818990</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>45913.625</v>
+      </c>
+      <c r="F179" t="n">
+        <v>23</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1</v>
+      </c>
+      <c r="K179" t="n">
+        <v>1</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>2</v>
+      </c>
+      <c r="N179" t="n">
+        <v>3</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>['7', '67']</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R179" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S179" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T179" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U179" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V179" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W179" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X179" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH179" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI179" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM179" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="n">
+        <v>7818984</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>45913.72916666666</v>
+      </c>
+      <c r="F180" t="n">
+        <v>23</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" t="n">
+        <v>1</v>
+      </c>
+      <c r="K180" t="n">
+        <v>2</v>
+      </c>
+      <c r="L180" t="n">
+        <v>3</v>
+      </c>
+      <c r="M180" t="n">
+        <v>2</v>
+      </c>
+      <c r="N180" t="n">
+        <v>5</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>['32', '61', '68']</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>['2', '84']</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R180" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S180" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U180" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V180" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W180" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X180" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB180" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH180" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI180" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ180" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BK180" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BL180" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM180" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BN180" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BO180" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BP180" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="n">
+        <v>7818988</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>45913.83333333334</v>
+      </c>
+      <c r="F181" t="n">
+        <v>23</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>1</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R181" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S181" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T181" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U181" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V181" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W181" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X181" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BM181" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN181" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO181" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP181" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -29337,7 +29337,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>8309675</v>
+        <v>8309754</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -29357,197 +29357,197 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '38', '82']</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="R133" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="S133" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="T133" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="U133" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V133" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X133" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH133" t="n">
         <v>3</v>
       </c>
-      <c r="V133" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W133" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X133" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE133" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF133" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AG133" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK133" t="n">
+      <c r="BI133" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BP133" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AL133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM133" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AN133" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO133" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AP133" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AQ133" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AR133" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AS133" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AT133" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AU133" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV133" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW133" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX133" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY133" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ133" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA133" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB133" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC133" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD133" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BE133" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="BF133" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BG133" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BH133" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="BI133" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BJ133" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BK133" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BL133" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BM133" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BN133" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BO133" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BP133" t="n">
-        <v>1.48</v>
       </c>
     </row>
     <row r="134">
@@ -29555,7 +29555,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>8309754</v>
+        <v>8309675</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -29575,197 +29575,197 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R134" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S134" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T134" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U134" t="n">
         <v>3</v>
       </c>
-      <c r="N134" t="n">
-        <v>3</v>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>['32', '38', '82']</t>
-        </is>
-      </c>
-      <c r="Q134" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R134" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S134" t="n">
+      <c r="V134" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W134" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X134" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA134" t="n">
         <v>3.65</v>
       </c>
-      <c r="T134" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U134" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V134" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="W134" t="n">
+      <c r="AB134" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK134" t="n">
         <v>1.25</v>
       </c>
-      <c r="X134" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE134" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF134" t="n">
+      <c r="AL134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO134" t="n">
         <v>2.5</v>
       </c>
-      <c r="AG134" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI134" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ134" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK134" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM134" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN134" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AO134" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AP134" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AQ134" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AR134" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS134" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AT134" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV134" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW134" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX134" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY134" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ134" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA134" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB134" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC134" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD134" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BE134" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="BF134" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BG134" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BH134" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI134" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BJ134" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BK134" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BL134" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BM134" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BN134" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BO134" t="n">
-        <v>3.91</v>
-      </c>
       <c r="BP134" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="135">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP183"/>
+  <dimension ref="A1:BP184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.33</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.25</v>
@@ -5274,7 +5274,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -8762,7 +8762,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR38" t="n">
         <v>1.81</v>
@@ -12032,7 +12032,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR53" t="n">
         <v>1.15</v>
@@ -13119,7 +13119,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.36</v>
@@ -14427,7 +14427,7 @@
         <v>0.25</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.7</v>
@@ -18790,7 +18790,7 @@
         <v>2</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR84" t="n">
         <v>1.8</v>
@@ -20313,7 +20313,7 @@
         <v>0.17</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.42</v>
@@ -20970,7 +20970,7 @@
         <v>2</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR94" t="n">
         <v>1.19</v>
@@ -23365,7 +23365,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.75</v>
@@ -25984,7 +25984,7 @@
         <v>2</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR117" t="n">
         <v>1.61</v>
@@ -26635,7 +26635,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.91</v>
@@ -28600,7 +28600,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR129" t="n">
         <v>1.39</v>
@@ -29469,7 +29469,7 @@
         <v>2.13</v>
       </c>
       <c r="AP133" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ133" t="n">
         <v>2.42</v>
@@ -36227,7 +36227,7 @@
         <v>0.33</v>
       </c>
       <c r="AP164" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ164" t="n">
         <v>0.55</v>
@@ -36666,7 +36666,7 @@
         <v>1</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR166" t="n">
         <v>1.48</v>
@@ -37753,7 +37753,7 @@
         <v>1.4</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.27</v>
@@ -38846,7 +38846,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR176" t="n">
         <v>1.51</v>
@@ -40448,6 +40448,224 @@
       </c>
       <c r="BP183" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="n">
+        <v>8309846</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>45939.85416666666</v>
+      </c>
+      <c r="F184" t="n">
+        <v>19</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>1</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>1</v>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="n">
+        <v>1</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R184" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S184" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="T184" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U184" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V184" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W184" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X184" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU184" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="BF184" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BG184" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BI184" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ184" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BM184" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BN184" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO184" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BP184" t="n">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -29337,7 +29337,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>8309754</v>
+        <v>8309675</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -29357,197 +29357,197 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R133" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S133" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U133" t="n">
         <v>3</v>
       </c>
-      <c r="N133" t="n">
-        <v>3</v>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>['32', '38', '82']</t>
-        </is>
-      </c>
-      <c r="Q133" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R133" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S133" t="n">
+      <c r="V133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X133" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA133" t="n">
         <v>3.65</v>
       </c>
-      <c r="T133" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U133" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V133" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="W133" t="n">
+      <c r="AB133" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK133" t="n">
         <v>1.25</v>
       </c>
-      <c r="X133" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE133" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF133" t="n">
+      <c r="AL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO133" t="n">
         <v>2.5</v>
       </c>
-      <c r="AG133" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AK133" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM133" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN133" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AO133" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AP133" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AQ133" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AR133" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS133" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AT133" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV133" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW133" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX133" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY133" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ133" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA133" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB133" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC133" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD133" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BE133" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="BF133" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BG133" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BH133" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI133" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BJ133" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BK133" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BL133" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BM133" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BN133" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BO133" t="n">
-        <v>3.91</v>
-      </c>
       <c r="BP133" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="134">
@@ -29555,7 +29555,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>8309675</v>
+        <v>8309754</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -29575,197 +29575,197 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '38', '82']</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="R134" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="S134" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="T134" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="U134" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V134" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="W134" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X134" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH134" t="n">
         <v>3</v>
       </c>
-      <c r="V134" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W134" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X134" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE134" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF134" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AG134" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AI134" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ134" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK134" t="n">
+      <c r="BI134" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BP134" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AL134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM134" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AN134" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO134" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AP134" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AQ134" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AR134" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AS134" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AT134" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AU134" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV134" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW134" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX134" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY134" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ134" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA134" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB134" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC134" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD134" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BE134" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="BF134" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BG134" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BH134" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="BI134" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BJ134" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BK134" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BL134" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BM134" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BN134" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BO134" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BP134" t="n">
-        <v>1.48</v>
       </c>
     </row>
     <row r="135">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="296">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -685,6 +685,9 @@
     <t>['17', '39', '45+1', '64']</t>
   </si>
   <si>
+    <t>['4', '18']</t>
+  </si>
+  <si>
     <t>['3', '84', '90+7']</t>
   </si>
   <si>
@@ -1260,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP185"/>
+  <dimension ref="A1:BP186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1516,7 +1519,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q2">
         <v>3.04</v>
@@ -2212,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ5">
         <v>1.27</v>
@@ -2340,7 +2343,7 @@
         <v>89</v>
       </c>
       <c r="P6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q6">
         <v>4.4</v>
@@ -2546,7 +2549,7 @@
         <v>90</v>
       </c>
       <c r="P7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q7">
         <v>3.97</v>
@@ -2752,7 +2755,7 @@
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q8">
         <v>2.85</v>
@@ -3164,7 +3167,7 @@
         <v>86</v>
       </c>
       <c r="P10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q10">
         <v>3.05</v>
@@ -3245,7 +3248,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ10">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3370,7 +3373,7 @@
         <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -4194,7 +4197,7 @@
         <v>97</v>
       </c>
       <c r="P15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q15">
         <v>2.49</v>
@@ -4478,7 +4481,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ16">
         <v>0.73</v>
@@ -4812,7 +4815,7 @@
         <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q18">
         <v>3.5</v>
@@ -5224,7 +5227,7 @@
         <v>86</v>
       </c>
       <c r="P20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q20">
         <v>2.55</v>
@@ -5636,7 +5639,7 @@
         <v>100</v>
       </c>
       <c r="P22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q22">
         <v>2.75</v>
@@ -5842,7 +5845,7 @@
         <v>101</v>
       </c>
       <c r="P23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q23">
         <v>5.3</v>
@@ -6254,7 +6257,7 @@
         <v>103</v>
       </c>
       <c r="P25" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q25">
         <v>2.8</v>
@@ -6872,7 +6875,7 @@
         <v>106</v>
       </c>
       <c r="P28" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q28">
         <v>2.25</v>
@@ -7078,7 +7081,7 @@
         <v>107</v>
       </c>
       <c r="P29" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q29">
         <v>2.68</v>
@@ -7159,7 +7162,7 @@
         <v>1</v>
       </c>
       <c r="AQ29">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR29">
         <v>1.27</v>
@@ -7284,7 +7287,7 @@
         <v>108</v>
       </c>
       <c r="P30" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q30">
         <v>2.23</v>
@@ -8108,7 +8111,7 @@
         <v>112</v>
       </c>
       <c r="P34" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q34">
         <v>2.95</v>
@@ -9138,7 +9141,7 @@
         <v>86</v>
       </c>
       <c r="P39" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9344,7 +9347,7 @@
         <v>115</v>
       </c>
       <c r="P40" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q40">
         <v>2.24</v>
@@ -9425,7 +9428,7 @@
         <v>2</v>
       </c>
       <c r="AQ40">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR40">
         <v>2.04</v>
@@ -9756,7 +9759,7 @@
         <v>117</v>
       </c>
       <c r="P42" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -10580,7 +10583,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q46">
         <v>2.65</v>
@@ -11198,7 +11201,7 @@
         <v>118</v>
       </c>
       <c r="P49" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q49">
         <v>2.88</v>
@@ -11610,7 +11613,7 @@
         <v>124</v>
       </c>
       <c r="P51" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q51">
         <v>3.1</v>
@@ -12512,7 +12515,7 @@
         <v>0.33</v>
       </c>
       <c r="AP55">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ55">
         <v>0.42</v>
@@ -12846,7 +12849,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -13052,7 +13055,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q58">
         <v>2.45</v>
@@ -13258,7 +13261,7 @@
         <v>130</v>
       </c>
       <c r="P59" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q59">
         <v>2.6</v>
@@ -13545,7 +13548,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ60">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR60">
         <v>1.99</v>
@@ -14906,7 +14909,7 @@
         <v>137</v>
       </c>
       <c r="P67" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q67">
         <v>2.45</v>
@@ -15112,7 +15115,7 @@
         <v>138</v>
       </c>
       <c r="P68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q68">
         <v>4.33</v>
@@ -15318,7 +15321,7 @@
         <v>139</v>
       </c>
       <c r="P69" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q69">
         <v>2.9</v>
@@ -15936,7 +15939,7 @@
         <v>141</v>
       </c>
       <c r="P72" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q72">
         <v>3.6</v>
@@ -16017,7 +16020,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ72">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR72">
         <v>1.62</v>
@@ -16220,7 +16223,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ73">
         <v>1.25</v>
@@ -16760,7 +16763,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q76">
         <v>2.35</v>
@@ -16966,7 +16969,7 @@
         <v>145</v>
       </c>
       <c r="P77" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q77">
         <v>2.63</v>
@@ -17378,7 +17381,7 @@
         <v>86</v>
       </c>
       <c r="P79" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q79">
         <v>2.78</v>
@@ -17790,7 +17793,7 @@
         <v>86</v>
       </c>
       <c r="P81" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
@@ -17871,7 +17874,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ81">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR81">
         <v>1.44</v>
@@ -18074,7 +18077,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ82">
         <v>0.6899999999999999</v>
@@ -18202,7 +18205,7 @@
         <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q83">
         <v>2.5</v>
@@ -18408,7 +18411,7 @@
         <v>148</v>
       </c>
       <c r="P84" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q84">
         <v>2</v>
@@ -18614,7 +18617,7 @@
         <v>149</v>
       </c>
       <c r="P85" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q85">
         <v>2.55</v>
@@ -19026,7 +19029,7 @@
         <v>151</v>
       </c>
       <c r="P87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q87">
         <v>2.55</v>
@@ -19519,7 +19522,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ89">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR89">
         <v>1.74</v>
@@ -19850,7 +19853,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q91">
         <v>2.34</v>
@@ -20262,7 +20265,7 @@
         <v>154</v>
       </c>
       <c r="P93" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q93">
         <v>2.3</v>
@@ -20468,7 +20471,7 @@
         <v>86</v>
       </c>
       <c r="P94" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q94">
         <v>3.2</v>
@@ -20674,7 +20677,7 @@
         <v>155</v>
       </c>
       <c r="P95" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q95">
         <v>4.76</v>
@@ -20958,7 +20961,7 @@
         <v>1.33</v>
       </c>
       <c r="AP96">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ96">
         <v>1.33</v>
@@ -21292,7 +21295,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q98">
         <v>2.96</v>
@@ -21498,7 +21501,7 @@
         <v>86</v>
       </c>
       <c r="P99" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q99">
         <v>4.75</v>
@@ -21704,7 +21707,7 @@
         <v>159</v>
       </c>
       <c r="P100" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q100">
         <v>2.25</v>
@@ -21910,7 +21913,7 @@
         <v>160</v>
       </c>
       <c r="P101" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q101">
         <v>2.64</v>
@@ -22116,7 +22119,7 @@
         <v>161</v>
       </c>
       <c r="P102" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q102">
         <v>3.95</v>
@@ -23352,7 +23355,7 @@
         <v>165</v>
       </c>
       <c r="P108" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q108">
         <v>2.75</v>
@@ -23558,7 +23561,7 @@
         <v>157</v>
       </c>
       <c r="P109" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q109">
         <v>3.3</v>
@@ -24382,7 +24385,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q113">
         <v>1.75</v>
@@ -24460,7 +24463,7 @@
         <v>0.29</v>
       </c>
       <c r="AP113">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ113">
         <v>0.25</v>
@@ -24588,7 +24591,7 @@
         <v>169</v>
       </c>
       <c r="P114" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q114">
         <v>3.61</v>
@@ -24669,7 +24672,7 @@
         <v>2</v>
       </c>
       <c r="AQ114">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR114">
         <v>1.16</v>
@@ -24794,7 +24797,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q115">
         <v>3.25</v>
@@ -25000,7 +25003,7 @@
         <v>171</v>
       </c>
       <c r="P116" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q116">
         <v>3.9</v>
@@ -25206,7 +25209,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q117">
         <v>3.1</v>
@@ -25618,7 +25621,7 @@
         <v>86</v>
       </c>
       <c r="P119" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q119">
         <v>6.5</v>
@@ -26108,7 +26111,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ121">
         <v>0.91</v>
@@ -26442,7 +26445,7 @@
         <v>175</v>
       </c>
       <c r="P123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26854,7 +26857,7 @@
         <v>177</v>
       </c>
       <c r="P125" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q125">
         <v>2</v>
@@ -27060,7 +27063,7 @@
         <v>178</v>
       </c>
       <c r="P126" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q126">
         <v>3.51</v>
@@ -27266,7 +27269,7 @@
         <v>179</v>
       </c>
       <c r="P127" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q127">
         <v>3.9</v>
@@ -27472,7 +27475,7 @@
         <v>180</v>
       </c>
       <c r="P128" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q128">
         <v>3.4</v>
@@ -27678,7 +27681,7 @@
         <v>86</v>
       </c>
       <c r="P129" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q129">
         <v>2.9</v>
@@ -27884,7 +27887,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q130">
         <v>2.65</v>
@@ -28296,7 +28299,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q132">
         <v>3.65</v>
@@ -28708,7 +28711,7 @@
         <v>86</v>
       </c>
       <c r="P134" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q134">
         <v>3.5</v>
@@ -29120,7 +29123,7 @@
         <v>86</v>
       </c>
       <c r="P136" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q136">
         <v>4.5</v>
@@ -29407,7 +29410,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ137">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR137">
         <v>1.64</v>
@@ -29738,7 +29741,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q139">
         <v>2.25</v>
@@ -29944,7 +29947,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q140">
         <v>4</v>
@@ -30356,7 +30359,7 @@
         <v>190</v>
       </c>
       <c r="P142" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q142">
         <v>2.01</v>
@@ -30768,7 +30771,7 @@
         <v>86</v>
       </c>
       <c r="P144" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q144">
         <v>1.98</v>
@@ -30846,7 +30849,7 @@
         <v>1.38</v>
       </c>
       <c r="AP144">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ144">
         <v>1.27</v>
@@ -31386,7 +31389,7 @@
         <v>194</v>
       </c>
       <c r="P147" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q147">
         <v>2.06</v>
@@ -31464,7 +31467,7 @@
         <v>0.38</v>
       </c>
       <c r="AP147">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ147">
         <v>0.55</v>
@@ -31592,7 +31595,7 @@
         <v>195</v>
       </c>
       <c r="P148" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q148">
         <v>3.5</v>
@@ -31798,7 +31801,7 @@
         <v>196</v>
       </c>
       <c r="P149" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q149">
         <v>3.44</v>
@@ -32004,7 +32007,7 @@
         <v>197</v>
       </c>
       <c r="P150" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q150">
         <v>3.4</v>
@@ -32416,7 +32419,7 @@
         <v>199</v>
       </c>
       <c r="P152" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q152">
         <v>2.58</v>
@@ -32909,7 +32912,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ154">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR154">
         <v>1.48</v>
@@ -33034,7 +33037,7 @@
         <v>201</v>
       </c>
       <c r="P155" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q155">
         <v>2.49</v>
@@ -33446,7 +33449,7 @@
         <v>203</v>
       </c>
       <c r="P157" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q157">
         <v>2.05</v>
@@ -33524,7 +33527,7 @@
         <v>1.11</v>
       </c>
       <c r="AP157">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ157">
         <v>1.33</v>
@@ -33858,7 +33861,7 @@
         <v>205</v>
       </c>
       <c r="P159" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q159">
         <v>2.78</v>
@@ -34270,7 +34273,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q161">
         <v>3.3</v>
@@ -34682,7 +34685,7 @@
         <v>86</v>
       </c>
       <c r="P163" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q163">
         <v>4</v>
@@ -35094,7 +35097,7 @@
         <v>86</v>
       </c>
       <c r="P165" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q165">
         <v>2.99</v>
@@ -35506,7 +35509,7 @@
         <v>209</v>
       </c>
       <c r="P167" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q167">
         <v>2.23</v>
@@ -35712,7 +35715,7 @@
         <v>210</v>
       </c>
       <c r="P168" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q168">
         <v>3.75</v>
@@ -35793,7 +35796,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ168">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR168">
         <v>1.28</v>
@@ -36124,7 +36127,7 @@
         <v>211</v>
       </c>
       <c r="P170" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q170">
         <v>2.5</v>
@@ -36330,7 +36333,7 @@
         <v>212</v>
       </c>
       <c r="P171" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q171">
         <v>2.2</v>
@@ -36948,7 +36951,7 @@
         <v>215</v>
       </c>
       <c r="P174" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q174">
         <v>2.26</v>
@@ -37235,7 +37238,7 @@
         <v>2</v>
       </c>
       <c r="AQ175">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR175">
         <v>1.66</v>
@@ -37360,7 +37363,7 @@
         <v>217</v>
       </c>
       <c r="P176" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q176">
         <v>2.35</v>
@@ -37772,7 +37775,7 @@
         <v>218</v>
       </c>
       <c r="P178" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q178">
         <v>2.7</v>
@@ -37978,7 +37981,7 @@
         <v>219</v>
       </c>
       <c r="P179" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q179">
         <v>2.8</v>
@@ -38184,7 +38187,7 @@
         <v>220</v>
       </c>
       <c r="P180" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q180">
         <v>2.32</v>
@@ -38390,7 +38393,7 @@
         <v>86</v>
       </c>
       <c r="P181" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q181">
         <v>3.6</v>
@@ -39214,7 +39217,7 @@
         <v>222</v>
       </c>
       <c r="P185" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q185">
         <v>2.62</v>
@@ -39371,6 +39374,212 @@
       </c>
       <c r="BP185">
         <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>8309823</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45943.66666666666</v>
+      </c>
+      <c r="F186">
+        <v>24</v>
+      </c>
+      <c r="G186" t="s">
+        <v>73</v>
+      </c>
+      <c r="H186" t="s">
+        <v>72</v>
+      </c>
+      <c r="I186">
+        <v>2</v>
+      </c>
+      <c r="J186">
+        <v>1</v>
+      </c>
+      <c r="K186">
+        <v>3</v>
+      </c>
+      <c r="L186">
+        <v>2</v>
+      </c>
+      <c r="M186">
+        <v>1</v>
+      </c>
+      <c r="N186">
+        <v>3</v>
+      </c>
+      <c r="O186" t="s">
+        <v>223</v>
+      </c>
+      <c r="P186" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q186">
+        <v>2.25</v>
+      </c>
+      <c r="R186">
+        <v>2.3</v>
+      </c>
+      <c r="S186">
+        <v>4.4</v>
+      </c>
+      <c r="T186">
+        <v>1.33</v>
+      </c>
+      <c r="U186">
+        <v>3.1</v>
+      </c>
+      <c r="V186">
+        <v>2.63</v>
+      </c>
+      <c r="W186">
+        <v>1.44</v>
+      </c>
+      <c r="X186">
+        <v>6.5</v>
+      </c>
+      <c r="Y186">
+        <v>1.1</v>
+      </c>
+      <c r="Z186">
+        <v>1.74</v>
+      </c>
+      <c r="AA186">
+        <v>3.6</v>
+      </c>
+      <c r="AB186">
+        <v>4.53</v>
+      </c>
+      <c r="AC186">
+        <v>1.05</v>
+      </c>
+      <c r="AD186">
+        <v>11</v>
+      </c>
+      <c r="AE186">
+        <v>1.25</v>
+      </c>
+      <c r="AF186">
+        <v>3.7</v>
+      </c>
+      <c r="AG186">
+        <v>1.8</v>
+      </c>
+      <c r="AH186">
+        <v>1.91</v>
+      </c>
+      <c r="AI186">
+        <v>1.7</v>
+      </c>
+      <c r="AJ186">
+        <v>2.05</v>
+      </c>
+      <c r="AK186">
+        <v>1.3</v>
+      </c>
+      <c r="AL186">
+        <v>1.3</v>
+      </c>
+      <c r="AM186">
+        <v>2</v>
+      </c>
+      <c r="AN186">
+        <v>2.45</v>
+      </c>
+      <c r="AO186">
+        <v>1.58</v>
+      </c>
+      <c r="AP186">
+        <v>2.5</v>
+      </c>
+      <c r="AQ186">
+        <v>1.46</v>
+      </c>
+      <c r="AR186">
+        <v>2.05</v>
+      </c>
+      <c r="AS186">
+        <v>1.41</v>
+      </c>
+      <c r="AT186">
+        <v>3.46</v>
+      </c>
+      <c r="AU186">
+        <v>6</v>
+      </c>
+      <c r="AV186">
+        <v>3</v>
+      </c>
+      <c r="AW186">
+        <v>5</v>
+      </c>
+      <c r="AX186">
+        <v>10</v>
+      </c>
+      <c r="AY186">
+        <v>11</v>
+      </c>
+      <c r="AZ186">
+        <v>13</v>
+      </c>
+      <c r="BA186">
+        <v>3</v>
+      </c>
+      <c r="BB186">
+        <v>3</v>
+      </c>
+      <c r="BC186">
+        <v>6</v>
+      </c>
+      <c r="BD186">
+        <v>1.4</v>
+      </c>
+      <c r="BE186">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="BF186">
+        <v>4.12</v>
+      </c>
+      <c r="BG186">
+        <v>1.2</v>
+      </c>
+      <c r="BH186">
+        <v>3.6</v>
+      </c>
+      <c r="BI186">
+        <v>1.44</v>
+      </c>
+      <c r="BJ186">
+        <v>2.53</v>
+      </c>
+      <c r="BK186">
+        <v>1.98</v>
+      </c>
+      <c r="BL186">
+        <v>1.95</v>
+      </c>
+      <c r="BM186">
+        <v>2.21</v>
+      </c>
+      <c r="BN186">
+        <v>1.58</v>
+      </c>
+      <c r="BO186">
+        <v>2.92</v>
+      </c>
+      <c r="BP186">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP186"/>
+  <dimension ref="A1:BP187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.25</v>
@@ -3966,7 +3966,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR16" t="n">
         <v>3.87</v>
@@ -6579,7 +6579,7 @@
         <v>1</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.36</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.09</v>
@@ -8326,7 +8326,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR36" t="n">
         <v>1.35</v>
@@ -11375,7 +11375,7 @@
         <v>1.67</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.33</v>
@@ -11814,7 +11814,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR52" t="n">
         <v>1.81</v>
@@ -12683,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.55</v>
@@ -13340,7 +13340,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR59" t="n">
         <v>1.73</v>
@@ -17043,7 +17043,7 @@
         <v>0.2</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.42</v>
@@ -17264,7 +17264,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR77" t="n">
         <v>1.53</v>
@@ -20534,7 +20534,7 @@
         <v>1</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR92" t="n">
         <v>1.52</v>
@@ -20749,7 +20749,7 @@
         <v>0.83</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.6899999999999999</v>
@@ -22932,7 +22932,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR103" t="n">
         <v>1.38</v>
@@ -25763,7 +25763,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.91</v>
@@ -27292,7 +27292,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR123" t="n">
         <v>1.36</v>
@@ -27943,7 +27943,7 @@
         <v>0.88</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.25</v>
@@ -30341,7 +30341,7 @@
         <v>1.88</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.46</v>
@@ -31216,7 +31216,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR141" t="n">
         <v>1.69</v>
@@ -32306,7 +32306,7 @@
         <v>2</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR146" t="n">
         <v>1.34</v>
@@ -35794,7 +35794,7 @@
         <v>2</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR162" t="n">
         <v>1.61</v>
@@ -36009,7 +36009,7 @@
         <v>2.3</v>
       </c>
       <c r="AP163" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ163" t="n">
         <v>2.42</v>
@@ -41101,6 +41101,224 @@
         <v>2.92</v>
       </c>
       <c r="BP186" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="n">
+        <v>8309653</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>45947.75</v>
+      </c>
+      <c r="F187" t="n">
+        <v>24</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" t="n">
+        <v>3</v>
+      </c>
+      <c r="K187" t="n">
+        <v>4</v>
+      </c>
+      <c r="L187" t="n">
+        <v>4</v>
+      </c>
+      <c r="M187" t="n">
+        <v>3</v>
+      </c>
+      <c r="N187" t="n">
+        <v>7</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>['11', '54', '66', '75']</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>['39', '42', '45']</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R187" t="n">
+        <v>2</v>
+      </c>
+      <c r="S187" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T187" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U187" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V187" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W187" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X187" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK187" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL187" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM187" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN187" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO187" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP187" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ187" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR187" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS187" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT187" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU187" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX187" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY187" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA187" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB187" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC187" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BE187" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF187" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BG187" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH187" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI187" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ187" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BK187" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL187" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM187" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN187" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO187" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP187" t="n">
         <v>1.32</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP187"/>
+  <dimension ref="A1:BP188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ2" t="n">
         <v>2.42</v>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR25" t="n">
         <v>1.21</v>
@@ -6797,7 +6797,7 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.46</v>
@@ -8544,7 +8544,7 @@
         <v>2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR37" t="n">
         <v>1.67</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.55</v>
@@ -11378,7 +11378,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR50" t="n">
         <v>1.74</v>
@@ -16610,7 +16610,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR74" t="n">
         <v>1.85</v>
@@ -16825,7 +16825,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.6899999999999999</v>
@@ -20098,7 +20098,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR90" t="n">
         <v>1.54</v>
@@ -20531,7 +20531,7 @@
         <v>0.4</v>
       </c>
       <c r="AP92" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.67</v>
@@ -21406,7 +21406,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR96" t="n">
         <v>2.1</v>
@@ -22711,7 +22711,7 @@
         <v>1.5</v>
       </c>
       <c r="AP102" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.91</v>
@@ -24237,7 +24237,7 @@
         <v>0.67</v>
       </c>
       <c r="AP109" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.7</v>
@@ -26202,7 +26202,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR118" t="n">
         <v>1.63</v>
@@ -28382,7 +28382,7 @@
         <v>2</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR128" t="n">
         <v>1.28</v>
@@ -29905,7 +29905,7 @@
         <v>1.43</v>
       </c>
       <c r="AP135" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.33</v>
@@ -30995,7 +30995,7 @@
         <v>0.89</v>
       </c>
       <c r="AP140" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.25</v>
@@ -32742,7 +32742,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR148" t="n">
         <v>1.58</v>
@@ -35576,7 +35576,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR161" t="n">
         <v>1.41</v>
@@ -36663,7 +36663,7 @@
         <v>1.38</v>
       </c>
       <c r="AP166" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.27</v>
@@ -37971,7 +37971,7 @@
         <v>0.4</v>
       </c>
       <c r="AP172" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.36</v>
@@ -39500,7 +39500,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR179" t="n">
         <v>1.8</v>
@@ -41320,6 +41320,224 @@
       </c>
       <c r="BP187" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="n">
+        <v>8309644</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>45947.85416666666</v>
+      </c>
+      <c r="F188" t="n">
+        <v>24</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>1</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1</v>
+      </c>
+      <c r="K188" t="n">
+        <v>2</v>
+      </c>
+      <c r="L188" t="n">
+        <v>2</v>
+      </c>
+      <c r="M188" t="n">
+        <v>3</v>
+      </c>
+      <c r="N188" t="n">
+        <v>5</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>['13', '55']</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>['20', '51', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="R188" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S188" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T188" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U188" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V188" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W188" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X188" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA188" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB188" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC188" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BE188" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF188" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BG188" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH188" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BI188" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ188" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK188" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BL188" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM188" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN188" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO188" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP188" t="n">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP188"/>
+  <dimension ref="A1:BP189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.91</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.55</v>
@@ -5274,7 +5274,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.67</v>
@@ -8762,7 +8762,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR38" t="n">
         <v>1.81</v>
@@ -11593,7 +11593,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.7</v>
@@ -12032,7 +12032,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR53" t="n">
         <v>1.15</v>
@@ -18790,7 +18790,7 @@
         <v>2</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR84" t="n">
         <v>1.8</v>
@@ -19005,7 +19005,7 @@
         <v>0.4</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.25</v>
@@ -20970,7 +20970,7 @@
         <v>2</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR94" t="n">
         <v>1.19</v>
@@ -21185,7 +21185,7 @@
         <v>1.83</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ95" t="n">
         <v>2.42</v>
@@ -25545,7 +25545,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.36</v>
@@ -25984,7 +25984,7 @@
         <v>2</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR117" t="n">
         <v>1.61</v>
@@ -28600,7 +28600,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR129" t="n">
         <v>1.39</v>
@@ -28815,7 +28815,7 @@
         <v>1.14</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.27</v>
@@ -32739,7 +32739,7 @@
         <v>1.22</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.46</v>
@@ -36445,7 +36445,7 @@
         <v>0.6</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.6899999999999999</v>
@@ -36666,7 +36666,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR166" t="n">
         <v>1.48</v>
@@ -38846,7 +38846,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR176" t="n">
         <v>1.51</v>
@@ -40369,7 +40369,7 @@
         <v>1.1</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.09</v>
@@ -40590,7 +40590,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR184" t="n">
         <v>1.53</v>
@@ -41537,6 +41537,224 @@
         <v>3.08</v>
       </c>
       <c r="BP188" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="n">
+        <v>8309663</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>45948.625</v>
+      </c>
+      <c r="F189" t="n">
+        <v>24</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
+        <v>1</v>
+      </c>
+      <c r="N189" t="n">
+        <v>2</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R189" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S189" t="n">
+        <v>3</v>
+      </c>
+      <c r="T189" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U189" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V189" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W189" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X189" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK189" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ189" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY189" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB189" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC189" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE189" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF189" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG189" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH189" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BI189" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ189" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK189" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL189" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BM189" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN189" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO189" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP189" t="n">
         <v>1.26</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP189"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.7</v>
@@ -4399,7 +4399,7 @@
         <v>3</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ18" t="n">
         <v>2.42</v>
@@ -7018,7 +7018,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR30" t="n">
         <v>1.59</v>
@@ -7887,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.6899999999999999</v>
@@ -10724,7 +10724,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR47" t="n">
         <v>1.59</v>
@@ -12247,7 +12247,7 @@
         <v>0.33</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.25</v>
@@ -12904,7 +12904,7 @@
         <v>2</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR57" t="n">
         <v>1.17</v>
@@ -15735,7 +15735,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.91</v>
@@ -15956,7 +15956,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR71" t="n">
         <v>1.29</v>
@@ -18133,7 +18133,7 @@
         <v>2</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.46</v>
@@ -19223,7 +19223,7 @@
         <v>1</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.09</v>
@@ -19444,7 +19444,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR87" t="n">
         <v>1.56</v>
@@ -22929,7 +22929,7 @@
         <v>0.83</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.67</v>
@@ -24458,7 +24458,7 @@
         <v>2</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR110" t="n">
         <v>2.01</v>
@@ -28597,7 +28597,7 @@
         <v>1.14</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.25</v>
@@ -28818,7 +28818,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR130" t="n">
         <v>1.53</v>
@@ -31870,7 +31870,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR144" t="n">
         <v>2</v>
@@ -33393,7 +33393,7 @@
         <v>1.25</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.33</v>
@@ -34486,7 +34486,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR156" t="n">
         <v>1.71</v>
@@ -35573,7 +35573,7 @@
         <v>1.2</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.46</v>
@@ -37756,7 +37756,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR171" t="n">
         <v>1.52</v>
@@ -39933,7 +39933,7 @@
         <v>1.09</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AQ181" t="n">
         <v>1.25</v>
@@ -41756,6 +41756,224 @@
       </c>
       <c r="BP189" t="n">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>8309659</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>45948.72916666666</v>
+      </c>
+      <c r="F190" t="n">
+        <v>24</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>2</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>2</v>
+      </c>
+      <c r="L190" t="n">
+        <v>2</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>2</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>['30', '43']</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R190" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="S190" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T190" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U190" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V190" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W190" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X190" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB190" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF190" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG190" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH190" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI190" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ190" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="BK190" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL190" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM190" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN190" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO190" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP190" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -41701,13 +41701,13 @@
         <v>6</v>
       </c>
       <c r="AX189" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY189" t="n">
         <v>7</v>
       </c>
       <c r="AZ189" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA189" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,7 +1786,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.25</v>
@@ -5492,7 +5492,7 @@
         <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR23" t="n">
         <v>1.24</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.17</v>
@@ -10503,7 +10503,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.33</v>
@@ -10939,7 +10939,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.6899999999999999</v>
@@ -15738,7 +15738,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR70" t="n">
         <v>1.48</v>
@@ -16607,7 +16607,7 @@
         <v>1.25</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.46</v>
@@ -19877,7 +19877,7 @@
         <v>2.17</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.46</v>
@@ -22060,7 +22060,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR99" t="n">
         <v>1.34</v>
@@ -22714,7 +22714,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR102" t="n">
         <v>1.56</v>
@@ -23801,7 +23801,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.09</v>
@@ -25766,7 +25766,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR116" t="n">
         <v>1.77</v>
@@ -26638,7 +26638,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR120" t="n">
         <v>1.67</v>
@@ -26856,7 +26856,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR121" t="n">
         <v>2.12</v>
@@ -27725,7 +27725,7 @@
         <v>0.25</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.25</v>
@@ -29254,7 +29254,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR132" t="n">
         <v>1.66</v>
@@ -30777,7 +30777,7 @@
         <v>0.5</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.36</v>
@@ -32960,7 +32960,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR149" t="n">
         <v>1.61</v>
@@ -35137,7 +35137,7 @@
         <v>0.88</v>
       </c>
       <c r="AP159" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.7</v>
@@ -35358,7 +35358,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR160" t="n">
         <v>1.75</v>
@@ -38843,7 +38843,7 @@
         <v>1.56</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.25</v>
@@ -41974,6 +41974,224 @@
       </c>
       <c r="BP190" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>8309696</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>45949.52083333334</v>
+      </c>
+      <c r="F191" t="n">
+        <v>24</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="n">
+        <v>1</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>3</v>
+      </c>
+      <c r="R191" t="n">
+        <v>2</v>
+      </c>
+      <c r="S191" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T191" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U191" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V191" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W191" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X191" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB191" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF191" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BG191" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH191" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BI191" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ191" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BK191" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL191" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM191" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN191" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO191" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP191" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP191"/>
+  <dimension ref="A1:BP192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3094,7 +3094,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.25</v>
@@ -6364,7 +6364,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR27" t="n">
         <v>1.93</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ35" t="n">
         <v>2.42</v>
@@ -9413,7 +9413,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.09</v>
@@ -9634,7 +9634,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR42" t="n">
         <v>1.19</v>
@@ -11160,7 +11160,7 @@
         <v>2</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR49" t="n">
         <v>1.45</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.67</v>
@@ -16171,7 +16171,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.46</v>
@@ -16392,7 +16392,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR73" t="n">
         <v>2.4</v>
@@ -17918,7 +17918,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR80" t="n">
         <v>1.8</v>
@@ -19441,7 +19441,7 @@
         <v>1.4</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.17</v>
@@ -21621,7 +21621,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.33</v>
@@ -21842,7 +21842,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR98" t="n">
         <v>1.82</v>
@@ -24676,7 +24676,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR111" t="n">
         <v>1.4</v>
@@ -26199,7 +26199,7 @@
         <v>1.14</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.46</v>
@@ -27071,7 +27071,7 @@
         <v>0.43</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.36</v>
@@ -27946,7 +27946,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR126" t="n">
         <v>1.72</v>
@@ -29033,7 +29033,7 @@
         <v>0.63</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.6899999999999999</v>
@@ -30998,7 +30998,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR140" t="n">
         <v>1.45</v>
@@ -32957,7 +32957,7 @@
         <v>0.89</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.83</v>
@@ -34268,7 +34268,7 @@
         <v>2</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR155" t="n">
         <v>2.11</v>
@@ -36881,7 +36881,7 @@
         <v>0.45</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.42</v>
@@ -39936,7 +39936,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR181" t="n">
         <v>1.4</v>
@@ -42134,13 +42134,13 @@
         <v>5</v>
       </c>
       <c r="AW191" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX191" t="n">
         <v>7</v>
       </c>
       <c r="AY191" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ191" t="n">
         <v>12</v>
@@ -42192,6 +42192,224 @@
       </c>
       <c r="BP191" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>8309824</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>45949.625</v>
+      </c>
+      <c r="F192" t="n">
+        <v>24</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>2</v>
+      </c>
+      <c r="K192" t="n">
+        <v>2</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>3</v>
+      </c>
+      <c r="N192" t="n">
+        <v>3</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>['26', '39', '54']</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R192" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S192" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="T192" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U192" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V192" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W192" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X192" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX192" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY192" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB192" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC192" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE192" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="BF192" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BG192" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH192" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI192" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ192" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK192" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL192" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM192" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BN192" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO192" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP192" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -42131,13 +42131,13 @@
         <v>1</v>
       </c>
       <c r="AV191" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW191" t="n">
         <v>6</v>
       </c>
       <c r="AX191" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY191" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP192"/>
+  <dimension ref="A1:BP193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.17</v>
@@ -2004,7 +2004,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.33</v>
@@ -7454,7 +7454,7 @@
         <v>2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR32" t="n">
         <v>1.89</v>
@@ -8759,7 +8759,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.25</v>
@@ -11596,7 +11596,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR51" t="n">
         <v>1.33</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.67</v>
@@ -14430,7 +14430,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR64" t="n">
         <v>1.6</v>
@@ -15299,7 +15299,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.09</v>
@@ -18572,7 +18572,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR83" t="n">
         <v>1.51</v>
@@ -21839,7 +21839,7 @@
         <v>0.83</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.38</v>
@@ -23147,7 +23147,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.42</v>
@@ -24240,7 +24240,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR109" t="n">
         <v>1.46</v>
@@ -29469,7 +29469,7 @@
         <v>0.43</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.55</v>
@@ -31652,7 +31652,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR143" t="n">
         <v>1.54</v>
@@ -32085,7 +32085,7 @@
         <v>0.22</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.25</v>
@@ -35140,7 +35140,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR159" t="n">
         <v>1.54</v>
@@ -35355,7 +35355,7 @@
         <v>0.9</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.83</v>
@@ -39064,7 +39064,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ177" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AR177" t="n">
         <v>1.29</v>
@@ -39497,7 +39497,7 @@
         <v>1.18</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ179" t="n">
         <v>1.46</v>
@@ -42410,6 +42410,224 @@
       </c>
       <c r="BP192" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="n">
+        <v>8309825</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>45954.70833333334</v>
+      </c>
+      <c r="F193" t="n">
+        <v>25</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>2</v>
+      </c>
+      <c r="M193" t="n">
+        <v>1</v>
+      </c>
+      <c r="N193" t="n">
+        <v>3</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>['61', '72']</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R193" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S193" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T193" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U193" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V193" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="W193" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X193" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI193" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AK193" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ193" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU193" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW193" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX193" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY193" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ193" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA193" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB193" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC193" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD193" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE193" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF193" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG193" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH193" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI193" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ193" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK193" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BL193" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BM193" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BN193" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO193" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BP193" t="n">
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -42570,13 +42570,13 @@
         <v>3</v>
       </c>
       <c r="AW193" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX193" t="n">
         <v>4</v>
       </c>
       <c r="AY193" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ193" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP193"/>
+  <dimension ref="A1:BP194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.83</v>
@@ -2222,7 +2222,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.55</v>
@@ -4838,7 +4838,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR20" t="n">
         <v>1.85</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.67</v>
@@ -10506,7 +10506,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR46" t="n">
         <v>2.04</v>
@@ -11593,7 +11593,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.64</v>
@@ -14212,7 +14212,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR63" t="n">
         <v>1.48</v>
@@ -17700,7 +17700,7 @@
         <v>2</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR79" t="n">
         <v>1.49</v>
@@ -19005,7 +19005,7 @@
         <v>0.4</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.25</v>
@@ -21185,7 +21185,7 @@
         <v>1.83</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ95" t="n">
         <v>2.42</v>
@@ -21624,7 +21624,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR97" t="n">
         <v>1.61</v>
@@ -24022,7 +24022,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR108" t="n">
         <v>1.53</v>
@@ -25545,7 +25545,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.36</v>
@@ -28815,7 +28815,7 @@
         <v>1.14</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.17</v>
@@ -29908,7 +29908,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR135" t="n">
         <v>1.46</v>
@@ -32739,7 +32739,7 @@
         <v>1.22</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.46</v>
@@ -33396,7 +33396,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR151" t="n">
         <v>1.38</v>
@@ -34704,7 +34704,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR157" t="n">
         <v>2.07</v>
@@ -36445,7 +36445,7 @@
         <v>0.6</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.6899999999999999</v>
@@ -37538,7 +37538,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR170" t="n">
         <v>1.74</v>
@@ -39282,7 +39282,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR178" t="n">
         <v>1.54</v>
@@ -40369,7 +40369,7 @@
         <v>1.1</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.09</v>
@@ -41677,7 +41677,7 @@
         <v>1.27</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.25</v>
@@ -42628,6 +42628,224 @@
       </c>
       <c r="BP193" t="n">
         <v>1.56</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="n">
+        <v>8309660</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>45955.625</v>
+      </c>
+      <c r="F194" t="n">
+        <v>25</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>1</v>
+      </c>
+      <c r="L194" t="n">
+        <v>2</v>
+      </c>
+      <c r="M194" t="n">
+        <v>1</v>
+      </c>
+      <c r="N194" t="n">
+        <v>3</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>['45+3', '55']</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R194" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S194" t="n">
+        <v>3</v>
+      </c>
+      <c r="T194" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U194" t="n">
+        <v>3</v>
+      </c>
+      <c r="V194" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X194" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AU194" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW194" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX194" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY194" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ194" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA194" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB194" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC194" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD194" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE194" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF194" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BG194" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH194" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI194" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ194" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK194" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL194" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM194" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN194" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO194" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP194" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP194"/>
+  <dimension ref="A1:BP195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2876,7 +2876,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.64</v>
@@ -5056,7 +5056,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR21" t="n">
         <v>1.26</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ23" t="n">
         <v>0.83</v>
@@ -9852,7 +9852,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR43" t="n">
         <v>1.59</v>
@@ -10285,7 +10285,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.42</v>
@@ -12250,7 +12250,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR54" t="n">
         <v>1.19</v>
@@ -12901,7 +12901,7 @@
         <v>0.33</v>
       </c>
       <c r="AP57" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.17</v>
@@ -15084,7 +15084,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR67" t="n">
         <v>1.92</v>
@@ -15517,7 +15517,7 @@
         <v>0.75</v>
       </c>
       <c r="AP69" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.55</v>
@@ -19008,7 +19008,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR85" t="n">
         <v>1.34</v>
@@ -20967,7 +20967,7 @@
         <v>0.8</v>
       </c>
       <c r="AP94" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.25</v>
@@ -22278,7 +22278,7 @@
         <v>2</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR100" t="n">
         <v>1.51</v>
@@ -25112,7 +25112,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR113" t="n">
         <v>2.07</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.46</v>
@@ -27728,7 +27728,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR125" t="n">
         <v>1.52</v>
@@ -28379,7 +28379,7 @@
         <v>1.38</v>
       </c>
       <c r="AP128" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.46</v>
@@ -32088,7 +32088,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR145" t="n">
         <v>1.7</v>
@@ -32303,7 +32303,7 @@
         <v>0.89</v>
       </c>
       <c r="AP146" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.67</v>
@@ -33614,7 +33614,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR152" t="n">
         <v>1.48</v>
@@ -34919,7 +34919,7 @@
         <v>0.44</v>
       </c>
       <c r="AP158" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.36</v>
@@ -37317,7 +37317,7 @@
         <v>2.36</v>
       </c>
       <c r="AP169" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ169" t="n">
         <v>2.42</v>
@@ -40154,7 +40154,7 @@
         <v>2</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AR182" t="n">
         <v>2.12</v>
@@ -42846,6 +42846,224 @@
       </c>
       <c r="BP194" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="n">
+        <v>8309664</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>45955.72916666666</v>
+      </c>
+      <c r="F195" t="n">
+        <v>25</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" t="n">
+        <v>1</v>
+      </c>
+      <c r="N195" t="n">
+        <v>2</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R195" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S195" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T195" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U195" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V195" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X195" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU195" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV195" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW195" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX195" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY195" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ195" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA195" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB195" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC195" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD195" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE195" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF195" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BG195" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH195" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI195" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ195" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK195" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL195" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM195" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN195" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO195" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP195" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -43006,13 +43006,13 @@
         <v>5</v>
       </c>
       <c r="AW195" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX195" t="n">
         <v>12</v>
       </c>
       <c r="AY195" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ195" t="n">
         <v>17</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP195"/>
+  <dimension ref="A1:BP196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.23</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.31</v>
@@ -5710,7 +5710,7 @@
         <v>2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
         <v>1.15</v>
@@ -7672,7 +7672,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR33" t="n">
         <v>1.92</v>
@@ -9416,7 +9416,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR41" t="n">
         <v>1.94</v>
@@ -13119,7 +13119,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.36</v>
@@ -14427,7 +14427,7 @@
         <v>0.25</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.64</v>
@@ -15302,7 +15302,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR68" t="n">
         <v>1.79</v>
@@ -19226,7 +19226,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR86" t="n">
         <v>1.44</v>
@@ -20313,7 +20313,7 @@
         <v>0.17</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.42</v>
@@ -23365,7 +23365,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.6899999999999999</v>
@@ -23804,7 +23804,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR107" t="n">
         <v>1.67</v>
@@ -26420,7 +26420,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR119" t="n">
         <v>1.41</v>
@@ -26635,7 +26635,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.83</v>
@@ -28164,7 +28164,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR127" t="n">
         <v>1.6</v>
@@ -29687,7 +29687,7 @@
         <v>2.13</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ134" t="n">
         <v>2.42</v>
@@ -30126,7 +30126,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR136" t="n">
         <v>1.33</v>
@@ -36227,7 +36227,7 @@
         <v>0.33</v>
       </c>
       <c r="AP164" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ164" t="n">
         <v>0.55</v>
@@ -37753,7 +37753,7 @@
         <v>1.4</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.17</v>
@@ -38192,7 +38192,7 @@
         <v>2</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR173" t="n">
         <v>2.12</v>
@@ -40372,7 +40372,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AR183" t="n">
         <v>1.66</v>
@@ -40587,7 +40587,7 @@
         <v>1.4</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.25</v>
@@ -43064,6 +43064,224 @@
       </c>
       <c r="BP195" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>8309694</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>45956.52083333334</v>
+      </c>
+      <c r="F196" t="n">
+        <v>25</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>1</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R196" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S196" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T196" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U196" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V196" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="W196" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X196" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS196" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AT196" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AU196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV196" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX196" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA196" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB196" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC196" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD196" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BE196" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="BF196" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BG196" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH196" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI196" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ196" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK196" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BL196" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BM196" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN196" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO196" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BP196" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP196"/>
+  <dimension ref="A1:BP198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,7 +1568,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.42</v>
@@ -4620,7 +4620,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR19" t="n">
         <v>0.72</v>
@@ -5274,7 +5274,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ24" t="n">
         <v>1</v>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.46</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.6899999999999999</v>
@@ -8541,7 +8541,7 @@
         <v>2</v>
       </c>
       <c r="AP37" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.46</v>
@@ -8762,7 +8762,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR38" t="n">
         <v>1.81</v>
@@ -8980,7 +8980,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR39" t="n">
         <v>1.57</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.17</v>
@@ -11157,7 +11157,7 @@
         <v>1.33</v>
       </c>
       <c r="AP49" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.38</v>
@@ -12032,7 +12032,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR53" t="n">
         <v>1.15</v>
@@ -12686,7 +12686,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR56" t="n">
         <v>1.62</v>
@@ -14209,7 +14209,7 @@
         <v>1</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.23</v>
@@ -14645,7 +14645,7 @@
         <v>0.25</v>
       </c>
       <c r="AP65" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.36</v>
@@ -15520,7 +15520,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR69" t="n">
         <v>1.22</v>
@@ -17479,7 +17479,7 @@
         <v>1.6</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ78" t="n">
         <v>2.42</v>
@@ -17697,7 +17697,7 @@
         <v>0.75</v>
       </c>
       <c r="AP79" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.23</v>
@@ -18790,7 +18790,7 @@
         <v>2</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR84" t="n">
         <v>1.8</v>
@@ -19662,7 +19662,7 @@
         <v>2</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR88" t="n">
         <v>1.91</v>
@@ -20970,7 +20970,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR94" t="n">
         <v>1.19</v>
@@ -22057,7 +22057,7 @@
         <v>1</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.83</v>
@@ -22275,7 +22275,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.31</v>
@@ -23586,7 +23586,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR106" t="n">
         <v>1.65</v>
@@ -24673,7 +24673,7 @@
         <v>0.86</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.38</v>
@@ -25981,10 +25981,10 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR117" t="n">
         <v>1.61</v>
@@ -28600,7 +28600,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR129" t="n">
         <v>1.39</v>
@@ -29472,7 +29472,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR133" t="n">
         <v>1.69</v>
@@ -30123,7 +30123,7 @@
         <v>1</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ136" t="n">
         <v>1</v>
@@ -32524,7 +32524,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR147" t="n">
         <v>2.04</v>
@@ -33175,7 +33175,7 @@
         <v>2.22</v>
       </c>
       <c r="AP150" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ150" t="n">
         <v>2.42</v>
@@ -33829,7 +33829,7 @@
         <v>0.4</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.42</v>
@@ -35791,7 +35791,7 @@
         <v>0.8</v>
       </c>
       <c r="AP162" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.67</v>
@@ -36230,7 +36230,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR164" t="n">
         <v>1.48</v>
@@ -36666,7 +36666,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR166" t="n">
         <v>1.48</v>
@@ -37099,7 +37099,7 @@
         <v>1.6</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.46</v>
@@ -38410,7 +38410,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AR174" t="n">
         <v>1.46</v>
@@ -38625,7 +38625,7 @@
         <v>1.73</v>
       </c>
       <c r="AP175" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ175" t="n">
         <v>1.46</v>
@@ -38846,7 +38846,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR176" t="n">
         <v>1.51</v>
@@ -39061,7 +39061,7 @@
         <v>0.78</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ177" t="n">
         <v>0.64</v>
@@ -39715,7 +39715,7 @@
         <v>0.82</v>
       </c>
       <c r="AP180" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ180" t="n">
         <v>0.6899999999999999</v>
@@ -40590,7 +40590,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR184" t="n">
         <v>1.53</v>
@@ -41680,7 +41680,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR189" t="n">
         <v>1.64</v>
@@ -43282,6 +43282,442 @@
       </c>
       <c r="BP196" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>8309819</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>45956.66666666666</v>
+      </c>
+      <c r="F197" t="n">
+        <v>25</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="n">
+        <v>1</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R197" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S197" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T197" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U197" t="n">
+        <v>3</v>
+      </c>
+      <c r="V197" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W197" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X197" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AU197" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV197" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX197" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB197" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC197" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BE197" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BF197" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG197" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH197" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI197" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ197" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BK197" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BL197" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM197" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN197" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO197" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP197" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>8309833</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>45956.77083333334</v>
+      </c>
+      <c r="F198" t="n">
+        <v>25</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>1</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>1</v>
+      </c>
+      <c r="L198" t="n">
+        <v>3</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>3</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>['7', '72', '90']</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R198" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S198" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T198" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U198" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V198" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W198" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X198" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC198" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE198" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF198" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BI198" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM198" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BN198" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO198" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BP198" t="n">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP198"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.6899999999999999</v>
@@ -4402,7 +4402,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR18" t="n">
         <v>1.83</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.42</v>
@@ -8108,7 +8108,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ35" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR35" t="n">
         <v>2.22</v>
@@ -10067,7 +10067,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.36</v>
@@ -13555,7 +13555,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.46</v>
@@ -13776,7 +13776,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR61" t="n">
         <v>1.7</v>
@@ -14866,7 +14866,7 @@
         <v>2</v>
       </c>
       <c r="AQ66" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR66" t="n">
         <v>2.02</v>
@@ -15081,7 +15081,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.31</v>
@@ -17482,7 +17482,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ78" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR78" t="n">
         <v>1.36</v>
@@ -17915,7 +17915,7 @@
         <v>1</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.38</v>
@@ -21188,7 +21188,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ95" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR95" t="n">
         <v>1.55</v>
@@ -23583,7 +23583,7 @@
         <v>0.5</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.5</v>
@@ -24894,7 +24894,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR112" t="n">
         <v>1.51</v>
@@ -29251,7 +29251,7 @@
         <v>0.88</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ132" t="n">
         <v>0.83</v>
@@ -29690,7 +29690,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ134" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR134" t="n">
         <v>1.62</v>
@@ -31213,7 +31213,7 @@
         <v>1</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.67</v>
@@ -33178,7 +33178,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ150" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR150" t="n">
         <v>1.59</v>
@@ -34483,7 +34483,7 @@
         <v>1.56</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.17</v>
@@ -36012,7 +36012,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ163" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR163" t="n">
         <v>1.6</v>
@@ -37320,7 +37320,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ169" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AR169" t="n">
         <v>1.36</v>
@@ -37535,7 +37535,7 @@
         <v>1.3</v>
       </c>
       <c r="AP170" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.23</v>
@@ -43507,7 +43507,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>8309833</v>
+        <v>8309651</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -43527,196 +43527,414 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>1</v>
+      </c>
+      <c r="N198" t="n">
+        <v>1</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R198" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S198" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T198" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V198" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W198" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X198" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU198" t="n">
         <v>3</v>
       </c>
-      <c r="M198" t="n">
-        <v>0</v>
-      </c>
-      <c r="N198" t="n">
-        <v>3</v>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>['7', '72', '90']</t>
-        </is>
-      </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q198" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R198" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S198" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T198" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U198" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V198" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="W198" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X198" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y198" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z198" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA198" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AB198" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AC198" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD198" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE198" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF198" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AG198" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH198" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI198" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ198" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK198" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL198" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM198" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN198" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO198" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP198" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AQ198" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR198" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS198" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AT198" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU198" t="n">
+      <c r="AV198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW198" t="n">
         <v>6</v>
       </c>
-      <c r="AV198" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW198" t="n">
-        <v>7</v>
-      </c>
       <c r="AX198" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY198" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ198" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA198" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB198" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BC198" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD198" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="BE198" t="n">
         <v>6.75</v>
       </c>
       <c r="BF198" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BI198" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM198" t="n">
         <v>2.24</v>
       </c>
-      <c r="BG198" t="n">
+      <c r="BN198" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO198" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BP198" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>8309833</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>45956.77083333334</v>
+      </c>
+      <c r="F199" t="n">
+        <v>25</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>1</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>1</v>
+      </c>
+      <c r="L199" t="n">
+        <v>3</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>3</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>['7', '72', '90']</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R199" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S199" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U199" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V199" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="W199" t="n">
         <v>1.36</v>
       </c>
-      <c r="BH198" t="n">
+      <c r="X199" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE199" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF199" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH199" t="n">
         <v>2.65</v>
       </c>
-      <c r="BI198" t="n">
+      <c r="BI199" t="n">
         <v>1.6</v>
       </c>
-      <c r="BJ198" t="n">
+      <c r="BJ199" t="n">
         <v>2.18</v>
       </c>
-      <c r="BK198" t="n">
+      <c r="BK199" t="n">
         <v>1.99</v>
       </c>
-      <c r="BL198" t="n">
+      <c r="BL199" t="n">
         <v>1.73</v>
       </c>
-      <c r="BM198" t="n">
+      <c r="BM199" t="n">
         <v>2.58</v>
       </c>
-      <c r="BN198" t="n">
+      <c r="BN199" t="n">
         <v>1.48</v>
       </c>
-      <c r="BO198" t="n">
+      <c r="BO199" t="n">
         <v>3.58</v>
       </c>
-      <c r="BP198" t="n">
+      <c r="BP199" t="n">
         <v>1.21</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -43227,13 +43227,13 @@
         <v>10</v>
       </c>
       <c r="AX196" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY196" t="n">
         <v>13</v>
       </c>
       <c r="AZ196" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA196" t="n">
         <v>8</v>
@@ -43445,22 +43445,22 @@
         <v>9</v>
       </c>
       <c r="AX197" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY197" t="n">
         <v>18</v>
       </c>
       <c r="AZ197" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA197" t="n">
         <v>4</v>
       </c>
       <c r="BB197" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC197" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD197" t="n">
         <v>1.92</v>
@@ -43878,16 +43878,16 @@
         <v>2</v>
       </c>
       <c r="AW199" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX199" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY199" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ199" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA199" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3312,7 +3312,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.46</v>
@@ -6582,7 +6582,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR28" t="n">
         <v>1.8</v>
@@ -7451,7 +7451,7 @@
         <v>0.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.64</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.46</v>
@@ -10070,7 +10070,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR44" t="n">
         <v>2.2</v>
@@ -13122,7 +13122,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR58" t="n">
         <v>1.48</v>
@@ -14648,7 +14648,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR65" t="n">
         <v>1.44</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ66" t="n">
         <v>2.46</v>
@@ -18787,7 +18787,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.15</v>
@@ -19659,7 +19659,7 @@
         <v>0.6</v>
       </c>
       <c r="AP88" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.5</v>
@@ -22496,7 +22496,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR101" t="n">
         <v>1.38</v>
@@ -24455,7 +24455,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.17</v>
@@ -25548,7 +25548,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR115" t="n">
         <v>1.48</v>
@@ -27074,7 +27074,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR122" t="n">
         <v>1.56</v>
@@ -27507,7 +27507,7 @@
         <v>0.5</v>
       </c>
       <c r="AP124" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.42</v>
@@ -30780,7 +30780,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR139" t="n">
         <v>1.56</v>
@@ -31431,7 +31431,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP142" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.6899999999999999</v>
@@ -34265,7 +34265,7 @@
         <v>0.9</v>
       </c>
       <c r="AP155" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ155" t="n">
         <v>1.38</v>
@@ -34922,7 +34922,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR158" t="n">
         <v>1.34</v>
@@ -37974,7 +37974,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AR172" t="n">
         <v>1.46</v>
@@ -38189,7 +38189,7 @@
         <v>1.22</v>
       </c>
       <c r="AP173" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ173" t="n">
         <v>1</v>
@@ -40151,7 +40151,7 @@
         <v>0.27</v>
       </c>
       <c r="AP182" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.31</v>
@@ -43936,6 +43936,224 @@
       </c>
       <c r="BP199" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>8309665</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>45957.75</v>
+      </c>
+      <c r="F200" t="n">
+        <v>25</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>1</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>1</v>
+      </c>
+      <c r="L200" t="n">
+        <v>2</v>
+      </c>
+      <c r="M200" t="n">
+        <v>2</v>
+      </c>
+      <c r="N200" t="n">
+        <v>4</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>['17', '69']</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>['83', '90+6']</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R200" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S200" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T200" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U200" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V200" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W200" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X200" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB200" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF200" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG200" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI200" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ200" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK200" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL200" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM200" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN200" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO200" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BP200" t="n">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -43507,7 +43507,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>8309651</v>
+        <v>8309833</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -43527,197 +43527,197 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
+          <t>['7', '72', '90']</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>['46']</t>
-        </is>
-      </c>
       <c r="Q198" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R198" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="S198" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="T198" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="U198" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V198" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="W198" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X198" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ198" t="n">
         <v>10</v>
       </c>
-      <c r="Y198" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z198" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA198" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB198" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC198" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD198" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="AE198" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF198" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG198" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH198" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI198" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AJ198" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AK198" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL198" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AM198" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN198" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO198" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AP198" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ198" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AR198" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS198" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AT198" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU198" t="n">
+      <c r="BA198" t="n">
         <v>3</v>
       </c>
-      <c r="AV198" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW198" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX198" t="n">
+      <c r="BB198" t="n">
         <v>4</v>
       </c>
-      <c r="AY198" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ198" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA198" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB198" t="n">
-        <v>6</v>
-      </c>
       <c r="BC198" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD198" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="BE198" t="n">
         <v>6.75</v>
       </c>
       <c r="BF198" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="BG198" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="BH198" t="n">
-        <v>3.54</v>
+        <v>2.65</v>
       </c>
       <c r="BI198" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM198" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BN198" t="n">
         <v>1.48</v>
       </c>
-      <c r="BJ198" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BK198" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BL198" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BM198" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BN198" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BO198" t="n">
-        <v>2.96</v>
+        <v>3.58</v>
       </c>
       <c r="BP198" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="199">
@@ -43725,7 +43725,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>8309833</v>
+        <v>8309651</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -43745,197 +43745,197 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>1</v>
+      </c>
+      <c r="N199" t="n">
+        <v>1</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R199" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S199" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U199" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V199" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W199" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X199" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU199" t="n">
         <v>3</v>
       </c>
-      <c r="M199" t="n">
-        <v>0</v>
-      </c>
-      <c r="N199" t="n">
-        <v>3</v>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>['7', '72', '90']</t>
-        </is>
-      </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q199" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R199" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S199" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T199" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U199" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V199" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="W199" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X199" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y199" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z199" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA199" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AB199" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AC199" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD199" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE199" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF199" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AG199" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH199" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI199" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ199" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK199" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL199" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM199" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN199" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO199" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP199" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AQ199" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR199" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS199" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AT199" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU199" t="n">
+      <c r="AV199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW199" t="n">
         <v>6</v>
       </c>
-      <c r="AV199" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW199" t="n">
-        <v>8</v>
-      </c>
       <c r="AX199" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY199" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ199" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC199" t="n">
         <v>10</v>
       </c>
-      <c r="BA199" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB199" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC199" t="n">
-        <v>7</v>
-      </c>
       <c r="BD199" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="BE199" t="n">
         <v>6.75</v>
       </c>
       <c r="BF199" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH199" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BI199" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM199" t="n">
         <v>2.24</v>
       </c>
-      <c r="BG199" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BH199" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BI199" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BJ199" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BK199" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BL199" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BM199" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BN199" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="BO199" t="n">
-        <v>3.58</v>
+        <v>2.96</v>
       </c>
       <c r="BP199" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="200">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -43507,7 +43507,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>8309833</v>
+        <v>8309651</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -43527,197 +43527,197 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>1</v>
+      </c>
+      <c r="N198" t="n">
+        <v>1</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R198" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S198" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T198" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V198" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W198" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X198" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU198" t="n">
         <v>3</v>
       </c>
-      <c r="M198" t="n">
-        <v>0</v>
-      </c>
-      <c r="N198" t="n">
-        <v>3</v>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>['7', '72', '90']</t>
-        </is>
-      </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q198" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R198" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S198" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T198" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U198" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V198" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="W198" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X198" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y198" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z198" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA198" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AB198" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AC198" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD198" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE198" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF198" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AG198" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH198" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI198" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ198" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK198" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL198" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM198" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN198" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO198" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP198" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AQ198" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR198" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS198" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AT198" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU198" t="n">
+      <c r="AV198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW198" t="n">
         <v>6</v>
       </c>
-      <c r="AV198" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW198" t="n">
-        <v>8</v>
-      </c>
       <c r="AX198" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY198" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ198" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC198" t="n">
         <v>10</v>
       </c>
-      <c r="BA198" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB198" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC198" t="n">
-        <v>7</v>
-      </c>
       <c r="BD198" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="BE198" t="n">
         <v>6.75</v>
       </c>
       <c r="BF198" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BI198" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM198" t="n">
         <v>2.24</v>
       </c>
-      <c r="BG198" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BH198" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BI198" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BJ198" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BK198" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BL198" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BM198" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BN198" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="BO198" t="n">
-        <v>3.58</v>
+        <v>2.96</v>
       </c>
       <c r="BP198" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="199">
@@ -43725,7 +43725,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>8309651</v>
+        <v>8309833</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -43745,197 +43745,197 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
+          <t>['7', '72', '90']</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>['46']</t>
-        </is>
-      </c>
       <c r="Q199" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R199" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="S199" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="T199" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="U199" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V199" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="W199" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X199" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ199" t="n">
         <v>10</v>
       </c>
-      <c r="Y199" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z199" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA199" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB199" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC199" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD199" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="AE199" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF199" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG199" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH199" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI199" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AJ199" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AK199" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL199" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AM199" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN199" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO199" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AP199" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ199" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AR199" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS199" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AT199" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU199" t="n">
+      <c r="BA199" t="n">
         <v>3</v>
       </c>
-      <c r="AV199" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW199" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX199" t="n">
+      <c r="BB199" t="n">
         <v>4</v>
       </c>
-      <c r="AY199" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ199" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA199" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB199" t="n">
-        <v>6</v>
-      </c>
       <c r="BC199" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD199" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="BE199" t="n">
         <v>6.75</v>
       </c>
       <c r="BF199" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="BG199" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="BH199" t="n">
-        <v>3.54</v>
+        <v>2.65</v>
       </c>
       <c r="BI199" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM199" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BN199" t="n">
         <v>1.48</v>
       </c>
-      <c r="BJ199" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BK199" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BL199" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BM199" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BN199" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BO199" t="n">
-        <v>2.96</v>
+        <v>3.58</v>
       </c>
       <c r="BP199" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="200">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ2" t="n">
         <v>2.46</v>
@@ -1350,7 +1350,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.31</v>
@@ -3748,7 +3748,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>1</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.42</v>
@@ -6797,7 +6797,7 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.46</v>
@@ -7018,7 +7018,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR30" t="n">
         <v>1.59</v>
@@ -7236,7 +7236,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR31" t="n">
         <v>2.2</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ33" t="n">
         <v>1</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.5</v>
@@ -10288,7 +10288,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR45" t="n">
         <v>1.09</v>
@@ -10724,7 +10724,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR47" t="n">
         <v>1.59</v>
@@ -11375,7 +11375,7 @@
         <v>1.67</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.46</v>
@@ -12468,7 +12468,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR55" t="n">
         <v>2.62</v>
@@ -12683,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.5</v>
@@ -12904,7 +12904,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR57" t="n">
         <v>1.17</v>
@@ -13994,7 +13994,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR62" t="n">
         <v>1.58</v>
@@ -15956,7 +15956,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR71" t="n">
         <v>1.29</v>
@@ -16825,7 +16825,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.6899999999999999</v>
@@ -17043,10 +17043,10 @@
         <v>0.2</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR76" t="n">
         <v>1.64</v>
@@ -19444,7 +19444,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR87" t="n">
         <v>1.56</v>
@@ -20316,7 +20316,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR91" t="n">
         <v>1.71</v>
@@ -20531,7 +20531,7 @@
         <v>0.4</v>
       </c>
       <c r="AP92" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.67</v>
@@ -20749,7 +20749,7 @@
         <v>0.83</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.6899999999999999</v>
@@ -22711,7 +22711,7 @@
         <v>1.5</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.83</v>
@@ -23150,7 +23150,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR104" t="n">
         <v>1.69</v>
@@ -24237,7 +24237,7 @@
         <v>0.67</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.64</v>
@@ -24458,7 +24458,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR110" t="n">
         <v>2.01</v>
@@ -25763,7 +25763,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ116" t="n">
         <v>0.83</v>
@@ -27510,7 +27510,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR124" t="n">
         <v>2.02</v>
@@ -27943,7 +27943,7 @@
         <v>0.88</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.38</v>
@@ -28818,7 +28818,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR130" t="n">
         <v>1.53</v>
@@ -29905,7 +29905,7 @@
         <v>1.43</v>
       </c>
       <c r="AP135" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.23</v>
@@ -30341,7 +30341,7 @@
         <v>1.88</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.46</v>
@@ -30562,7 +30562,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR138" t="n">
         <v>1.36</v>
@@ -30995,7 +30995,7 @@
         <v>0.89</v>
       </c>
       <c r="AP140" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.38</v>
@@ -31870,7 +31870,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR144" t="n">
         <v>2</v>
@@ -33832,7 +33832,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR153" t="n">
         <v>1.25</v>
@@ -34486,7 +34486,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR156" t="n">
         <v>1.71</v>
@@ -36009,7 +36009,7 @@
         <v>2.3</v>
       </c>
       <c r="AP163" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ163" t="n">
         <v>2.46</v>
@@ -36663,7 +36663,7 @@
         <v>1.38</v>
       </c>
       <c r="AP166" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.15</v>
@@ -36884,7 +36884,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AR167" t="n">
         <v>1.62</v>
@@ -37756,7 +37756,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR171" t="n">
         <v>1.52</v>
@@ -37971,7 +37971,7 @@
         <v>0.4</v>
       </c>
       <c r="AP172" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.42</v>
@@ -41241,7 +41241,7 @@
         <v>0.73</v>
       </c>
       <c r="AP187" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ187" t="n">
         <v>0.67</v>
@@ -41459,7 +41459,7 @@
         <v>1.33</v>
       </c>
       <c r="AP188" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.46</v>
@@ -41898,7 +41898,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR190" t="n">
         <v>1.4</v>
@@ -44154,6 +44154,442 @@
       </c>
       <c r="BP200" t="n">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>8309650</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>45961.625</v>
+      </c>
+      <c r="F201" t="n">
+        <v>26</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>2</v>
+      </c>
+      <c r="K201" t="n">
+        <v>2</v>
+      </c>
+      <c r="L201" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" t="n">
+        <v>2</v>
+      </c>
+      <c r="N201" t="n">
+        <v>3</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>['22', '40']</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R201" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S201" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="T201" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U201" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="V201" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="W201" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X201" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM201" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN201" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO201" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BP201" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>8309655</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>45961.72916666666</v>
+      </c>
+      <c r="F202" t="n">
+        <v>26</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" t="n">
+        <v>1</v>
+      </c>
+      <c r="L202" t="n">
+        <v>1</v>
+      </c>
+      <c r="M202" t="n">
+        <v>2</v>
+      </c>
+      <c r="N202" t="n">
+        <v>3</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>['15', '70']</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R202" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S202" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T202" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U202" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V202" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W202" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X202" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -44314,13 +44314,13 @@
         <v>7</v>
       </c>
       <c r="AW201" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX201" t="n">
         <v>8</v>
       </c>
       <c r="AY201" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ201" t="n">
         <v>15</v>
@@ -44532,13 +44532,13 @@
         <v>4</v>
       </c>
       <c r="AW202" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX202" t="n">
         <v>3</v>
       </c>
       <c r="AY202" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ202" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP202"/>
+  <dimension ref="A1:BP204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,7 +1786,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.42</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.64</v>
@@ -5489,10 +5489,10 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR23" t="n">
         <v>1.24</v>
@@ -5710,7 +5710,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR24" t="n">
         <v>1.15</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.38</v>
@@ -7672,7 +7672,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR33" t="n">
         <v>1.92</v>
@@ -9416,7 +9416,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR41" t="n">
         <v>1.94</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.31</v>
@@ -10285,7 +10285,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.62</v>
@@ -12901,7 +12901,7 @@
         <v>0.33</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.31</v>
@@ -13773,7 +13773,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ61" t="n">
         <v>2.46</v>
@@ -13991,7 +13991,7 @@
         <v>0.25</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.62</v>
@@ -15302,7 +15302,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR68" t="n">
         <v>1.79</v>
@@ -15517,7 +15517,7 @@
         <v>0.75</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.5</v>
@@ -15738,7 +15738,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR70" t="n">
         <v>1.48</v>
@@ -17261,7 +17261,7 @@
         <v>0.25</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.67</v>
@@ -19226,7 +19226,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR86" t="n">
         <v>1.44</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.46</v>
@@ -20967,7 +20967,7 @@
         <v>0.8</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.15</v>
@@ -22060,7 +22060,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR99" t="n">
         <v>1.34</v>
@@ -22714,7 +22714,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR102" t="n">
         <v>1.56</v>
@@ -23804,7 +23804,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR107" t="n">
         <v>1.67</v>
@@ -24019,7 +24019,7 @@
         <v>1.17</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.23</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.46</v>
@@ -25766,7 +25766,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR116" t="n">
         <v>1.77</v>
@@ -26420,7 +26420,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR119" t="n">
         <v>1.41</v>
@@ -26638,7 +26638,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR120" t="n">
         <v>1.67</v>
@@ -26856,7 +26856,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR121" t="n">
         <v>2.12</v>
@@ -28161,10 +28161,10 @@
         <v>1</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR127" t="n">
         <v>1.6</v>
@@ -28379,7 +28379,7 @@
         <v>1.38</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.46</v>
@@ -29254,7 +29254,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR132" t="n">
         <v>1.66</v>
@@ -30126,7 +30126,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR136" t="n">
         <v>1.33</v>
@@ -31649,7 +31649,7 @@
         <v>1</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.64</v>
@@ -32303,7 +32303,7 @@
         <v>0.89</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.67</v>
@@ -32960,7 +32960,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR149" t="n">
         <v>1.61</v>
@@ -34047,7 +34047,7 @@
         <v>1.78</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.46</v>
@@ -34919,7 +34919,7 @@
         <v>0.44</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.42</v>
@@ -35358,7 +35358,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR160" t="n">
         <v>1.75</v>
@@ -37317,7 +37317,7 @@
         <v>2.36</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ169" t="n">
         <v>2.46</v>
@@ -38192,7 +38192,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR173" t="n">
         <v>2.12</v>
@@ -38407,7 +38407,7 @@
         <v>0.3</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.5</v>
@@ -40372,7 +40372,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR183" t="n">
         <v>1.66</v>
@@ -42116,7 +42116,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ191" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR191" t="n">
         <v>1.44</v>
@@ -42985,7 +42985,7 @@
         <v>0.25</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.31</v>
@@ -43206,7 +43206,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR196" t="n">
         <v>1.53</v>
@@ -43507,7 +43507,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>8309651</v>
+        <v>8309833</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -43527,197 +43527,197 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
+          <t>['7', '72', '90']</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>['46']</t>
-        </is>
-      </c>
       <c r="Q198" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R198" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="S198" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="T198" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="U198" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V198" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="W198" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X198" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ198" t="n">
         <v>10</v>
       </c>
-      <c r="Y198" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z198" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA198" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB198" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC198" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD198" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="AE198" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF198" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG198" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH198" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI198" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AJ198" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AK198" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL198" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AM198" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN198" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO198" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AP198" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ198" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AR198" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS198" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AT198" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU198" t="n">
+      <c r="BA198" t="n">
         <v>3</v>
       </c>
-      <c r="AV198" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW198" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX198" t="n">
+      <c r="BB198" t="n">
         <v>4</v>
       </c>
-      <c r="AY198" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ198" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA198" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB198" t="n">
-        <v>6</v>
-      </c>
       <c r="BC198" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD198" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="BE198" t="n">
         <v>6.75</v>
       </c>
       <c r="BF198" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="BG198" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="BH198" t="n">
-        <v>3.54</v>
+        <v>2.65</v>
       </c>
       <c r="BI198" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM198" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BN198" t="n">
         <v>1.48</v>
       </c>
-      <c r="BJ198" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BK198" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BL198" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BM198" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BN198" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BO198" t="n">
-        <v>2.96</v>
+        <v>3.58</v>
       </c>
       <c r="BP198" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="199">
@@ -43725,7 +43725,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>8309833</v>
+        <v>8309651</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -43745,197 +43745,197 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>1</v>
+      </c>
+      <c r="N199" t="n">
+        <v>1</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R199" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S199" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U199" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V199" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W199" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X199" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU199" t="n">
         <v>3</v>
       </c>
-      <c r="M199" t="n">
-        <v>0</v>
-      </c>
-      <c r="N199" t="n">
-        <v>3</v>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>['7', '72', '90']</t>
-        </is>
-      </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q199" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R199" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S199" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T199" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U199" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V199" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="W199" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X199" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y199" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z199" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA199" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AB199" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AC199" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD199" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE199" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF199" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AG199" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH199" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI199" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ199" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK199" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL199" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM199" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN199" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO199" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP199" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AQ199" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR199" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS199" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AT199" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU199" t="n">
+      <c r="AV199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW199" t="n">
         <v>6</v>
       </c>
-      <c r="AV199" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW199" t="n">
-        <v>8</v>
-      </c>
       <c r="AX199" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY199" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ199" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC199" t="n">
         <v>10</v>
       </c>
-      <c r="BA199" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB199" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC199" t="n">
-        <v>7</v>
-      </c>
       <c r="BD199" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="BE199" t="n">
         <v>6.75</v>
       </c>
       <c r="BF199" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH199" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BI199" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM199" t="n">
         <v>2.24</v>
       </c>
-      <c r="BG199" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BH199" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BI199" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BJ199" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BK199" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BL199" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BM199" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BN199" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="BO199" t="n">
-        <v>3.58</v>
+        <v>2.96</v>
       </c>
       <c r="BP199" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="200">
@@ -44590,6 +44590,442 @@
       </c>
       <c r="BP202" t="n">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>8309820</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>45962.75</v>
+      </c>
+      <c r="F203" t="n">
+        <v>26</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>1</v>
+      </c>
+      <c r="N203" t="n">
+        <v>1</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R203" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S203" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T203" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U203" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V203" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W203" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X203" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB203" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BM203" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN203" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO203" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="BP203" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>8309667</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>45963.52083333334</v>
+      </c>
+      <c r="F204" t="n">
+        <v>26</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>1</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="n">
+        <v>1</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>['90+9']</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="R204" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S204" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U204" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V204" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W204" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X204" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU204" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI204" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ204" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK204" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM204" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN204" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO204" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP204" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP204"/>
+  <dimension ref="A1:BP207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.23</v>
@@ -2440,7 +2440,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.38</v>
@@ -3966,7 +3966,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR16" t="n">
         <v>3.87</v>
@@ -4184,7 +4184,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR19" t="n">
         <v>0.72</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.31</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.15</v>
@@ -5928,7 +5928,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR25" t="n">
         <v>1.21</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.31</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ35" t="n">
         <v>2.46</v>
@@ -8326,7 +8326,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR36" t="n">
         <v>1.35</v>
@@ -8544,7 +8544,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR37" t="n">
         <v>1.67</v>
@@ -8980,7 +8980,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR39" t="n">
         <v>1.57</v>
@@ -9413,7 +9413,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ41" t="n">
         <v>0.92</v>
@@ -10503,7 +10503,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.23</v>
@@ -10939,7 +10939,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.6899999999999999</v>
@@ -11378,7 +11378,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR50" t="n">
         <v>1.74</v>
@@ -11814,7 +11814,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR52" t="n">
         <v>1.81</v>
@@ -12686,7 +12686,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR56" t="n">
         <v>1.62</v>
@@ -13119,7 +13119,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.42</v>
@@ -13337,10 +13337,10 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR59" t="n">
         <v>1.73</v>
@@ -14427,7 +14427,7 @@
         <v>0.25</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.64</v>
@@ -15520,7 +15520,7 @@
         <v>2</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR69" t="n">
         <v>1.22</v>
@@ -16171,7 +16171,7 @@
         <v>1.75</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.46</v>
@@ -16607,10 +16607,10 @@
         <v>1.25</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR74" t="n">
         <v>1.85</v>
@@ -17264,7 +17264,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR77" t="n">
         <v>1.53</v>
@@ -19441,7 +19441,7 @@
         <v>1.4</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.31</v>
@@ -19662,7 +19662,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR88" t="n">
         <v>1.91</v>
@@ -19877,7 +19877,7 @@
         <v>2.17</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.46</v>
@@ -20098,7 +20098,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR90" t="n">
         <v>1.54</v>
@@ -20313,7 +20313,7 @@
         <v>0.17</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.62</v>
@@ -20534,7 +20534,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR92" t="n">
         <v>1.52</v>
@@ -21406,7 +21406,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR96" t="n">
         <v>2.1</v>
@@ -21621,7 +21621,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.23</v>
@@ -22932,7 +22932,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR103" t="n">
         <v>1.38</v>
@@ -23365,7 +23365,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.6899999999999999</v>
@@ -23586,7 +23586,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR106" t="n">
         <v>1.65</v>
@@ -23801,7 +23801,7 @@
         <v>0.8</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.92</v>
@@ -26199,10 +26199,10 @@
         <v>1.14</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR118" t="n">
         <v>1.63</v>
@@ -26635,7 +26635,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ120" t="n">
         <v>1</v>
@@ -27071,7 +27071,7 @@
         <v>0.43</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.42</v>
@@ -27292,7 +27292,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR123" t="n">
         <v>1.36</v>
@@ -27725,7 +27725,7 @@
         <v>0.25</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.31</v>
@@ -28382,7 +28382,7 @@
         <v>2</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR128" t="n">
         <v>1.28</v>
@@ -29033,7 +29033,7 @@
         <v>0.63</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.6899999999999999</v>
@@ -29472,7 +29472,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR133" t="n">
         <v>1.69</v>
@@ -29687,7 +29687,7 @@
         <v>2.13</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ134" t="n">
         <v>2.46</v>
@@ -30777,7 +30777,7 @@
         <v>0.5</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.42</v>
@@ -31216,7 +31216,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR141" t="n">
         <v>1.69</v>
@@ -32306,7 +32306,7 @@
         <v>2</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR146" t="n">
         <v>1.34</v>
@@ -32524,7 +32524,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR147" t="n">
         <v>2.04</v>
@@ -32742,7 +32742,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR148" t="n">
         <v>1.58</v>
@@ -32957,7 +32957,7 @@
         <v>0.89</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ149" t="n">
         <v>1</v>
@@ -35137,7 +35137,7 @@
         <v>0.88</v>
       </c>
       <c r="AP159" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.64</v>
@@ -35576,7 +35576,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR161" t="n">
         <v>1.41</v>
@@ -35794,7 +35794,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR162" t="n">
         <v>1.61</v>
@@ -36227,10 +36227,10 @@
         <v>0.33</v>
       </c>
       <c r="AP164" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR164" t="n">
         <v>1.48</v>
@@ -36881,7 +36881,7 @@
         <v>0.45</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.62</v>
@@ -37753,7 +37753,7 @@
         <v>1.4</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.31</v>
@@ -38410,7 +38410,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR174" t="n">
         <v>1.46</v>
@@ -38843,7 +38843,7 @@
         <v>1.56</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.15</v>
@@ -39500,7 +39500,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR179" t="n">
         <v>1.8</v>
@@ -40587,7 +40587,7 @@
         <v>1.4</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.15</v>
@@ -41244,7 +41244,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ187" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR187" t="n">
         <v>1.52</v>
@@ -41462,7 +41462,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR188" t="n">
         <v>1.55</v>
@@ -42113,7 +42113,7 @@
         <v>0.91</v>
       </c>
       <c r="AP191" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ191" t="n">
         <v>1</v>
@@ -42331,7 +42331,7 @@
         <v>1.25</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.38</v>
@@ -43203,7 +43203,7 @@
         <v>1.09</v>
       </c>
       <c r="AP196" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ196" t="n">
         <v>0.92</v>
@@ -43424,7 +43424,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AR197" t="n">
         <v>1.8</v>
@@ -45026,6 +45026,660 @@
       </c>
       <c r="BP204" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>8309645</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>45963.72916666666</v>
+      </c>
+      <c r="F205" t="n">
+        <v>26</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="n">
+        <v>1</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" t="n">
+        <v>2</v>
+      </c>
+      <c r="N205" t="n">
+        <v>2</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>['35', '47']</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R205" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S205" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V205" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W205" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X205" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM205" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BN205" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO205" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP205" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>8309816</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>45963.72916666666</v>
+      </c>
+      <c r="F206" t="n">
+        <v>26</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>1</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>1</v>
+      </c>
+      <c r="L206" t="n">
+        <v>2</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="n">
+        <v>2</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>['20', '75']</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R206" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S206" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T206" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U206" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V206" t="n">
+        <v>3</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X206" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI206" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ206" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BK206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL206" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BM206" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN206" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BO206" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP206" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>8309668</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>45963.85416666666</v>
+      </c>
+      <c r="F207" t="n">
+        <v>26</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R207" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S207" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T207" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U207" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V207" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W207" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X207" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW207" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX207" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY207" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB207" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC207" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD207" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BE207" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF207" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG207" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH207" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI207" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ207" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK207" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL207" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM207" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN207" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO207" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BP207" t="n">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -45180,22 +45180,22 @@
         <v>3.12</v>
       </c>
       <c r="AU205" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV205" t="n">
         <v>3</v>
       </c>
       <c r="AW205" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX205" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY205" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ205" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA205" t="n">
         <v>8</v>
@@ -45622,13 +45622,13 @@
         <v>1</v>
       </c>
       <c r="AW207" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX207" t="n">
         <v>9</v>
       </c>
       <c r="AY207" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ207" t="n">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -43507,7 +43507,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>8309833</v>
+        <v>8309651</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -43527,197 +43527,197 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>1</v>
+      </c>
+      <c r="N198" t="n">
+        <v>1</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R198" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S198" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T198" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V198" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W198" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X198" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU198" t="n">
         <v>3</v>
       </c>
-      <c r="M198" t="n">
-        <v>0</v>
-      </c>
-      <c r="N198" t="n">
-        <v>3</v>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>['7', '72', '90']</t>
-        </is>
-      </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q198" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R198" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S198" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T198" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U198" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V198" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="W198" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X198" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y198" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z198" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA198" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AB198" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AC198" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD198" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE198" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF198" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AG198" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH198" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI198" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ198" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK198" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL198" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM198" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN198" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO198" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP198" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AQ198" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR198" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS198" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AT198" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU198" t="n">
+      <c r="AV198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW198" t="n">
         <v>6</v>
       </c>
-      <c r="AV198" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW198" t="n">
-        <v>8</v>
-      </c>
       <c r="AX198" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY198" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ198" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC198" t="n">
         <v>10</v>
       </c>
-      <c r="BA198" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB198" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC198" t="n">
-        <v>7</v>
-      </c>
       <c r="BD198" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="BE198" t="n">
         <v>6.75</v>
       </c>
       <c r="BF198" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BI198" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM198" t="n">
         <v>2.24</v>
       </c>
-      <c r="BG198" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BH198" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BI198" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BJ198" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BK198" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BL198" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BM198" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BN198" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="BO198" t="n">
-        <v>3.58</v>
+        <v>2.96</v>
       </c>
       <c r="BP198" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="199">
@@ -43725,7 +43725,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>8309651</v>
+        <v>8309833</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -43745,197 +43745,197 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
+          <t>['7', '72', '90']</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>['46']</t>
-        </is>
-      </c>
       <c r="Q199" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R199" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="S199" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="T199" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="U199" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V199" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="W199" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X199" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ199" t="n">
         <v>10</v>
       </c>
-      <c r="Y199" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z199" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA199" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB199" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC199" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD199" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="AE199" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF199" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG199" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH199" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI199" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AJ199" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AK199" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL199" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AM199" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN199" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO199" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AP199" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ199" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AR199" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS199" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AT199" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU199" t="n">
+      <c r="BA199" t="n">
         <v>3</v>
       </c>
-      <c r="AV199" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW199" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX199" t="n">
+      <c r="BB199" t="n">
         <v>4</v>
       </c>
-      <c r="AY199" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ199" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA199" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB199" t="n">
-        <v>6</v>
-      </c>
       <c r="BC199" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD199" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="BE199" t="n">
         <v>6.75</v>
       </c>
       <c r="BF199" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="BG199" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="BH199" t="n">
-        <v>3.54</v>
+        <v>2.65</v>
       </c>
       <c r="BI199" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM199" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BN199" t="n">
         <v>1.48</v>
       </c>
-      <c r="BJ199" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BK199" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BL199" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BM199" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BN199" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BO199" t="n">
-        <v>2.96</v>
+        <v>3.58</v>
       </c>
       <c r="BP199" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="200">
@@ -45033,7 +45033,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>8309645</v>
+        <v>8309816</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -45053,197 +45053,197 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K205" t="n">
         <v>1</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
         <v>2</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
+          <t>['20', '75']</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P205" t="inlineStr">
-        <is>
-          <t>['35', '47']</t>
-        </is>
-      </c>
       <c r="Q205" t="n">
-        <v>2.58</v>
+        <v>2.05</v>
       </c>
       <c r="R205" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S205" t="n">
-        <v>3.73</v>
+        <v>5.4</v>
       </c>
       <c r="T205" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="U205" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V205" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="W205" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="X205" t="n">
-        <v>6.4</v>
+        <v>9.5</v>
       </c>
       <c r="Y205" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z205" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM205" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AA205" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB205" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AC205" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD205" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE205" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF205" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG205" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH205" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI205" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ205" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK205" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL205" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AM205" t="n">
-        <v>1.63</v>
       </c>
       <c r="AN205" t="n">
         <v>2.5</v>
       </c>
       <c r="AO205" t="n">
-        <v>1.46</v>
+        <v>0.67</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.57</v>
+        <v>0.62</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS205" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI205" t="n">
         <v>1.61</v>
       </c>
-      <c r="AT205" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AU205" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV205" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW205" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX205" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY205" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ205" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA205" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB205" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC205" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD205" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BE205" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BF205" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BG205" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BH205" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI205" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BJ205" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BK205" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BL205" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BM205" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="BN205" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO205" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BP205" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="206">
@@ -45251,7 +45251,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>8309816</v>
+        <v>8309645</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -45271,197 +45271,197 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K206" t="n">
         <v>1</v>
       </c>
       <c r="L206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N206" t="n">
         <v>2</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>['20', '75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35', '47']</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>2.05</v>
+        <v>2.58</v>
       </c>
       <c r="R206" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S206" t="n">
-        <v>5.4</v>
+        <v>3.73</v>
       </c>
       <c r="T206" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="U206" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V206" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="W206" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X206" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL206" t="n">
         <v>1.32</v>
       </c>
-      <c r="X206" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Y206" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z206" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA206" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB206" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AC206" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD206" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE206" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF206" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AG206" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH206" t="n">
+      <c r="AM206" t="n">
         <v>1.63</v>
-      </c>
-      <c r="AI206" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AJ206" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AK206" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AL206" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM206" t="n">
-        <v>2.1</v>
       </c>
       <c r="AN206" t="n">
         <v>2.5</v>
       </c>
       <c r="AO206" t="n">
-        <v>0.67</v>
+        <v>1.46</v>
       </c>
       <c r="AP206" t="n">
-        <v>2.54</v>
+        <v>2.31</v>
       </c>
       <c r="AQ206" t="n">
-        <v>0.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR206" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BG206" t="n">
         <v>1.38</v>
       </c>
-      <c r="AS206" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AT206" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AU206" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV206" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW206" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX206" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY206" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ206" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA206" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB206" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC206" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD206" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BE206" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF206" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="BG206" t="n">
-        <v>1.34</v>
-      </c>
       <c r="BH206" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="BI206" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="BJ206" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BK206" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BL206" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BM206" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="BN206" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="BO206" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BP206" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="207">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -43507,7 +43507,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>8309651</v>
+        <v>8309833</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -43527,197 +43527,197 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
+          <t>['7', '72', '90']</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P198" t="inlineStr">
-        <is>
-          <t>['46']</t>
-        </is>
-      </c>
       <c r="Q198" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R198" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="S198" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="T198" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="U198" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V198" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="W198" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X198" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ198" t="n">
         <v>10</v>
       </c>
-      <c r="Y198" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z198" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA198" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB198" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC198" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD198" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="AE198" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF198" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG198" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH198" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI198" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AJ198" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AK198" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL198" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AM198" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN198" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO198" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AP198" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ198" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AR198" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS198" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AT198" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU198" t="n">
+      <c r="BA198" t="n">
         <v>3</v>
       </c>
-      <c r="AV198" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW198" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX198" t="n">
+      <c r="BB198" t="n">
         <v>4</v>
       </c>
-      <c r="AY198" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ198" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA198" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB198" t="n">
-        <v>6</v>
-      </c>
       <c r="BC198" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD198" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="BE198" t="n">
         <v>6.75</v>
       </c>
       <c r="BF198" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="BG198" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="BH198" t="n">
-        <v>3.54</v>
+        <v>2.65</v>
       </c>
       <c r="BI198" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM198" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BN198" t="n">
         <v>1.48</v>
       </c>
-      <c r="BJ198" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="BK198" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BL198" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BM198" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BN198" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BO198" t="n">
-        <v>2.96</v>
+        <v>3.58</v>
       </c>
       <c r="BP198" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="199">
@@ -43725,7 +43725,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>8309833</v>
+        <v>8309651</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -43745,197 +43745,197 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>1</v>
+      </c>
+      <c r="N199" t="n">
+        <v>1</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R199" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S199" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U199" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V199" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W199" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X199" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU199" t="n">
         <v>3</v>
       </c>
-      <c r="M199" t="n">
-        <v>0</v>
-      </c>
-      <c r="N199" t="n">
-        <v>3</v>
-      </c>
-      <c r="O199" t="inlineStr">
-        <is>
-          <t>['7', '72', '90']</t>
-        </is>
-      </c>
-      <c r="P199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="Q199" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R199" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S199" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T199" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U199" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V199" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="W199" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X199" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y199" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z199" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA199" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AB199" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AC199" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD199" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE199" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF199" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AG199" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH199" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI199" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ199" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK199" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AL199" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AM199" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN199" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO199" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP199" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AQ199" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR199" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AS199" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AT199" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU199" t="n">
+      <c r="AV199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW199" t="n">
         <v>6</v>
       </c>
-      <c r="AV199" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW199" t="n">
-        <v>8</v>
-      </c>
       <c r="AX199" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY199" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ199" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC199" t="n">
         <v>10</v>
       </c>
-      <c r="BA199" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB199" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC199" t="n">
-        <v>7</v>
-      </c>
       <c r="BD199" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="BE199" t="n">
         <v>6.75</v>
       </c>
       <c r="BF199" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH199" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BI199" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM199" t="n">
         <v>2.24</v>
       </c>
-      <c r="BG199" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BH199" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BI199" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BJ199" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BK199" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BL199" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BM199" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BN199" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="BO199" t="n">
-        <v>3.58</v>
+        <v>2.96</v>
       </c>
       <c r="BP199" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="200">
@@ -45033,7 +45033,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>8309816</v>
+        <v>8309645</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -45053,197 +45053,197 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K205" t="n">
         <v>1</v>
       </c>
       <c r="L205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N205" t="n">
         <v>2</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>['20', '75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35', '47']</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>2.05</v>
+        <v>2.58</v>
       </c>
       <c r="R205" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S205" t="n">
-        <v>5.4</v>
+        <v>3.73</v>
       </c>
       <c r="T205" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="U205" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V205" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="W205" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X205" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL205" t="n">
         <v>1.32</v>
       </c>
-      <c r="X205" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Y205" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z205" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA205" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB205" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AC205" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD205" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE205" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF205" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AG205" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH205" t="n">
+      <c r="AM205" t="n">
         <v>1.63</v>
-      </c>
-      <c r="AI205" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AJ205" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AK205" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AL205" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM205" t="n">
-        <v>2.1</v>
       </c>
       <c r="AN205" t="n">
         <v>2.5</v>
       </c>
       <c r="AO205" t="n">
-        <v>0.67</v>
+        <v>1.46</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.54</v>
+        <v>2.31</v>
       </c>
       <c r="AQ205" t="n">
-        <v>0.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR205" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BG205" t="n">
         <v>1.38</v>
       </c>
-      <c r="AS205" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AT205" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AU205" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW205" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX205" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY205" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ205" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA205" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB205" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC205" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD205" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BE205" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF205" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="BG205" t="n">
-        <v>1.34</v>
-      </c>
       <c r="BH205" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="BI205" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="BJ205" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BK205" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BL205" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BM205" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="BN205" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="BO205" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BP205" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="206">
@@ -45251,7 +45251,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>8309645</v>
+        <v>8309816</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -45271,197 +45271,197 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" t="n">
         <v>1</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
         <v>2</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
+          <t>['20', '75']</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>['35', '47']</t>
-        </is>
-      </c>
       <c r="Q206" t="n">
-        <v>2.58</v>
+        <v>2.05</v>
       </c>
       <c r="R206" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S206" t="n">
-        <v>3.73</v>
+        <v>5.4</v>
       </c>
       <c r="T206" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="U206" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V206" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="W206" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="X206" t="n">
-        <v>6.4</v>
+        <v>9.5</v>
       </c>
       <c r="Y206" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z206" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM206" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AA206" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB206" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AC206" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD206" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE206" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF206" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG206" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH206" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI206" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ206" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK206" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL206" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AM206" t="n">
-        <v>1.63</v>
       </c>
       <c r="AN206" t="n">
         <v>2.5</v>
       </c>
       <c r="AO206" t="n">
-        <v>1.46</v>
+        <v>0.67</v>
       </c>
       <c r="AP206" t="n">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.57</v>
+        <v>0.62</v>
       </c>
       <c r="AR206" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS206" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI206" t="n">
         <v>1.61</v>
       </c>
-      <c r="AT206" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AU206" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV206" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW206" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX206" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY206" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ206" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA206" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB206" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC206" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD206" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BE206" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BF206" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BG206" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BH206" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI206" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BJ206" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BK206" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BL206" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BM206" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="BN206" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO206" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BP206" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="207">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP207"/>
+  <dimension ref="A1:BP208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.31</v>
@@ -3312,7 +3312,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.23</v>
@@ -6582,7 +6582,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR28" t="n">
         <v>1.8</v>
@@ -8759,7 +8759,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.15</v>
@@ -10070,7 +10070,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR44" t="n">
         <v>2.2</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.62</v>
@@ -13122,7 +13122,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR58" t="n">
         <v>1.48</v>
@@ -14648,7 +14648,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR65" t="n">
         <v>1.44</v>
@@ -15299,7 +15299,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.92</v>
@@ -21839,7 +21839,7 @@
         <v>0.83</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.38</v>
@@ -22496,7 +22496,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR101" t="n">
         <v>1.38</v>
@@ -23147,7 +23147,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.62</v>
@@ -25548,7 +25548,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR115" t="n">
         <v>1.48</v>
@@ -27074,7 +27074,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR122" t="n">
         <v>1.56</v>
@@ -29469,7 +29469,7 @@
         <v>0.43</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.54</v>
@@ -30780,7 +30780,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR139" t="n">
         <v>1.56</v>
@@ -32085,7 +32085,7 @@
         <v>0.22</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.31</v>
@@ -34922,7 +34922,7 @@
         <v>2</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR158" t="n">
         <v>1.34</v>
@@ -35355,7 +35355,7 @@
         <v>0.9</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ160" t="n">
         <v>1</v>
@@ -37974,7 +37974,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR172" t="n">
         <v>1.46</v>
@@ -39497,7 +39497,7 @@
         <v>1.18</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ179" t="n">
         <v>1.57</v>
@@ -42549,7 +42549,7 @@
         <v>0.7</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ193" t="n">
         <v>0.64</v>
@@ -44078,7 +44078,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AR200" t="n">
         <v>2.17</v>
@@ -45680,6 +45680,224 @@
       </c>
       <c r="BP207" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>8309624</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>45964.79166666666</v>
+      </c>
+      <c r="F208" t="n">
+        <v>26</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>1</v>
+      </c>
+      <c r="L208" t="n">
+        <v>2</v>
+      </c>
+      <c r="M208" t="n">
+        <v>1</v>
+      </c>
+      <c r="N208" t="n">
+        <v>3</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>['36', '59']</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R208" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S208" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T208" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U208" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="V208" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="W208" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X208" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ208" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT208" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU208" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC208" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD208" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE208" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF208" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BG208" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH208" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI208" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ208" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK208" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL208" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM208" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BN208" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO208" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BP208" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP208"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.15</v>
@@ -2004,7 +2004,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.62</v>
@@ -7454,7 +7454,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR32" t="n">
         <v>1.89</v>
@@ -11596,7 +11596,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR51" t="n">
         <v>1.33</v>
@@ -12465,7 +12465,7 @@
         <v>0.33</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.62</v>
@@ -14430,7 +14430,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR64" t="n">
         <v>1.6</v>
@@ -16389,7 +16389,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.38</v>
@@ -18351,7 +18351,7 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.6899999999999999</v>
@@ -18572,7 +18572,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR83" t="n">
         <v>1.51</v>
@@ -21403,7 +21403,7 @@
         <v>1.33</v>
       </c>
       <c r="AP96" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.57</v>
@@ -24240,7 +24240,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR109" t="n">
         <v>1.46</v>
@@ -25109,7 +25109,7 @@
         <v>0.29</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.31</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ121" t="n">
         <v>1</v>
@@ -31652,7 +31652,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR143" t="n">
         <v>1.54</v>
@@ -31867,7 +31867,7 @@
         <v>1.38</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.31</v>
@@ -32521,7 +32521,7 @@
         <v>0.38</v>
       </c>
       <c r="AP147" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.54</v>
@@ -34701,7 +34701,7 @@
         <v>1.11</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.23</v>
@@ -35140,7 +35140,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR159" t="n">
         <v>1.54</v>
@@ -39064,7 +39064,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ177" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR177" t="n">
         <v>1.29</v>
@@ -41023,7 +41023,7 @@
         <v>1.58</v>
       </c>
       <c r="AP186" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.46</v>
@@ -42552,7 +42552,7 @@
         <v>2</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR193" t="n">
         <v>1.74</v>
@@ -45404,13 +45404,13 @@
         <v>3</v>
       </c>
       <c r="AW206" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX206" t="n">
         <v>7</v>
       </c>
       <c r="AY206" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ206" t="n">
         <v>10</v>
@@ -45898,6 +45898,224 @@
       </c>
       <c r="BP208" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>8309727</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>45966.72916666666</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>2</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>2</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>['53', '90+2']</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>2</v>
+      </c>
+      <c r="R209" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S209" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T209" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U209" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="V209" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="W209" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X209" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT209" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AU209" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV209" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX209" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY209" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC209" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BE209" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF209" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BG209" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH209" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI209" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ209" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK209" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL209" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM209" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN209" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO209" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BP209" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -46058,16 +46058,16 @@
         <v>4</v>
       </c>
       <c r="AW209" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX209" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY209" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ209" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA209" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.54</v>
@@ -2876,7 +2876,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR21" t="n">
         <v>1.26</v>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.57</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.6899999999999999</v>
@@ -9852,7 +9852,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR43" t="n">
         <v>1.59</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.31</v>
@@ -12250,7 +12250,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR54" t="n">
         <v>1.19</v>
@@ -14209,7 +14209,7 @@
         <v>1</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.23</v>
@@ -15084,7 +15084,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR67" t="n">
         <v>1.92</v>
@@ -17479,7 +17479,7 @@
         <v>1.6</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ78" t="n">
         <v>2.46</v>
@@ -19008,7 +19008,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR85" t="n">
         <v>1.34</v>
@@ -22057,7 +22057,7 @@
         <v>1</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ99" t="n">
         <v>1</v>
@@ -22278,7 +22278,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR100" t="n">
         <v>1.51</v>
@@ -24673,7 +24673,7 @@
         <v>0.86</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.38</v>
@@ -25112,7 +25112,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR113" t="n">
         <v>2.07</v>
@@ -27728,7 +27728,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR125" t="n">
         <v>1.52</v>
@@ -30123,7 +30123,7 @@
         <v>1</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ136" t="n">
         <v>0.92</v>
@@ -32088,7 +32088,7 @@
         <v>2</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR145" t="n">
         <v>1.7</v>
@@ -33614,7 +33614,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR152" t="n">
         <v>1.48</v>
@@ -33829,7 +33829,7 @@
         <v>0.4</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.62</v>
@@ -37099,7 +37099,7 @@
         <v>1.6</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.46</v>
@@ -39061,7 +39061,7 @@
         <v>0.78</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ177" t="n">
         <v>0.58</v>
@@ -40154,7 +40154,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR182" t="n">
         <v>2.12</v>
@@ -42988,7 +42988,7 @@
         <v>2</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="AR195" t="n">
         <v>1.33</v>
@@ -43857,7 +43857,7 @@
         <v>1.25</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.15</v>
@@ -46116,6 +46116,224 @@
       </c>
       <c r="BP209" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>8309654</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>45968.83333333334</v>
+      </c>
+      <c r="F210" t="n">
+        <v>27</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>1</v>
+      </c>
+      <c r="J210" t="n">
+        <v>2</v>
+      </c>
+      <c r="K210" t="n">
+        <v>3</v>
+      </c>
+      <c r="L210" t="n">
+        <v>1</v>
+      </c>
+      <c r="M210" t="n">
+        <v>2</v>
+      </c>
+      <c r="N210" t="n">
+        <v>3</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>['9', '33']</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R210" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S210" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T210" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U210" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="V210" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W210" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X210" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB210" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC210" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE210" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="BF210" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BG210" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH210" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BI210" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BJ210" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BK210" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BL210" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BM210" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BN210" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BO210" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="BP210" t="n">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP210"/>
+  <dimension ref="A1:BP212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.46</v>
@@ -3094,7 +3094,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.54</v>
@@ -5492,7 +5492,7 @@
         <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR23" t="n">
         <v>1.24</v>
@@ -6364,7 +6364,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR27" t="n">
         <v>1.93</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.62</v>
@@ -9631,10 +9631,10 @@
         <v>0.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR42" t="n">
         <v>1.19</v>
@@ -11160,7 +11160,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR49" t="n">
         <v>1.45</v>
@@ -11593,7 +11593,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.58</v>
@@ -12029,7 +12029,7 @@
         <v>1</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.15</v>
@@ -15738,7 +15738,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR70" t="n">
         <v>1.48</v>
@@ -15953,7 +15953,7 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.31</v>
@@ -16392,7 +16392,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR73" t="n">
         <v>2.4</v>
@@ -17918,7 +17918,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR80" t="n">
         <v>1.8</v>
@@ -18569,7 +18569,7 @@
         <v>0.2</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.58</v>
@@ -19005,7 +19005,7 @@
         <v>0.4</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.5</v>
@@ -21185,7 +21185,7 @@
         <v>1.83</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ95" t="n">
         <v>2.46</v>
@@ -21842,7 +21842,7 @@
         <v>2</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR98" t="n">
         <v>1.82</v>
@@ -22060,7 +22060,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR99" t="n">
         <v>1.34</v>
@@ -22493,7 +22493,7 @@
         <v>0.2</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ101" t="n">
         <v>0.38</v>
@@ -22714,7 +22714,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR102" t="n">
         <v>1.56</v>
@@ -24676,7 +24676,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR111" t="n">
         <v>1.4</v>
@@ -24891,7 +24891,7 @@
         <v>2</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ112" t="n">
         <v>2.46</v>
@@ -25545,7 +25545,7 @@
         <v>0.33</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.38</v>
@@ -25766,7 +25766,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR116" t="n">
         <v>1.77</v>
@@ -26417,7 +26417,7 @@
         <v>0.67</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.92</v>
@@ -26638,7 +26638,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR120" t="n">
         <v>1.67</v>
@@ -26856,7 +26856,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR121" t="n">
         <v>2.12</v>
@@ -27289,7 +27289,7 @@
         <v>1.14</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.62</v>
@@ -27946,7 +27946,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR126" t="n">
         <v>1.72</v>
@@ -28815,7 +28815,7 @@
         <v>1.14</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.31</v>
@@ -29254,7 +29254,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR132" t="n">
         <v>1.66</v>
@@ -30559,7 +30559,7 @@
         <v>0.44</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.62</v>
@@ -30998,7 +30998,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR140" t="n">
         <v>1.45</v>
@@ -32739,7 +32739,7 @@
         <v>1.22</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.57</v>
@@ -32960,7 +32960,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR149" t="n">
         <v>1.61</v>
@@ -33611,7 +33611,7 @@
         <v>0.2</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.5</v>
@@ -34268,7 +34268,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR155" t="n">
         <v>2.11</v>
@@ -35358,7 +35358,7 @@
         <v>2</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR160" t="n">
         <v>1.75</v>
@@ -36445,7 +36445,7 @@
         <v>0.6</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.6899999999999999</v>
@@ -39279,7 +39279,7 @@
         <v>1.18</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.23</v>
@@ -39936,7 +39936,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR181" t="n">
         <v>1.4</v>
@@ -40369,7 +40369,7 @@
         <v>1.1</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ183" t="n">
         <v>0.92</v>
@@ -40805,7 +40805,7 @@
         <v>0.75</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ185" t="n">
         <v>0.6899999999999999</v>
@@ -41677,7 +41677,7 @@
         <v>1.27</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.15</v>
@@ -42116,7 +42116,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR191" t="n">
         <v>1.44</v>
@@ -42334,7 +42334,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AR192" t="n">
         <v>1.65</v>
@@ -42767,7 +42767,7 @@
         <v>1.33</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ194" t="n">
         <v>1.23</v>
@@ -44732,7 +44732,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR203" t="n">
         <v>1.44</v>
@@ -46334,6 +46334,442 @@
       </c>
       <c r="BP210" t="n">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>8309834</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>45969.52083333334</v>
+      </c>
+      <c r="F211" t="n">
+        <v>27</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>1</v>
+      </c>
+      <c r="N211" t="n">
+        <v>1</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>4</v>
+      </c>
+      <c r="R211" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S211" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T211" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U211" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V211" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W211" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X211" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB211" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC211" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BE211" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF211" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG211" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH211" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI211" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ211" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BK211" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL211" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM211" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN211" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO211" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP211" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>8309688</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>45969.625</v>
+      </c>
+      <c r="F212" t="n">
+        <v>27</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" t="n">
+        <v>2</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="n">
+        <v>2</v>
+      </c>
+      <c r="N212" t="n">
+        <v>3</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>['28', '79']</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>4</v>
+      </c>
+      <c r="R212" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S212" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T212" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U212" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V212" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="W212" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X212" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU212" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV212" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB212" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC212" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE212" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF212" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI212" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ212" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK212" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL212" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM212" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN212" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO212" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP212" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP212"/>
+  <dimension ref="A1:BP216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.6899999999999999</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.31</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.58</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.62</v>
@@ -4402,7 +4402,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR18" t="n">
         <v>1.83</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR20" t="n">
         <v>1.85</v>
@@ -5274,7 +5274,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.14</v>
@@ -6582,7 +6582,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR28" t="n">
         <v>1.8</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.62</v>
@@ -8108,7 +8108,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ35" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR35" t="n">
         <v>2.22</v>
@@ -8759,10 +8759,10 @@
         <v>1.5</v>
       </c>
       <c r="AP38" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR38" t="n">
         <v>1.81</v>
@@ -10067,10 +10067,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR44" t="n">
         <v>2.2</v>
@@ -10285,7 +10285,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.62</v>
@@ -10506,7 +10506,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR46" t="n">
         <v>2.04</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.62</v>
@@ -12032,7 +12032,7 @@
         <v>1</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR53" t="n">
         <v>1.15</v>
@@ -12465,7 +12465,7 @@
         <v>0.33</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ55" t="n">
         <v>0.62</v>
@@ -12901,7 +12901,7 @@
         <v>0.33</v>
       </c>
       <c r="AP57" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.31</v>
@@ -13122,7 +13122,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR58" t="n">
         <v>1.48</v>
@@ -13555,7 +13555,7 @@
         <v>2.33</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.46</v>
@@ -13776,7 +13776,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR61" t="n">
         <v>1.7</v>
@@ -14212,7 +14212,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR63" t="n">
         <v>1.48</v>
@@ -14648,7 +14648,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR65" t="n">
         <v>1.44</v>
@@ -14866,7 +14866,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ66" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR66" t="n">
         <v>2.02</v>
@@ -15081,7 +15081,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.5</v>
@@ -15299,7 +15299,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.92</v>
@@ -15517,7 +15517,7 @@
         <v>0.75</v>
       </c>
       <c r="AP69" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.54</v>
@@ -16389,7 +16389,7 @@
         <v>1.25</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.5</v>
@@ -17482,7 +17482,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ78" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR78" t="n">
         <v>1.36</v>
@@ -17700,7 +17700,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR79" t="n">
         <v>1.49</v>
@@ -17915,7 +17915,7 @@
         <v>1</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.5</v>
@@ -18351,7 +18351,7 @@
         <v>1</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ82" t="n">
         <v>0.6899999999999999</v>
@@ -18790,7 +18790,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR84" t="n">
         <v>1.8</v>
@@ -20967,10 +20967,10 @@
         <v>0.8</v>
       </c>
       <c r="AP94" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR94" t="n">
         <v>1.19</v>
@@ -21188,7 +21188,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ95" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR95" t="n">
         <v>1.55</v>
@@ -21403,7 +21403,7 @@
         <v>1.33</v>
       </c>
       <c r="AP96" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.57</v>
@@ -21624,7 +21624,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR97" t="n">
         <v>1.61</v>
@@ -21839,7 +21839,7 @@
         <v>0.83</v>
       </c>
       <c r="AP98" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.5</v>
@@ -22496,7 +22496,7 @@
         <v>1</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR101" t="n">
         <v>1.38</v>
@@ -23147,7 +23147,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.62</v>
@@ -23583,7 +23583,7 @@
         <v>0.5</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.54</v>
@@ -24022,7 +24022,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR108" t="n">
         <v>1.53</v>
@@ -24894,7 +24894,7 @@
         <v>1</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR112" t="n">
         <v>1.51</v>
@@ -25109,7 +25109,7 @@
         <v>0.29</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.5</v>
@@ -25327,7 +25327,7 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.46</v>
@@ -25548,7 +25548,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR115" t="n">
         <v>1.48</v>
@@ -25984,7 +25984,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR117" t="n">
         <v>1.61</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ121" t="n">
         <v>1.14</v>
@@ -27074,7 +27074,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR122" t="n">
         <v>1.56</v>
@@ -28379,7 +28379,7 @@
         <v>1.38</v>
       </c>
       <c r="AP128" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.57</v>
@@ -28600,7 +28600,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR129" t="n">
         <v>1.39</v>
@@ -29251,7 +29251,7 @@
         <v>0.88</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.14</v>
@@ -29469,7 +29469,7 @@
         <v>0.43</v>
       </c>
       <c r="AP133" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.54</v>
@@ -29690,7 +29690,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ134" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR134" t="n">
         <v>1.62</v>
@@ -29908,7 +29908,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR135" t="n">
         <v>1.46</v>
@@ -30780,7 +30780,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR139" t="n">
         <v>1.56</v>
@@ -31213,7 +31213,7 @@
         <v>1</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.62</v>
@@ -31867,7 +31867,7 @@
         <v>1.38</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.31</v>
@@ -32085,7 +32085,7 @@
         <v>0.22</v>
       </c>
       <c r="AP145" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.5</v>
@@ -32303,7 +32303,7 @@
         <v>0.89</v>
       </c>
       <c r="AP146" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.62</v>
@@ -32521,7 +32521,7 @@
         <v>0.38</v>
       </c>
       <c r="AP147" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.54</v>
@@ -33178,7 +33178,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ150" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR150" t="n">
         <v>1.59</v>
@@ -33396,7 +33396,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR151" t="n">
         <v>1.38</v>
@@ -34483,7 +34483,7 @@
         <v>1.56</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.31</v>
@@ -34701,10 +34701,10 @@
         <v>1.11</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR157" t="n">
         <v>2.07</v>
@@ -34919,10 +34919,10 @@
         <v>0.44</v>
       </c>
       <c r="AP158" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR158" t="n">
         <v>1.34</v>
@@ -35355,7 +35355,7 @@
         <v>0.9</v>
       </c>
       <c r="AP160" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.14</v>
@@ -36012,7 +36012,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ163" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR163" t="n">
         <v>1.6</v>
@@ -36666,7 +36666,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR166" t="n">
         <v>1.48</v>
@@ -37317,10 +37317,10 @@
         <v>2.36</v>
       </c>
       <c r="AP169" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ169" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR169" t="n">
         <v>1.36</v>
@@ -37535,10 +37535,10 @@
         <v>1.3</v>
       </c>
       <c r="AP170" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR170" t="n">
         <v>1.74</v>
@@ -37974,7 +37974,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR172" t="n">
         <v>1.46</v>
@@ -38846,7 +38846,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR176" t="n">
         <v>1.51</v>
@@ -39282,7 +39282,7 @@
         <v>1</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR178" t="n">
         <v>1.54</v>
@@ -39497,7 +39497,7 @@
         <v>1.18</v>
       </c>
       <c r="AP179" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ179" t="n">
         <v>1.57</v>
@@ -40590,7 +40590,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR184" t="n">
         <v>1.53</v>
@@ -41023,7 +41023,7 @@
         <v>1.58</v>
       </c>
       <c r="AP186" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.46</v>
@@ -41680,7 +41680,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR189" t="n">
         <v>1.64</v>
@@ -42549,7 +42549,7 @@
         <v>0.7</v>
       </c>
       <c r="AP193" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ193" t="n">
         <v>0.58</v>
@@ -42770,7 +42770,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AR194" t="n">
         <v>1.56</v>
@@ -42985,7 +42985,7 @@
         <v>0.25</v>
       </c>
       <c r="AP195" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ195" t="n">
         <v>0.5</v>
@@ -43639,10 +43639,10 @@
         <v>2.42</v>
       </c>
       <c r="AP198" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ198" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AR198" t="n">
         <v>1.8</v>
@@ -43860,7 +43860,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR199" t="n">
         <v>1.28</v>
@@ -44078,7 +44078,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR200" t="n">
         <v>2.17</v>
@@ -44947,7 +44947,7 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ204" t="n">
         <v>0.92</v>
@@ -45819,10 +45819,10 @@
         <v>0.42</v>
       </c>
       <c r="AP208" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="AR208" t="n">
         <v>1.72</v>
@@ -46037,7 +46037,7 @@
         <v>0.64</v>
       </c>
       <c r="AP209" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ209" t="n">
         <v>0.58</v>
@@ -46706,7 +46706,7 @@
         <v>2.84</v>
       </c>
       <c r="AU212" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV212" t="n">
         <v>4</v>
@@ -46718,7 +46718,7 @@
         <v>6</v>
       </c>
       <c r="AY212" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ212" t="n">
         <v>10</v>
@@ -46770,6 +46770,878 @@
       </c>
       <c r="BP212" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>8309658</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>45969.72916666666</v>
+      </c>
+      <c r="F213" t="n">
+        <v>27</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>1</v>
+      </c>
+      <c r="M213" t="n">
+        <v>2</v>
+      </c>
+      <c r="N213" t="n">
+        <v>3</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>['68', '86']</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R213" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S213" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T213" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U213" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V213" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="W213" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X213" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV213" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY213" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA213" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB213" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC213" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BE213" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BF213" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH213" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BI213" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BJ213" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BK213" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BM213" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BN213" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO213" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="BP213" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8309647</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>45969.85416666666</v>
+      </c>
+      <c r="F214" t="n">
+        <v>27</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" t="n">
+        <v>2</v>
+      </c>
+      <c r="L214" t="n">
+        <v>4</v>
+      </c>
+      <c r="M214" t="n">
+        <v>2</v>
+      </c>
+      <c r="N214" t="n">
+        <v>6</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>['12', '75', '80', '90+9']</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>['37', '64']</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S214" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U214" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V214" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X214" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8309666</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>45970.625</v>
+      </c>
+      <c r="F215" t="n">
+        <v>27</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" t="n">
+        <v>2</v>
+      </c>
+      <c r="M215" t="n">
+        <v>1</v>
+      </c>
+      <c r="N215" t="n">
+        <v>3</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>['20', '72']</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R215" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S215" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U215" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V215" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X215" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>8309691</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>45970.72916666666</v>
+      </c>
+      <c r="F216" t="n">
+        <v>27</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>1</v>
+      </c>
+      <c r="J216" t="n">
+        <v>2</v>
+      </c>
+      <c r="K216" t="n">
+        <v>3</v>
+      </c>
+      <c r="L216" t="n">
+        <v>4</v>
+      </c>
+      <c r="M216" t="n">
+        <v>3</v>
+      </c>
+      <c r="N216" t="n">
+        <v>7</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>['39', '46', '56', '67']</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>['11', '15', '65']</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R216" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="S216" t="n">
+        <v>6</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U216" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V216" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X216" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB216" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN216" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO216" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP216"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2004,7 +2004,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.62</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.92</v>
@@ -7454,7 +7454,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR32" t="n">
         <v>1.89</v>
@@ -8541,7 +8541,7 @@
         <v>2</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.57</v>
@@ -11157,7 +11157,7 @@
         <v>1.33</v>
       </c>
       <c r="AP49" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.5</v>
@@ -11596,7 +11596,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR51" t="n">
         <v>1.33</v>
@@ -14430,7 +14430,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR64" t="n">
         <v>1.6</v>
@@ -14645,7 +14645,7 @@
         <v>0.25</v>
       </c>
       <c r="AP65" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.36</v>
@@ -17697,7 +17697,7 @@
         <v>0.75</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.14</v>
@@ -18572,7 +18572,7 @@
         <v>1</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR83" t="n">
         <v>1.51</v>
@@ -22275,7 +22275,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.5</v>
@@ -24240,7 +24240,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR109" t="n">
         <v>1.46</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.07</v>
@@ -31652,7 +31652,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR143" t="n">
         <v>1.54</v>
@@ -33175,7 +33175,7 @@
         <v>2.22</v>
       </c>
       <c r="AP150" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ150" t="n">
         <v>2.5</v>
@@ -35140,7 +35140,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR159" t="n">
         <v>1.54</v>
@@ -35791,7 +35791,7 @@
         <v>0.8</v>
       </c>
       <c r="AP162" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.62</v>
@@ -38625,7 +38625,7 @@
         <v>1.73</v>
       </c>
       <c r="AP175" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ175" t="n">
         <v>1.46</v>
@@ -39064,7 +39064,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ177" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR177" t="n">
         <v>1.29</v>
@@ -39715,7 +39715,7 @@
         <v>0.82</v>
       </c>
       <c r="AP180" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ180" t="n">
         <v>0.6899999999999999</v>
@@ -42552,7 +42552,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR193" t="n">
         <v>1.74</v>
@@ -43421,7 +43421,7 @@
         <v>0.55</v>
       </c>
       <c r="AP197" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AQ197" t="n">
         <v>0.54</v>
@@ -46040,7 +46040,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ209" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AR209" t="n">
         <v>2</v>
@@ -47642,6 +47642,224 @@
       </c>
       <c r="BP216" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>8309826</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>45970.83333333334</v>
+      </c>
+      <c r="F217" t="n">
+        <v>27</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>2</v>
+      </c>
+      <c r="K217" t="n">
+        <v>2</v>
+      </c>
+      <c r="L217" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="n">
+        <v>2</v>
+      </c>
+      <c r="N217" t="n">
+        <v>3</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>['15', '39']</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S217" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U217" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V217" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X217" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BM217" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN217" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BO217" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP217" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -47360,19 +47360,19 @@
         <v>2.52</v>
       </c>
       <c r="AU215" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV215" t="n">
         <v>6</v>
       </c>
       <c r="AW215" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX215" t="n">
         <v>6</v>
       </c>
       <c r="AY215" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ215" t="n">
         <v>12</v>
@@ -47578,19 +47578,19 @@
         <v>3.17</v>
       </c>
       <c r="AU216" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV216" t="n">
         <v>5</v>
       </c>
       <c r="AW216" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX216" t="n">
         <v>6</v>
       </c>
       <c r="AY216" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AZ216" t="n">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -45033,7 +45033,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>8309816</v>
+        <v>8309645</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -45053,197 +45053,197 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K205" t="n">
         <v>1</v>
       </c>
       <c r="L205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N205" t="n">
         <v>2</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>['20', '75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35', '47']</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>2.05</v>
+        <v>2.58</v>
       </c>
       <c r="R205" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S205" t="n">
-        <v>5.4</v>
+        <v>3.73</v>
       </c>
       <c r="T205" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="U205" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V205" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="W205" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X205" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL205" t="n">
         <v>1.32</v>
       </c>
-      <c r="X205" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="Y205" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z205" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA205" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB205" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AC205" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD205" t="n">
-        <v>7</v>
-      </c>
-      <c r="AE205" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF205" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AG205" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH205" t="n">
+      <c r="AM205" t="n">
         <v>1.63</v>
-      </c>
-      <c r="AI205" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AJ205" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AK205" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AL205" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AM205" t="n">
-        <v>2.1</v>
       </c>
       <c r="AN205" t="n">
         <v>2.5</v>
       </c>
       <c r="AO205" t="n">
-        <v>0.67</v>
+        <v>1.46</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.54</v>
+        <v>2.31</v>
       </c>
       <c r="AQ205" t="n">
-        <v>0.62</v>
+        <v>1.57</v>
       </c>
       <c r="AR205" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BG205" t="n">
         <v>1.38</v>
       </c>
-      <c r="AS205" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AT205" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AU205" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV205" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW205" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX205" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY205" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ205" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA205" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB205" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC205" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD205" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BE205" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF205" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="BG205" t="n">
-        <v>1.34</v>
-      </c>
       <c r="BH205" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="BI205" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="BJ205" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BK205" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BL205" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BM205" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="BN205" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="BO205" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BP205" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="206">
@@ -45251,7 +45251,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>8309645</v>
+        <v>8309816</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -45271,197 +45271,197 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" t="n">
         <v>1</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
         <v>2</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
+          <t>['20', '75']</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>['35', '47']</t>
-        </is>
-      </c>
       <c r="Q206" t="n">
-        <v>2.58</v>
+        <v>2.05</v>
       </c>
       <c r="R206" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S206" t="n">
-        <v>3.73</v>
+        <v>5.4</v>
       </c>
       <c r="T206" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="U206" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V206" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="W206" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="X206" t="n">
-        <v>6.4</v>
+        <v>9.5</v>
       </c>
       <c r="Y206" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z206" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM206" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AA206" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB206" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AC206" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD206" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE206" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF206" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG206" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH206" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI206" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ206" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK206" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AL206" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AM206" t="n">
-        <v>1.63</v>
       </c>
       <c r="AN206" t="n">
         <v>2.5</v>
       </c>
       <c r="AO206" t="n">
-        <v>1.46</v>
+        <v>0.67</v>
       </c>
       <c r="AP206" t="n">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.57</v>
+        <v>0.62</v>
       </c>
       <c r="AR206" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS206" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI206" t="n">
         <v>1.61</v>
       </c>
-      <c r="AT206" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AU206" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV206" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW206" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX206" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY206" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ206" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA206" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB206" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC206" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD206" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BE206" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BF206" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BG206" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BH206" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI206" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BJ206" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="BK206" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BL206" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BM206" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="BN206" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO206" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BP206" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="207">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -47581,13 +47581,13 @@
         <v>9</v>
       </c>
       <c r="AV216" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW216" t="n">
         <v>12</v>
       </c>
       <c r="AX216" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY216" t="n">
         <v>21</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
         <v>2.5</v>
@@ -1350,7 +1350,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.5</v>
@@ -3530,7 +3530,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>3</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ18" t="n">
         <v>2.5</v>
@@ -4620,7 +4620,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR19" t="n">
         <v>0.72</v>
@@ -6579,7 +6579,7 @@
         <v>1</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.36</v>
@@ -6797,7 +6797,7 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.46</v>
@@ -7018,7 +7018,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR30" t="n">
         <v>1.59</v>
@@ -7454,7 +7454,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR32" t="n">
         <v>1.89</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.92</v>
@@ -7887,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.6899999999999999</v>
@@ -8977,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR39" t="n">
         <v>1.57</v>
@@ -10724,7 +10724,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR47" t="n">
         <v>1.59</v>
@@ -11375,7 +11375,7 @@
         <v>1.67</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.57</v>
@@ -11596,7 +11596,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR51" t="n">
         <v>1.33</v>
@@ -12247,7 +12247,7 @@
         <v>0.33</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.5</v>
@@ -12683,10 +12683,10 @@
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR56" t="n">
         <v>1.62</v>
@@ -12904,7 +12904,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR57" t="n">
         <v>1.17</v>
@@ -14430,7 +14430,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR64" t="n">
         <v>1.6</v>
@@ -15520,7 +15520,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR69" t="n">
         <v>1.22</v>
@@ -15735,7 +15735,7 @@
         <v>1.5</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.14</v>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR71" t="n">
         <v>1.29</v>
@@ -16825,7 +16825,7 @@
         <v>1.25</v>
       </c>
       <c r="AP75" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.6899999999999999</v>
@@ -17043,7 +17043,7 @@
         <v>0.2</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.62</v>
@@ -18133,7 +18133,7 @@
         <v>2</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ81" t="n">
         <v>1.46</v>
@@ -18572,7 +18572,7 @@
         <v>1</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR83" t="n">
         <v>1.51</v>
@@ -19223,7 +19223,7 @@
         <v>1</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.92</v>
@@ -19444,7 +19444,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR87" t="n">
         <v>1.56</v>
@@ -19662,7 +19662,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR88" t="n">
         <v>1.91</v>
@@ -20531,7 +20531,7 @@
         <v>0.4</v>
       </c>
       <c r="AP92" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.62</v>
@@ -20749,7 +20749,7 @@
         <v>0.83</v>
       </c>
       <c r="AP93" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.6899999999999999</v>
@@ -22711,7 +22711,7 @@
         <v>1.5</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ102" t="n">
         <v>1.14</v>
@@ -22929,7 +22929,7 @@
         <v>0.83</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.62</v>
@@ -23586,7 +23586,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR106" t="n">
         <v>1.65</v>
@@ -24237,10 +24237,10 @@
         <v>0.67</v>
       </c>
       <c r="AP109" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR109" t="n">
         <v>1.46</v>
@@ -24458,7 +24458,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR110" t="n">
         <v>2.01</v>
@@ -25763,7 +25763,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.14</v>
@@ -27943,7 +27943,7 @@
         <v>0.88</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.5</v>
@@ -28597,7 +28597,7 @@
         <v>1.14</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.07</v>
@@ -28818,7 +28818,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR130" t="n">
         <v>1.53</v>
@@ -29472,7 +29472,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR133" t="n">
         <v>1.69</v>
@@ -29905,7 +29905,7 @@
         <v>1.43</v>
       </c>
       <c r="AP135" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.14</v>
@@ -30341,7 +30341,7 @@
         <v>1.88</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.46</v>
@@ -30995,7 +30995,7 @@
         <v>0.89</v>
       </c>
       <c r="AP140" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.5</v>
@@ -31652,7 +31652,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR143" t="n">
         <v>1.54</v>
@@ -31870,7 +31870,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR144" t="n">
         <v>2</v>
@@ -32524,7 +32524,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ147" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR147" t="n">
         <v>2.04</v>
@@ -33393,7 +33393,7 @@
         <v>1.25</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.14</v>
@@ -34486,7 +34486,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR156" t="n">
         <v>1.71</v>
@@ -35140,7 +35140,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR159" t="n">
         <v>1.54</v>
@@ -35573,7 +35573,7 @@
         <v>1.2</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ161" t="n">
         <v>1.57</v>
@@ -36009,7 +36009,7 @@
         <v>2.3</v>
       </c>
       <c r="AP163" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ163" t="n">
         <v>2.5</v>
@@ -36230,7 +36230,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR164" t="n">
         <v>1.48</v>
@@ -36663,7 +36663,7 @@
         <v>1.38</v>
       </c>
       <c r="AP166" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.07</v>
@@ -37756,7 +37756,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR171" t="n">
         <v>1.52</v>
@@ -37971,7 +37971,7 @@
         <v>0.4</v>
       </c>
       <c r="AP172" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.36</v>
@@ -38410,7 +38410,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR174" t="n">
         <v>1.46</v>
@@ -39064,7 +39064,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ177" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR177" t="n">
         <v>1.29</v>
@@ -39933,7 +39933,7 @@
         <v>1.09</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ181" t="n">
         <v>1.5</v>
@@ -41241,7 +41241,7 @@
         <v>0.73</v>
       </c>
       <c r="AP187" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ187" t="n">
         <v>0.62</v>
@@ -41459,7 +41459,7 @@
         <v>1.33</v>
       </c>
       <c r="AP188" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.57</v>
@@ -41895,10 +41895,10 @@
         <v>1.27</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR190" t="n">
         <v>1.4</v>
@@ -42552,7 +42552,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR193" t="n">
         <v>1.74</v>
@@ -43424,7 +43424,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ197" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR197" t="n">
         <v>1.8</v>
@@ -44293,10 +44293,10 @@
         <v>1.17</v>
       </c>
       <c r="AP201" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AR201" t="n">
         <v>1.53</v>
@@ -44511,7 +44511,7 @@
         <v>0.42</v>
       </c>
       <c r="AP202" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AQ202" t="n">
         <v>0.62</v>
@@ -45604,7 +45604,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ207" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR207" t="n">
         <v>1.61</v>
@@ -46040,7 +46040,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ209" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR209" t="n">
         <v>2</v>
@@ -47784,7 +47784,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ217" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AR217" t="n">
         <v>1.82</v>
@@ -47860,6 +47860,660 @@
       </c>
       <c r="BP217" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>8309648</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>45982.83333333334</v>
+      </c>
+      <c r="F218" t="n">
+        <v>28</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>2</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="n">
+        <v>2</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>['87', '90+6']</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="R218" t="n">
+        <v>2</v>
+      </c>
+      <c r="S218" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="T218" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U218" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V218" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W218" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X218" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY218" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA218" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB218" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>8309827</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>45982.83333333334</v>
+      </c>
+      <c r="F219" t="n">
+        <v>28</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1</v>
+      </c>
+      <c r="K219" t="n">
+        <v>1</v>
+      </c>
+      <c r="L219" t="n">
+        <v>2</v>
+      </c>
+      <c r="M219" t="n">
+        <v>1</v>
+      </c>
+      <c r="N219" t="n">
+        <v>3</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>['48', '56']</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>['45+3']</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R219" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S219" t="n">
+        <v>3</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U219" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V219" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="W219" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X219" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW219" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX219" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY219" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ219" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA219" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB219" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC219" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BE219" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF219" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI219" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ219" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BK219" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM219" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BN219" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO219" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BP219" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>8309646</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>45982.83333333334</v>
+      </c>
+      <c r="F220" t="n">
+        <v>28</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>3</v>
+      </c>
+      <c r="R220" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S220" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U220" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="V220" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="W220" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X220" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -48017,19 +48017,19 @@
         <v>5</v>
       </c>
       <c r="AV218" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW218" t="n">
         <v>11</v>
       </c>
       <c r="AX218" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY218" t="n">
         <v>16</v>
       </c>
       <c r="AZ218" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA218" t="n">
         <v>8</v>
@@ -48232,22 +48232,22 @@
         <v>2.84</v>
       </c>
       <c r="AU219" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV219" t="n">
         <v>2</v>
       </c>
       <c r="AW219" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX219" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY219" t="n">
         <v>19</v>
       </c>
       <c r="AZ219" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA219" t="n">
         <v>6</v>
@@ -48459,13 +48459,13 @@
         <v>7</v>
       </c>
       <c r="AX220" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY220" t="n">
         <v>9</v>
       </c>
       <c r="AZ220" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA220" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP220"/>
+  <dimension ref="A1:BP224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.6899999999999999</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.14</v>
@@ -2658,7 +2658,7 @@
         <v>1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.5</v>
@@ -3748,7 +3748,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR16" t="n">
         <v>3.87</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.57</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.5</v>
@@ -5710,7 +5710,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR24" t="n">
         <v>1.15</v>
@@ -6800,7 +6800,7 @@
         <v>1</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR29" t="n">
         <v>1.27</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ30" t="n">
         <v>1.21</v>
@@ -7233,10 +7233,10 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR31" t="n">
         <v>2.2</v>
@@ -7451,7 +7451,7 @@
         <v>0.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.71</v>
@@ -7672,7 +7672,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR33" t="n">
         <v>1.92</v>
@@ -8326,7 +8326,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR36" t="n">
         <v>1.35</v>
@@ -9195,10 +9195,10 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR40" t="n">
         <v>2.04</v>
@@ -9416,7 +9416,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR41" t="n">
         <v>1.94</v>
@@ -10067,7 +10067,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.36</v>
@@ -10288,7 +10288,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR45" t="n">
         <v>1.09</v>
@@ -10503,7 +10503,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ46" t="n">
         <v>1.14</v>
@@ -10939,7 +10939,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.6899999999999999</v>
@@ -11814,7 +11814,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR52" t="n">
         <v>1.81</v>
@@ -12468,7 +12468,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR55" t="n">
         <v>2.62</v>
@@ -13119,7 +13119,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.36</v>
@@ -13340,7 +13340,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR59" t="n">
         <v>1.73</v>
@@ -13555,10 +13555,10 @@
         <v>2.33</v>
       </c>
       <c r="AP60" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR60" t="n">
         <v>1.99</v>
@@ -13994,7 +13994,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR62" t="n">
         <v>1.58</v>
@@ -14427,7 +14427,7 @@
         <v>0.25</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.71</v>
@@ -14863,7 +14863,7 @@
         <v>2</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ66" t="n">
         <v>2.5</v>
@@ -15081,7 +15081,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.5</v>
@@ -15302,7 +15302,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR68" t="n">
         <v>1.79</v>
@@ -16174,7 +16174,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR72" t="n">
         <v>1.62</v>
@@ -16607,7 +16607,7 @@
         <v>1.25</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.57</v>
@@ -17046,7 +17046,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR76" t="n">
         <v>1.64</v>
@@ -17264,7 +17264,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR77" t="n">
         <v>1.53</v>
@@ -17915,7 +17915,7 @@
         <v>1</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.5</v>
@@ -18136,7 +18136,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR81" t="n">
         <v>1.44</v>
@@ -18787,7 +18787,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.07</v>
@@ -19226,7 +19226,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR86" t="n">
         <v>1.44</v>
@@ -19659,7 +19659,7 @@
         <v>0.6</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.5</v>
@@ -19877,10 +19877,10 @@
         <v>2.17</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR89" t="n">
         <v>1.74</v>
@@ -20313,10 +20313,10 @@
         <v>0.17</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR91" t="n">
         <v>1.71</v>
@@ -20534,7 +20534,7 @@
         <v>1</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR92" t="n">
         <v>1.52</v>
@@ -22932,7 +22932,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR103" t="n">
         <v>1.38</v>
@@ -23150,7 +23150,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR104" t="n">
         <v>1.69</v>
@@ -23365,7 +23365,7 @@
         <v>0.71</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ105" t="n">
         <v>0.6899999999999999</v>
@@ -23583,7 +23583,7 @@
         <v>0.5</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.5</v>
@@ -23801,10 +23801,10 @@
         <v>0.8</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR107" t="n">
         <v>1.67</v>
@@ -24455,7 +24455,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ110" t="n">
         <v>1.21</v>
@@ -25330,7 +25330,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR114" t="n">
         <v>1.16</v>
@@ -26420,7 +26420,7 @@
         <v>1</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR119" t="n">
         <v>1.41</v>
@@ -26635,7 +26635,7 @@
         <v>1.17</v>
       </c>
       <c r="AP120" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.14</v>
@@ -27292,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR123" t="n">
         <v>1.36</v>
@@ -27507,10 +27507,10 @@
         <v>0.5</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR124" t="n">
         <v>2.02</v>
@@ -27725,7 +27725,7 @@
         <v>0.25</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.5</v>
@@ -28164,7 +28164,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR127" t="n">
         <v>1.6</v>
@@ -29251,7 +29251,7 @@
         <v>0.88</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.14</v>
@@ -29687,7 +29687,7 @@
         <v>2.13</v>
       </c>
       <c r="AP134" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ134" t="n">
         <v>2.5</v>
@@ -30126,7 +30126,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR136" t="n">
         <v>1.33</v>
@@ -30344,7 +30344,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR137" t="n">
         <v>1.64</v>
@@ -30562,7 +30562,7 @@
         <v>1</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR138" t="n">
         <v>1.36</v>
@@ -30777,7 +30777,7 @@
         <v>0.5</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.36</v>
@@ -31213,10 +31213,10 @@
         <v>1</v>
       </c>
       <c r="AP141" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR141" t="n">
         <v>1.69</v>
@@ -31431,7 +31431,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.6899999999999999</v>
@@ -32306,7 +32306,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR146" t="n">
         <v>1.34</v>
@@ -33832,7 +33832,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ153" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR153" t="n">
         <v>1.25</v>
@@ -34050,7 +34050,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR154" t="n">
         <v>1.48</v>
@@ -34265,7 +34265,7 @@
         <v>0.9</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ155" t="n">
         <v>1.5</v>
@@ -34483,7 +34483,7 @@
         <v>1.56</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.21</v>
@@ -35137,7 +35137,7 @@
         <v>0.88</v>
       </c>
       <c r="AP159" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.71</v>
@@ -35794,7 +35794,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR162" t="n">
         <v>1.61</v>
@@ -36227,7 +36227,7 @@
         <v>0.33</v>
       </c>
       <c r="AP164" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ164" t="n">
         <v>0.5</v>
@@ -36884,7 +36884,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ167" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR167" t="n">
         <v>1.62</v>
@@ -37102,7 +37102,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR168" t="n">
         <v>1.28</v>
@@ -37535,7 +37535,7 @@
         <v>1.3</v>
       </c>
       <c r="AP170" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.14</v>
@@ -37753,7 +37753,7 @@
         <v>1.4</v>
       </c>
       <c r="AP171" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ171" t="n">
         <v>1.21</v>
@@ -38189,10 +38189,10 @@
         <v>1.22</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ173" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR173" t="n">
         <v>2.12</v>
@@ -38628,7 +38628,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR175" t="n">
         <v>1.66</v>
@@ -38843,7 +38843,7 @@
         <v>1.56</v>
       </c>
       <c r="AP176" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.07</v>
@@ -40151,7 +40151,7 @@
         <v>0.27</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.5</v>
@@ -40372,7 +40372,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR183" t="n">
         <v>1.66</v>
@@ -40587,7 +40587,7 @@
         <v>1.4</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.07</v>
@@ -41026,7 +41026,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR186" t="n">
         <v>2.05</v>
@@ -41244,7 +41244,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ187" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR187" t="n">
         <v>1.52</v>
@@ -42113,7 +42113,7 @@
         <v>0.91</v>
       </c>
       <c r="AP191" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ191" t="n">
         <v>1.14</v>
@@ -43203,10 +43203,10 @@
         <v>1.09</v>
       </c>
       <c r="AP196" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ196" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR196" t="n">
         <v>1.53</v>
@@ -43639,7 +43639,7 @@
         <v>2.42</v>
       </c>
       <c r="AP198" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ198" t="n">
         <v>2.5</v>
@@ -44075,7 +44075,7 @@
         <v>0.36</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ200" t="n">
         <v>0.36</v>
@@ -44514,7 +44514,7 @@
         <v>1</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR202" t="n">
         <v>1.5</v>
@@ -44950,7 +44950,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ204" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR204" t="n">
         <v>1.33</v>
@@ -45165,7 +45165,7 @@
         <v>1.46</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AQ205" t="n">
         <v>1.57</v>
@@ -45383,10 +45383,10 @@
         <v>0.67</v>
       </c>
       <c r="AP206" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ206" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR206" t="n">
         <v>1.38</v>
@@ -47127,7 +47127,7 @@
         <v>1.15</v>
       </c>
       <c r="AP214" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AQ214" t="n">
         <v>1.07</v>
@@ -48514,6 +48514,878 @@
       </c>
       <c r="BP220" t="n">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>8309835</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>45983.75</v>
+      </c>
+      <c r="F221" t="n">
+        <v>28</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>2</v>
+      </c>
+      <c r="M221" t="n">
+        <v>1</v>
+      </c>
+      <c r="N221" t="n">
+        <v>3</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>['83', '90+1']</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R221" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S221" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T221" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U221" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V221" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W221" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X221" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO221" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP221" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>8309830</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>45983.85416666666</v>
+      </c>
+      <c r="F222" t="n">
+        <v>28</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>1</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>1</v>
+      </c>
+      <c r="L222" t="n">
+        <v>2</v>
+      </c>
+      <c r="M222" t="n">
+        <v>1</v>
+      </c>
+      <c r="N222" t="n">
+        <v>3</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>['33', '59']</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R222" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S222" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T222" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U222" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V222" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="W222" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X222" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AU222" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV222" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW222" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX222" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY222" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ222" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA222" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB222" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC222" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE222" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF222" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI222" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ222" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK222" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BL222" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM222" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BN222" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO222" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BP222" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>8309692</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>45984.75</v>
+      </c>
+      <c r="F223" t="n">
+        <v>28</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>1</v>
+      </c>
+      <c r="K223" t="n">
+        <v>1</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" t="n">
+        <v>1</v>
+      </c>
+      <c r="N223" t="n">
+        <v>1</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R223" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S223" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T223" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U223" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V223" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W223" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X223" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU223" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY223" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA223" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB223" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC223" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BE223" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BF223" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH223" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI223" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BM223" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN223" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BO223" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP223" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>8309690</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>45984.85416666666</v>
+      </c>
+      <c r="F224" t="n">
+        <v>28</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>3</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>3</v>
+      </c>
+      <c r="L224" t="n">
+        <v>4</v>
+      </c>
+      <c r="M224" t="n">
+        <v>1</v>
+      </c>
+      <c r="N224" t="n">
+        <v>5</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>['8', '16', '25', '85']</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R224" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S224" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T224" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U224" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V224" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W224" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X224" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AU224" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV224" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW224" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB224" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC224" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BE224" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH224" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BI224" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ224" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BK224" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL224" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM224" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BN224" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO224" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP224" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -48032,13 +48032,13 @@
         <v>21</v>
       </c>
       <c r="BA218" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB218" t="n">
         <v>5</v>
       </c>
       <c r="BC218" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD218" t="n">
         <v>1.64</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP224"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.36</v>
@@ -6146,7 +6146,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR26" t="n">
         <v>1.32</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.5</v>
@@ -7890,7 +7890,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR34" t="n">
         <v>1.42</v>
@@ -9849,7 +9849,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.5</v>
@@ -10942,7 +10942,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR48" t="n">
         <v>1.88</v>
@@ -13773,7 +13773,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ61" t="n">
         <v>2.5</v>
@@ -13991,7 +13991,7 @@
         <v>0.25</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.57</v>
@@ -16828,7 +16828,7 @@
         <v>1</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR75" t="n">
         <v>1.64</v>
@@ -17261,7 +17261,7 @@
         <v>0.25</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.57</v>
@@ -18354,7 +18354,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR82" t="n">
         <v>2.2</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.57</v>
@@ -20752,7 +20752,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR93" t="n">
         <v>1.7</v>
@@ -23368,7 +23368,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR105" t="n">
         <v>1.7</v>
@@ -24019,7 +24019,7 @@
         <v>1.17</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ108" t="n">
         <v>1.14</v>
@@ -28161,7 +28161,7 @@
         <v>1</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.07</v>
@@ -29036,7 +29036,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR131" t="n">
         <v>1.57</v>
@@ -31434,7 +31434,7 @@
         <v>2</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR142" t="n">
         <v>2.04</v>
@@ -31649,7 +31649,7 @@
         <v>1</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.71</v>
@@ -34047,7 +34047,7 @@
         <v>1.78</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ154" t="n">
         <v>1.36</v>
@@ -36448,7 +36448,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR165" t="n">
         <v>1.59</v>
@@ -38407,7 +38407,7 @@
         <v>0.3</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.5</v>
@@ -39718,7 +39718,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ180" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR180" t="n">
         <v>1.72</v>
@@ -40808,7 +40808,7 @@
         <v>1</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AR185" t="n">
         <v>1.54</v>
@@ -44729,7 +44729,7 @@
         <v>0.83</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.14</v>
@@ -49386,6 +49386,224 @@
       </c>
       <c r="BP224" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>8309657</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>45985.83333333334</v>
+      </c>
+      <c r="F225" t="n">
+        <v>28</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>1</v>
+      </c>
+      <c r="N225" t="n">
+        <v>1</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R225" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S225" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T225" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U225" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V225" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W225" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X225" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ225" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AT225" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV225" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW225" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX225" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY225" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ225" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA225" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB225" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC225" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BE225" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF225" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BG225" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH225" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI225" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ225" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK225" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BL225" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BM225" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BN225" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO225" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP225" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -48677,13 +48677,13 @@
         <v>10</v>
       </c>
       <c r="AX221" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY221" t="n">
         <v>15</v>
       </c>
       <c r="AZ221" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA221" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,7 +1786,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.57</v>
@@ -5492,7 +5492,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR23" t="n">
         <v>1.24</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.07</v>
@@ -8541,7 +8541,7 @@
         <v>2</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.57</v>
@@ -11157,7 +11157,7 @@
         <v>1.33</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.5</v>
@@ -14645,7 +14645,7 @@
         <v>0.25</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.36</v>
@@ -15738,7 +15738,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR70" t="n">
         <v>1.48</v>
@@ -17697,7 +17697,7 @@
         <v>0.75</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.14</v>
@@ -22060,7 +22060,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR99" t="n">
         <v>1.34</v>
@@ -22275,7 +22275,7 @@
         <v>0.33</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ100" t="n">
         <v>0.5</v>
@@ -22714,7 +22714,7 @@
         <v>1</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR102" t="n">
         <v>1.56</v>
@@ -25766,7 +25766,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR116" t="n">
         <v>1.77</v>
@@ -25981,7 +25981,7 @@
         <v>1.17</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.07</v>
@@ -26638,7 +26638,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR120" t="n">
         <v>1.67</v>
@@ -26856,7 +26856,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR121" t="n">
         <v>2.12</v>
@@ -29254,7 +29254,7 @@
         <v>2</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR132" t="n">
         <v>1.66</v>
@@ -32960,7 +32960,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ149" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR149" t="n">
         <v>1.61</v>
@@ -33175,7 +33175,7 @@
         <v>2.22</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ150" t="n">
         <v>2.5</v>
@@ -35358,7 +35358,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR160" t="n">
         <v>1.75</v>
@@ -35791,7 +35791,7 @@
         <v>0.8</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.57</v>
@@ -38625,7 +38625,7 @@
         <v>1.73</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ175" t="n">
         <v>1.36</v>
@@ -39715,7 +39715,7 @@
         <v>0.82</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ180" t="n">
         <v>0.86</v>
@@ -42116,7 +42116,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR191" t="n">
         <v>1.44</v>
@@ -43421,7 +43421,7 @@
         <v>0.55</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ197" t="n">
         <v>0.5</v>
@@ -44732,7 +44732,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR203" t="n">
         <v>1.44</v>
@@ -46694,7 +46694,7 @@
         <v>1</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR212" t="n">
         <v>1.53</v>
@@ -47781,7 +47781,7 @@
         <v>0.58</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AQ217" t="n">
         <v>0.71</v>
@@ -49604,6 +49604,224 @@
       </c>
       <c r="BP225" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>8309652</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>45989.77083333334</v>
+      </c>
+      <c r="F226" t="n">
+        <v>29</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Colo-Colo</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>2</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>2</v>
+      </c>
+      <c r="L226" t="n">
+        <v>3</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="n">
+        <v>3</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>['12', '44', '50']</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R226" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S226" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T226" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="U226" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V226" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="W226" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X226" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN226" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AU226" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV226" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW226" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX226" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY226" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA226" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB226" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC226" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BE226" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF226" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BG226" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH226" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BI226" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ226" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK226" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL226" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM226" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BN226" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO226" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BP226" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.07</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.5</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.71</v>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.5</v>
@@ -5056,7 +5056,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR21" t="n">
         <v>1.26</v>
@@ -5271,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.07</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.07</v>
@@ -5925,10 +5925,10 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR25" t="n">
         <v>1.21</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.86</v>
@@ -6364,7 +6364,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR27" t="n">
         <v>1.93</v>
@@ -6582,7 +6582,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR28" t="n">
         <v>1.8</v>
@@ -6800,7 +6800,7 @@
         <v>1</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR29" t="n">
         <v>1.27</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ35" t="n">
         <v>2.5</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.57</v>
@@ -8544,7 +8544,7 @@
         <v>2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR37" t="n">
         <v>1.67</v>
@@ -9198,7 +9198,7 @@
         <v>2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR40" t="n">
         <v>2.04</v>
@@ -9413,7 +9413,7 @@
         <v>0.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.07</v>
@@ -9631,10 +9631,10 @@
         <v>0.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR42" t="n">
         <v>1.19</v>
@@ -9852,7 +9852,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR43" t="n">
         <v>1.59</v>
@@ -10070,7 +10070,7 @@
         <v>2</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR44" t="n">
         <v>2.2</v>
@@ -10285,7 +10285,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.57</v>
@@ -10721,7 +10721,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.21</v>
@@ -11160,7 +11160,7 @@
         <v>2</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR49" t="n">
         <v>1.45</v>
@@ -11378,7 +11378,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR50" t="n">
         <v>1.74</v>
@@ -11593,7 +11593,7 @@
         <v>0.33</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.71</v>
@@ -12029,7 +12029,7 @@
         <v>1</v>
       </c>
       <c r="AP53" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ53" t="n">
         <v>1.07</v>
@@ -12250,7 +12250,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR54" t="n">
         <v>1.19</v>
@@ -12901,7 +12901,7 @@
         <v>0.33</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.21</v>
@@ -13122,7 +13122,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR58" t="n">
         <v>1.48</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ59" t="n">
         <v>0.57</v>
@@ -13558,7 +13558,7 @@
         <v>2</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR60" t="n">
         <v>1.99</v>
@@ -14209,7 +14209,7 @@
         <v>1</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.14</v>
@@ -14648,7 +14648,7 @@
         <v>2</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR65" t="n">
         <v>1.44</v>
@@ -15084,7 +15084,7 @@
         <v>2</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR67" t="n">
         <v>1.92</v>
@@ -15517,7 +15517,7 @@
         <v>0.75</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.5</v>
@@ -15953,7 +15953,7 @@
         <v>1</v>
       </c>
       <c r="AP71" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.21</v>
@@ -16171,10 +16171,10 @@
         <v>1.75</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR72" t="n">
         <v>1.62</v>
@@ -16392,7 +16392,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR73" t="n">
         <v>2.4</v>
@@ -16610,7 +16610,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR74" t="n">
         <v>1.85</v>
@@ -17479,7 +17479,7 @@
         <v>1.6</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ78" t="n">
         <v>2.5</v>
@@ -17918,7 +17918,7 @@
         <v>2</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR80" t="n">
         <v>1.8</v>
@@ -18136,7 +18136,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR81" t="n">
         <v>1.44</v>
@@ -18569,7 +18569,7 @@
         <v>0.2</v>
       </c>
       <c r="AP83" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.71</v>
@@ -19005,10 +19005,10 @@
         <v>0.4</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR85" t="n">
         <v>1.34</v>
@@ -19441,7 +19441,7 @@
         <v>1.4</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.21</v>
@@ -19880,7 +19880,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR89" t="n">
         <v>1.74</v>
@@ -20098,7 +20098,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR90" t="n">
         <v>1.54</v>
@@ -20967,7 +20967,7 @@
         <v>0.8</v>
       </c>
       <c r="AP94" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.07</v>
@@ -21185,7 +21185,7 @@
         <v>1.83</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ95" t="n">
         <v>2.5</v>
@@ -21406,7 +21406,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR96" t="n">
         <v>2.1</v>
@@ -21621,7 +21621,7 @@
         <v>1.2</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.14</v>
@@ -21842,7 +21842,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR98" t="n">
         <v>1.82</v>
@@ -22057,7 +22057,7 @@
         <v>1</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.07</v>
@@ -22278,7 +22278,7 @@
         <v>2</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR100" t="n">
         <v>1.51</v>
@@ -22493,10 +22493,10 @@
         <v>0.2</v>
       </c>
       <c r="AP101" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR101" t="n">
         <v>1.38</v>
@@ -24673,10 +24673,10 @@
         <v>0.86</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR111" t="n">
         <v>1.4</v>
@@ -24891,7 +24891,7 @@
         <v>2</v>
       </c>
       <c r="AP112" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ112" t="n">
         <v>2.5</v>
@@ -25112,7 +25112,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR113" t="n">
         <v>2.07</v>
@@ -25327,10 +25327,10 @@
         <v>2</v>
       </c>
       <c r="AP114" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR114" t="n">
         <v>1.16</v>
@@ -25545,10 +25545,10 @@
         <v>0.33</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR115" t="n">
         <v>1.48</v>
@@ -26199,10 +26199,10 @@
         <v>1.14</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR118" t="n">
         <v>1.63</v>
@@ -26417,7 +26417,7 @@
         <v>0.67</v>
       </c>
       <c r="AP119" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.07</v>
@@ -27071,10 +27071,10 @@
         <v>0.43</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR122" t="n">
         <v>1.56</v>
@@ -27289,7 +27289,7 @@
         <v>1.14</v>
       </c>
       <c r="AP123" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.57</v>
@@ -27728,7 +27728,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR125" t="n">
         <v>1.52</v>
@@ -27946,7 +27946,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR126" t="n">
         <v>1.72</v>
@@ -28379,10 +28379,10 @@
         <v>1.38</v>
       </c>
       <c r="AP128" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR128" t="n">
         <v>1.28</v>
@@ -28815,7 +28815,7 @@
         <v>1.14</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.21</v>
@@ -29033,7 +29033,7 @@
         <v>0.63</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.86</v>
@@ -30123,7 +30123,7 @@
         <v>1</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.07</v>
@@ -30344,7 +30344,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR137" t="n">
         <v>1.64</v>
@@ -30559,7 +30559,7 @@
         <v>0.44</v>
       </c>
       <c r="AP138" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.57</v>
@@ -30780,7 +30780,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR139" t="n">
         <v>1.56</v>
@@ -30998,7 +30998,7 @@
         <v>1</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR140" t="n">
         <v>1.45</v>
@@ -32088,7 +32088,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR145" t="n">
         <v>1.7</v>
@@ -32303,7 +32303,7 @@
         <v>0.89</v>
       </c>
       <c r="AP146" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.57</v>
@@ -32739,10 +32739,10 @@
         <v>1.22</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR148" t="n">
         <v>1.58</v>
@@ -32957,7 +32957,7 @@
         <v>0.89</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ149" t="n">
         <v>1.07</v>
@@ -33611,10 +33611,10 @@
         <v>0.2</v>
       </c>
       <c r="AP152" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR152" t="n">
         <v>1.48</v>
@@ -33829,7 +33829,7 @@
         <v>0.4</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.57</v>
@@ -34050,7 +34050,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR154" t="n">
         <v>1.48</v>
@@ -34268,7 +34268,7 @@
         <v>2</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR155" t="n">
         <v>2.11</v>
@@ -34919,10 +34919,10 @@
         <v>0.44</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR158" t="n">
         <v>1.34</v>
@@ -35576,7 +35576,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR161" t="n">
         <v>1.41</v>
@@ -36445,7 +36445,7 @@
         <v>0.6</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ165" t="n">
         <v>0.86</v>
@@ -36881,7 +36881,7 @@
         <v>0.45</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ167" t="n">
         <v>0.57</v>
@@ -37099,10 +37099,10 @@
         <v>1.6</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR168" t="n">
         <v>1.28</v>
@@ -37317,7 +37317,7 @@
         <v>2.36</v>
       </c>
       <c r="AP169" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ169" t="n">
         <v>2.5</v>
@@ -37974,7 +37974,7 @@
         <v>1</v>
       </c>
       <c r="AQ172" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR172" t="n">
         <v>1.46</v>
@@ -38628,7 +38628,7 @@
         <v>2</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR175" t="n">
         <v>1.66</v>
@@ -39061,7 +39061,7 @@
         <v>0.78</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ177" t="n">
         <v>0.71</v>
@@ -39279,7 +39279,7 @@
         <v>1.18</v>
       </c>
       <c r="AP178" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.14</v>
@@ -39500,7 +39500,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR179" t="n">
         <v>1.8</v>
@@ -39936,7 +39936,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR181" t="n">
         <v>1.4</v>
@@ -40154,7 +40154,7 @@
         <v>2</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR182" t="n">
         <v>2.12</v>
@@ -40369,7 +40369,7 @@
         <v>1.1</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.07</v>
@@ -40805,7 +40805,7 @@
         <v>0.75</v>
       </c>
       <c r="AP185" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ185" t="n">
         <v>0.86</v>
@@ -41026,7 +41026,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR186" t="n">
         <v>2.05</v>
@@ -41462,7 +41462,7 @@
         <v>1</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR188" t="n">
         <v>1.55</v>
@@ -41677,7 +41677,7 @@
         <v>1.27</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.07</v>
@@ -42331,10 +42331,10 @@
         <v>1.25</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR192" t="n">
         <v>1.65</v>
@@ -42767,7 +42767,7 @@
         <v>1.33</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ194" t="n">
         <v>1.14</v>
@@ -42985,10 +42985,10 @@
         <v>0.25</v>
       </c>
       <c r="AP195" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR195" t="n">
         <v>1.33</v>
@@ -43857,7 +43857,7 @@
         <v>1.25</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.07</v>
@@ -44078,7 +44078,7 @@
         <v>2</v>
       </c>
       <c r="AQ200" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR200" t="n">
         <v>2.17</v>
@@ -44947,7 +44947,7 @@
         <v>1</v>
       </c>
       <c r="AP204" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ204" t="n">
         <v>1.07</v>
@@ -45168,7 +45168,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR205" t="n">
         <v>1.51</v>
@@ -45601,7 +45601,7 @@
         <v>0.5</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ207" t="n">
         <v>0.5</v>
@@ -45822,7 +45822,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR208" t="n">
         <v>1.72</v>
@@ -46255,10 +46255,10 @@
         <v>0.31</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ210" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AR210" t="n">
         <v>1.3</v>
@@ -46473,10 +46473,10 @@
         <v>1.38</v>
       </c>
       <c r="AP211" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AR211" t="n">
         <v>1.54</v>
@@ -46691,7 +46691,7 @@
         <v>1</v>
       </c>
       <c r="AP212" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.07</v>
@@ -47345,7 +47345,7 @@
         <v>1.23</v>
       </c>
       <c r="AP215" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.14</v>
@@ -47566,7 +47566,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ216" t="n">
-        <v>0.36</v>
+        <v>0.53</v>
       </c>
       <c r="AR216" t="n">
         <v>1.96</v>
@@ -48874,7 +48874,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AR222" t="n">
         <v>1.53</v>
@@ -49822,6 +49822,1096 @@
       </c>
       <c r="BP226" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>8309821</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>45990.5</v>
+      </c>
+      <c r="F227" t="n">
+        <v>29</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R227" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S227" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T227" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U227" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="V227" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W227" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X227" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ227" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT227" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AU227" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV227" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW227" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX227" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY227" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ227" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA227" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB227" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC227" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BE227" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="BF227" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG227" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH227" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI227" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ227" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK227" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL227" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM227" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN227" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO227" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP227" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>8309831</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>45990.75</v>
+      </c>
+      <c r="F228" t="n">
+        <v>29</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" t="n">
+        <v>3</v>
+      </c>
+      <c r="N228" t="n">
+        <v>3</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>['71', '74', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R228" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S228" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T228" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U228" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V228" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W228" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X228" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU228" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV228" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW228" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX228" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY228" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA228" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB228" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC228" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BE228" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF228" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BG228" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH228" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI228" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ228" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK228" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL228" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM228" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN228" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO228" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BP228" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>8309828</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>45991.75</v>
+      </c>
+      <c r="F229" t="n">
+        <v>29</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" t="n">
+        <v>1</v>
+      </c>
+      <c r="N229" t="n">
+        <v>1</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R229" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S229" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T229" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="U229" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V229" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W229" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X229" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU229" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV229" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA229" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB229" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC229" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BE229" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="BF229" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BG229" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH229" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="BI229" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ229" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BK229" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BL229" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM229" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN229" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO229" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BP229" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>8309639</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>45991.75</v>
+      </c>
+      <c r="F230" t="n">
+        <v>29</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" t="n">
+        <v>1</v>
+      </c>
+      <c r="N230" t="n">
+        <v>1</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="R230" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S230" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T230" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U230" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V230" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W230" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X230" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU230" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY230" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA230" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB230" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC230" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE230" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF230" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BG230" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH230" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI230" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ230" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK230" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL230" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM230" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BN230" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO230" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP230" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>8309640</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="n">
+        <v>45991.75</v>
+      </c>
+      <c r="F231" t="n">
+        <v>29</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>1</v>
+      </c>
+      <c r="J231" t="n">
+        <v>1</v>
+      </c>
+      <c r="K231" t="n">
+        <v>2</v>
+      </c>
+      <c r="L231" t="n">
+        <v>2</v>
+      </c>
+      <c r="M231" t="n">
+        <v>4</v>
+      </c>
+      <c r="N231" t="n">
+        <v>6</v>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>['14', '83']</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>['25', '49', '90+7', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R231" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S231" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="T231" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U231" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V231" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W231" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X231" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM231" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP231" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AQ231" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR231" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS231" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT231" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU231" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV231" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW231" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX231" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY231" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ231" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA231" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB231" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC231" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD231" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BE231" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF231" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG231" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH231" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="BI231" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ231" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BK231" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL231" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM231" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN231" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO231" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP231" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Chile Primera División_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP233"/>
+  <dimension ref="A1:BP234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.21</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.14</v>
@@ -6146,7 +6146,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR26" t="n">
         <v>1.32</v>
@@ -7890,7 +7890,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR34" t="n">
         <v>1.42</v>
@@ -8759,7 +8759,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ38" t="n">
         <v>1</v>
@@ -10942,7 +10942,7 @@
         <v>2.57</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR48" t="n">
         <v>1.88</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.57</v>
@@ -15299,7 +15299,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.07</v>
@@ -16828,7 +16828,7 @@
         <v>1</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR75" t="n">
         <v>1.64</v>
@@ -18354,7 +18354,7 @@
         <v>2.47</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR82" t="n">
         <v>2.2</v>
@@ -20752,7 +20752,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR93" t="n">
         <v>1.7</v>
@@ -21839,7 +21839,7 @@
         <v>0.83</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.47</v>
@@ -23147,7 +23147,7 @@
         <v>0.57</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.57</v>
@@ -23368,7 +23368,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR105" t="n">
         <v>1.7</v>
@@ -29036,7 +29036,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR131" t="n">
         <v>1.57</v>
@@ -29469,7 +29469,7 @@
         <v>0.43</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.5</v>
@@ -31434,7 +31434,7 @@
         <v>2</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR142" t="n">
         <v>2.04</v>
@@ -32085,7 +32085,7 @@
         <v>0.22</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.67</v>
@@ -35355,7 +35355,7 @@
         <v>0.9</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.07</v>
@@ -36448,7 +36448,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR165" t="n">
         <v>1.59</v>
@@ -39497,7 +39497,7 @@
         <v>1.18</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ179" t="n">
         <v>1.67</v>
@@ -39718,7 +39718,7 @@
         <v>2</v>
       </c>
       <c r="AQ180" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR180" t="n">
         <v>1.72</v>
@@ -40808,7 +40808,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR185" t="n">
         <v>1.54</v>
@@ -42549,7 +42549,7 @@
         <v>0.7</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ193" t="n">
         <v>0.71</v>
@@ -45819,7 +45819,7 @@
         <v>0.42</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ208" t="n">
         <v>0.53</v>
@@ -46909,7 +46909,7 @@
         <v>2.46</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ213" t="n">
         <v>2.4</v>
@@ -49528,7 +49528,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ225" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AR225" t="n">
         <v>1.4</v>
@@ -51348,6 +51348,224 @@
       </c>
       <c r="BP233" t="n">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="n">
+        <v>8309832</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="n">
+        <v>45996.83333333334</v>
+      </c>
+      <c r="F234" t="n">
+        <v>30</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>1</v>
+      </c>
+      <c r="J234" t="n">
+        <v>1</v>
+      </c>
+      <c r="K234" t="n">
+        <v>2</v>
+      </c>
+      <c r="L234" t="n">
+        <v>2</v>
+      </c>
+      <c r="M234" t="n">
+        <v>2</v>
+      </c>
+      <c r="N234" t="n">
+        <v>4</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>['45+4', '90+5']</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>['18', '82']</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R234" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S234" t="n">
+        <v>5</v>
+      </c>
+      <c r="T234" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U234" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V234" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W234" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X234" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM234" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AN234" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ234" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AR234" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS234" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT234" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV234" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW234" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX234" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY234" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ234" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA234" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB234" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC234" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD234" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE234" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF234" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="BG234" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH234" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BI234" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ234" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BK234" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL234" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM234" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN234" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO234" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BP234" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
